--- a/Appliance_parts_batch_1_H1_titles.xlsx
+++ b/Appliance_parts_batch_1_H1_titles.xlsx
@@ -5123,44 +5123,64 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="3" t="inlineStr">
+      <c r="A163" t="inlineStr">
         <is>
           <t>/products/danby-890011174</t>
         </is>
       </c>
-      <c r="B163" s="3" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>Danby</t>
         </is>
       </c>
-      <c r="C163" s="3" t="inlineStr"/>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="inlineStr"/>
-      <c r="F163" s="3" t="inlineStr"/>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Danby Refrigerator Wire Freezer Shelf - 890011174</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>genuinereplacementparts, encompass</t>
+        </is>
+      </c>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="inlineStr">
+      <c r="A164" t="inlineStr">
         <is>
           <t>/products/danby-dar044a6bsldb</t>
         </is>
       </c>
-      <c r="B164" s="3" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>Danby</t>
         </is>
       </c>
-      <c r="C164" s="3" t="inlineStr"/>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr"/>
-      <c r="F164" s="3" t="inlineStr"/>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Danby 4.4 Cu. Ft. Outdoor Compact Refrigerator Stainless Steel - DAR044A6BSLDB</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>SERP (townappliance, walmart, energystar - as DAR044A6BSLDBO)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -5183,24 +5203,32 @@
       <c r="F165" s="3" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="inlineStr">
+      <c r="A166" t="inlineStr">
         <is>
           <t>/products/goodman-zp29k5e-pfv-130</t>
         </is>
       </c>
-      <c r="B166" s="3" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>Goodman</t>
         </is>
       </c>
-      <c r="C166" s="3" t="inlineStr"/>
-      <c r="D166" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr"/>
-      <c r="F166" s="3" t="inlineStr"/>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Goodman HVAC Copeland 2.5 Ton R410A Scroll Compressor - ZP29K5E-PFV-130</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>SERP (ebay, technicalhotandcoldparts)</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -5243,104 +5271,148 @@
       <c r="F168" s="3" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="3" t="inlineStr">
+      <c r="A169" t="inlineStr">
         <is>
           <t>/products/kenmore-30120-0030100-00</t>
         </is>
       </c>
-      <c r="B169" s="3" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>Kenmore</t>
         </is>
       </c>
-      <c r="C169" s="3" t="inlineStr"/>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E169" s="3" t="inlineStr"/>
-      <c r="F169" s="3" t="inlineStr"/>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Kenmore Refrigerator Evaporator Fan Motor Assembly - 30120-0030100-00</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>searspartsdirect, genuinereplacementparts, shopjimmy, encompass</t>
+        </is>
+      </c>
     </row>
     <row r="170">
-      <c r="A170" s="3" t="inlineStr">
+      <c r="A170" t="inlineStr">
         <is>
           <t>/products/kenmore-3017837600</t>
         </is>
       </c>
-      <c r="B170" s="3" t="inlineStr">
+      <c r="B170" t="inlineStr">
         <is>
           <t>Kenmore</t>
         </is>
       </c>
-      <c r="C170" s="3" t="inlineStr"/>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="inlineStr"/>
-      <c r="F170" s="3" t="inlineStr"/>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Kenmore Refrigerator Shelf Assembly - 3017837600</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>encompass, searspartsdirect</t>
+        </is>
+      </c>
     </row>
     <row r="171">
-      <c r="A171" s="3" t="inlineStr">
+      <c r="A171" t="inlineStr">
         <is>
           <t>/products/lokring-appliance-a20160019</t>
         </is>
       </c>
-      <c r="B171" s="3" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>Lokring</t>
         </is>
       </c>
-      <c r="C171" s="3" t="inlineStr"/>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E171" s="3" t="inlineStr"/>
-      <c r="F171" s="3" t="inlineStr"/>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Lokring Appliance LG Repair Kit - A20160019</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>reliableparts, partadvantage, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="inlineStr">
+      <c r="A172" t="inlineStr">
         <is>
           <t>/products/lokring-appliance-l14000166</t>
         </is>
       </c>
-      <c r="B172" s="3" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>Lokring</t>
         </is>
       </c>
-      <c r="C172" s="3" t="inlineStr"/>
-      <c r="D172" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E172" s="3" t="inlineStr"/>
-      <c r="F172" s="3" t="inlineStr"/>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Lokring Appliance LRSZ 120 Degree Tube Cutter - L14000166</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>reliableparts, encompass, partadvantage, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="173">
-      <c r="A173" s="3" t="inlineStr">
+      <c r="A173" t="inlineStr">
         <is>
           <t>/products/magic-chef-model-hvdr1040b</t>
         </is>
       </c>
-      <c r="B173" s="3" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>Magic</t>
         </is>
       </c>
-      <c r="C173" s="3" t="inlineStr"/>
-      <c r="D173" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E173" s="3" t="inlineStr"/>
-      <c r="F173" s="3" t="inlineStr"/>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Magic Chef 9.9 Cu. Ft. Top Freezer Refrigerator Black - HVDR1040B</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>SERP (appliancefactoryparts, homedepot)</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -5363,164 +5435,248 @@
       <c r="F174" s="3" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="3" t="inlineStr">
+      <c r="A175" t="inlineStr">
         <is>
           <t>/products/midea-11002012040074</t>
         </is>
       </c>
-      <c r="B175" s="3" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C175" s="3" t="inlineStr"/>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E175" s="3" t="inlineStr"/>
-      <c r="F175" s="3" t="inlineStr"/>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Midea Washer Single Phase Asynchronous Motor - 11002012040074</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>encompass, hnkparts, searspartsdirect, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="176">
-      <c r="A176" s="3" t="inlineStr">
+      <c r="A176" t="inlineStr">
         <is>
           <t>/products/panasonic-model-nnt945sfx</t>
         </is>
       </c>
-      <c r="B176" s="3" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>Panasonic</t>
         </is>
       </c>
-      <c r="C176" s="3" t="inlineStr"/>
-      <c r="D176" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="inlineStr"/>
-      <c r="F176" s="3" t="inlineStr"/>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Panasonic 2.2 Cu. Ft. 1250W Inverter Countertop Microwave Stainless Steel - NN-T945SFX</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>SERP (bjs, appliancefactoryparts)</t>
+        </is>
+      </c>
     </row>
     <row r="177">
-      <c r="A177" s="3" t="inlineStr">
+      <c r="A177" t="inlineStr">
         <is>
           <t>/products/powermate-a203120-power-tool-control-cable</t>
         </is>
       </c>
-      <c r="B177" s="3" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>Powermate</t>
         </is>
       </c>
-      <c r="C177" s="3" t="inlineStr"/>
-      <c r="D177" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="inlineStr"/>
-      <c r="F177" s="3" t="inlineStr"/>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Powermate Tiller Forward Extension Control Cable - A203120</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="178">
-      <c r="A178" s="3" t="inlineStr">
+      <c r="A178" t="inlineStr">
         <is>
           <t>/products/ryobi-elect-tools-300627004</t>
         </is>
       </c>
-      <c r="B178" s="3" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>Ryobi</t>
         </is>
       </c>
-      <c r="C178" s="3" t="inlineStr"/>
-      <c r="D178" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="inlineStr"/>
-      <c r="F178" s="3" t="inlineStr"/>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Ryobi Router 1/2" Collet Assembly - 300627004</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>encompass, ereplacementparts, partswarehouse</t>
+        </is>
+      </c>
     </row>
     <row r="179">
-      <c r="A179" s="3" t="inlineStr">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>/products/whirlpool-model-caws923mq1</t>
         </is>
       </c>
-      <c r="B179" s="3" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C179" s="3" t="inlineStr"/>
-      <c r="D179" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E179" s="3" t="inlineStr"/>
-      <c r="F179" s="3" t="inlineStr"/>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Whirlpool Top Load Washer - CAWS923MQ1</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance, REVIEW</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>SERP (parts retailers list it as a washer model)</t>
+        </is>
+      </c>
     </row>
     <row r="180">
-      <c r="A180" s="3" t="inlineStr">
+      <c r="A180" t="inlineStr">
         <is>
           <t>/products/whirlpool-wp6-2011900</t>
         </is>
       </c>
-      <c r="B180" s="3" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C180" s="3" t="inlineStr"/>
-      <c r="D180" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="inlineStr"/>
-      <c r="F180" s="3" t="inlineStr"/>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Whirlpool Washer Brake Assembly - WP6-2011900</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>encompass, hnkparts, partsdr, applianceparts4all, appliancepartspros, searspartsdirect</t>
+        </is>
+      </c>
     </row>
     <row r="181">
-      <c r="A181" s="3" t="inlineStr">
+      <c r="A181" t="inlineStr">
         <is>
           <t>/products/ge-model-gtd75ecsl1ws</t>
         </is>
       </c>
-      <c r="B181" s="3" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C181" s="3" t="inlineStr"/>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E181" s="3" t="inlineStr"/>
-      <c r="F181" s="3" t="inlineStr"/>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>GE 7.4 Cu. Ft. Smart Electric Dryer with HE Sensor Dry - GTD75ECSL1WS</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>SERP (geappliances.com for GTD75ECSLWS, filtersfast)</t>
+        </is>
+      </c>
     </row>
     <row r="182">
-      <c r="A182" s="3" t="inlineStr">
+      <c r="A182" t="inlineStr">
         <is>
           <t>/products/lg-mgc66363126-dishwasher-control-panel</t>
         </is>
       </c>
-      <c r="B182" s="3" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C182" s="3" t="inlineStr"/>
-      <c r="D182" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E182" s="3" t="inlineStr"/>
-      <c r="F182" s="3" t="inlineStr"/>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>LG WashTower Washer/Dryer Control Panel Assembly - MGC66363126</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Your URL says "dishwasher control panel" - competitors list it for LG WashTower models</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>shopjimmy, encompass, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">

--- a/Appliance_parts_batch_1_H1_titles.xlsx
+++ b/Appliance_parts_batch_1_H1_titles.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Samsung Refrigerator Bespoke 4-Door Middle Panel Pink Glass - RA-F36DMMP0/AA</t>
+          <t>Samsung Bespoke French Door Panel (Pink Glass) - RA-F36DMMP0/AA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1159,32 +1159,32 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>/products/panasonic-f800lbr60sap-microwave-escutcheon</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Panasonic</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Panasonic Microwave Escutcheon - F800LBR60SAP</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Panasonic Microwave Escutcheon Base - F800LBR60SAP</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>NOT FOUND online - name taken from your URL</t>
         </is>
@@ -1303,32 +1303,32 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>/products/80755248-braun-shaver-clean-charge-station-series-8-9</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>80755248</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Braun Shaver Clean &amp; Charge Station Series 8/9 - 80755248</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Braun Clean &amp; Charge Station - 80755248</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>NOT FOUND online (nearest: 80755247) - name taken from your URL</t>
         </is>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Samsung TV The Frame 65-Inch Customizable Bezel Sand Gold Metal - VG-SCFC65SGMZA</t>
+          <t>Samsung The Frame Customizable Bezel (Sand Gold Metal) - VG-SCFC65SGMZA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Samsung DVM High Static Pressure Duct Air Conditioner Indoor Unit - AM140FNHDEH/EU</t>
+          <t>Samsung Medium Static Pressure Duct Air Conditioner Indoor Unit - AM140FNHDEH/EU</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2151,32 +2151,32 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>/products/midea-model-pp09hmb82</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Midea Window Air Conditioner - PP09HMB82</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Midea Pelonis Packaged Terminal Air Conditioner - PP09HMB82</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>REVIEW - model not confirmed</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>appliancefactoryparts (only a parts compatibility mention)</t>
         </is>
@@ -2847,32 +2847,32 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>/products/encompass-11000064</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>Encompass</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Encompass Part - 11000064</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Encompass Parts Switch Assembly - 11000064</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
         <is>
           <t>REVIEW - needs manual name</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>NOT FOUND online and no name in your URL</t>
         </is>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Milwaukee Power Tool Handle Part - 14-34-0003</t>
+          <t>Milwaukee Housing Assembly - 14-34-0003</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3279,32 +3279,32 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="A99" t="inlineStr">
         <is>
           <t>/products/blomberg-model-7169581600</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>Blomberg</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Blomberg Washer - 7169581600</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Blomberg Front Load Washer - 7169581600</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
         <is>
           <t>Model number - whole appliance, REVIEW</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>SERP (ebay parts listing references it as a washer model)</t>
         </is>
@@ -4555,32 +4555,32 @@
       <c r="F143" s="3" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="A144" t="inlineStr">
         <is>
           <t>/products/midea-model-mdtf18whr</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Midea 18.1 Cu. Ft. Top Freezer Refrigerator White - MDTF18WHR</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Midea Vissani Top Freezer Refrigerator - MDTF18WHR</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
         <is>
           <t>Model number - whole appliance, REVIEW</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>SERP (energystar, as Vissani MDTF18WHR5)</t>
         </is>
@@ -5551,32 +5551,32 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+      <c r="A179" t="inlineStr">
         <is>
           <t>/products/whirlpool-model-caws923mq1</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C179" t="inlineStr">
         <is>
           <t>Whirlpool Top Load Washer - CAWS923MQ1</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
         <is>
           <t>Model number - whole appliance, REVIEW</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F179" t="inlineStr">
         <is>
           <t>SERP (parts retailers list it as a washer model)</t>
         </is>
@@ -5679,104 +5679,148 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="3" t="inlineStr">
+      <c r="A183" t="inlineStr">
         <is>
           <t>/products/samsung-dd82-01246a</t>
         </is>
       </c>
-      <c r="B183" s="3" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C183" s="3" t="inlineStr"/>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr"/>
-      <c r="F183" s="3" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Samsung Dishwasher Circulation and Drain Pump Motor Sump Assembly - DD82-01246A</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>partsdr, applianceparts4all, encompass, partselect, reliableparts, partadvantage, repairclinic, appliancepartspros</t>
+        </is>
+      </c>
     </row>
     <row r="184">
-      <c r="A184" s="3" t="inlineStr">
+      <c r="A184" t="inlineStr">
         <is>
           <t>/products/w11678109-whirlpool-microwave-door-assembly</t>
         </is>
       </c>
-      <c r="B184" s="3" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>W11678109</t>
         </is>
       </c>
-      <c r="C184" s="3" t="inlineStr"/>
-      <c r="D184" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E184" s="3" t="inlineStr"/>
-      <c r="F184" s="3" t="inlineStr"/>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Whirlpool Microwave Door Assembly - W11678109</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>ifixit, reliableparts, partadvantage, applianceparts4all, hnkparts, appliancepartspros, repairclinic</t>
+        </is>
+      </c>
     </row>
     <row r="185">
-      <c r="A185" s="3" t="inlineStr">
+      <c r="A185" t="inlineStr">
         <is>
           <t>/products/whirlpool-wp8212044</t>
         </is>
       </c>
-      <c r="B185" s="3" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C185" s="3" t="inlineStr"/>
-      <c r="D185" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E185" s="3" t="inlineStr"/>
-      <c r="F185" s="3" t="inlineStr"/>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Whirlpool KitchenAid Food Processor Work Bowl with Black Handle - WP8212044</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Sold for KitchenAid KFP740; same part as row 408</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>partsdr, searspartsdirect, encompass, ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="186">
-      <c r="A186" s="3" t="inlineStr">
+      <c r="A186" t="inlineStr">
         <is>
           <t>/products/whirlpool-wpw10339442</t>
         </is>
       </c>
-      <c r="B186" s="3" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C186" s="3" t="inlineStr"/>
-      <c r="D186" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E186" s="3" t="inlineStr"/>
-      <c r="F186" s="3" t="inlineStr"/>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Whirlpool Gas Range Surface Burner Control Knob Black - WPW10339442</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>partselect, searspartsdirect, partadvantage, ifixit, applianceparts4all, encompass, hnkparts, appliancepartspros</t>
+        </is>
+      </c>
     </row>
     <row r="187">
-      <c r="A187" s="3" t="inlineStr">
+      <c r="A187" t="inlineStr">
         <is>
           <t>/products/air-king-5s1107103</t>
         </is>
       </c>
-      <c r="B187" s="3" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="C187" s="3" t="inlineStr"/>
-      <c r="D187" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E187" s="3" t="inlineStr"/>
-      <c r="F187" s="3" t="inlineStr"/>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Air King Range Hood Motor Assembly - 5S1107103</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>encompass (airking.encompass.com)</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -5799,44 +5843,68 @@
       <c r="F188" s="3" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="3" t="inlineStr">
+      <c r="A189" t="inlineStr">
         <is>
           <t>/products/delonghi-model-ecam29043sb</t>
         </is>
       </c>
-      <c r="B189" s="3" t="inlineStr">
+      <c r="B189" t="inlineStr">
         <is>
           <t>Delonghi</t>
         </is>
       </c>
-      <c r="C189" s="3" t="inlineStr"/>
-      <c r="D189" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E189" s="3" t="inlineStr"/>
-      <c r="F189" s="3" t="inlineStr"/>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>De'Longhi Magnifica Evo Automatic Espresso Machine Silver - ECAM29043SB</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>SERP (chefsupplies, greentoe, ereplacementparts)</t>
+        </is>
+      </c>
     </row>
     <row r="190">
-      <c r="A190" s="3" t="inlineStr">
+      <c r="A190" t="inlineStr">
         <is>
           <t>/products/ge-wh12x10410</t>
         </is>
       </c>
-      <c r="B190" s="3" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C190" s="3" t="inlineStr"/>
-      <c r="D190" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E190" s="3" t="inlineStr"/>
-      <c r="F190" s="3" t="inlineStr"/>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>GE Washer Water Temperature ATC Sensor Probe - WH12X10410</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>partsdr, applianceparts4all, ifixit, appliancepartspros, searspartsdirect</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -5859,504 +5927,748 @@
       <c r="F191" s="3" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="3" t="inlineStr">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>/products/haier-model-hb3600vd1m22</t>
         </is>
       </c>
-      <c r="B192" s="3" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>Haier</t>
         </is>
       </c>
-      <c r="C192" s="3" t="inlineStr"/>
-      <c r="D192" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="inlineStr"/>
-      <c r="F192" s="3" t="inlineStr"/>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Haier Ducted Air Handler Indoor Unit - HB3600VD1M22</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance, REVIEW</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>SERP (repairclinic, walmart, appliancefactoryparts)</t>
+        </is>
+      </c>
     </row>
     <row r="193">
-      <c r="A193" s="3" t="inlineStr">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>/products/kenmore-daewoo-stmr183pe1w</t>
         </is>
       </c>
-      <c r="B193" s="3" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>Kenmore</t>
         </is>
       </c>
-      <c r="C193" s="3" t="inlineStr"/>
-      <c r="D193" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E193" s="3" t="inlineStr"/>
-      <c r="F193" s="3" t="inlineStr"/>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>Kenmore Seasons Top Mount Refrigerator White - STMR183PE1W</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance, REVIEW</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>SERP (hdsupply parts listings name it as Seasons refrigerator model)</t>
+        </is>
+      </c>
     </row>
     <row r="194">
-      <c r="A194" s="3" t="inlineStr">
+      <c r="A194" t="inlineStr">
         <is>
           <t>/products/lg-0czza20001n</t>
         </is>
       </c>
-      <c r="B194" s="3" t="inlineStr">
+      <c r="B194" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C194" s="3" t="inlineStr"/>
-      <c r="D194" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E194" s="3" t="inlineStr"/>
-      <c r="F194" s="3" t="inlineStr"/>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>LG Air Conditioner Fan Motor Dual Run Capacitor 6+50 MFD 270V - 0CZZA20001N</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>genuinereplacementparts, applianceparts4all, appliancepartspros, searspartsdirect, repairclinic</t>
+        </is>
+      </c>
     </row>
     <row r="195">
-      <c r="A195" s="3" t="inlineStr">
+      <c r="A195" t="inlineStr">
         <is>
           <t>/products/lg-aba77088205</t>
         </is>
       </c>
-      <c r="B195" s="3" t="inlineStr">
+      <c r="B195" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C195" s="3" t="inlineStr"/>
-      <c r="D195" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="inlineStr"/>
-      <c r="F195" s="3" t="inlineStr"/>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>LG TV Stand Bracket Assembly - ABA77088205</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>encompass, shopjimmy, reliableparts</t>
+        </is>
+      </c>
     </row>
     <row r="196">
-      <c r="A196" s="3" t="inlineStr">
+      <c r="A196" t="inlineStr">
         <is>
           <t>/products/lg-lf25z6211s</t>
         </is>
       </c>
-      <c r="B196" s="3" t="inlineStr">
+      <c r="B196" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C196" s="3" t="inlineStr"/>
-      <c r="D196" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E196" s="3" t="inlineStr"/>
-      <c r="F196" s="3" t="inlineStr"/>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>LG 25 Cu. Ft. Counter-Depth MAX French 3-Door Refrigerator - LF25Z6211S</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>SERP (lg.com spec sheet, rtings, townappliance)</t>
+        </is>
+      </c>
     </row>
     <row r="197">
-      <c r="A197" s="3" t="inlineStr">
+      <c r="A197" t="inlineStr">
         <is>
           <t>/products/lg-man63048901</t>
         </is>
       </c>
-      <c r="B197" s="3" t="inlineStr">
+      <c r="B197" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C197" s="3" t="inlineStr"/>
-      <c r="D197" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E197" s="3" t="inlineStr"/>
-      <c r="F197" s="3" t="inlineStr"/>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Door Bin Guard Assembly - MAN63048901</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>partadvantage, encompass, ereplacementparts, searspartsdirect</t>
+        </is>
+      </c>
     </row>
     <row r="198">
-      <c r="A198" s="3" t="inlineStr">
+      <c r="A198" t="inlineStr">
         <is>
           <t>/products/midea-19871100000002</t>
         </is>
       </c>
-      <c r="B198" s="3" t="inlineStr">
+      <c r="B198" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C198" s="3" t="inlineStr"/>
-      <c r="D198" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E198" s="3" t="inlineStr"/>
-      <c r="F198" s="3" t="inlineStr"/>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Midea Range Oven Door Assembly Stainless Steel - 19871100000002</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>encompass, partselect</t>
+        </is>
+      </c>
     </row>
     <row r="199">
-      <c r="A199" s="3" t="inlineStr">
+      <c r="A199" t="inlineStr">
         <is>
           <t>/products/panasonic-model-nnsc67ns</t>
         </is>
       </c>
-      <c r="B199" s="3" t="inlineStr">
+      <c r="B199" t="inlineStr">
         <is>
           <t>Panasonic</t>
         </is>
       </c>
-      <c r="C199" s="3" t="inlineStr"/>
-      <c r="D199" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E199" s="3" t="inlineStr"/>
-      <c r="F199" s="3" t="inlineStr"/>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Panasonic 1.3 Cu. Ft. 1200W Inverter Countertop Microwave Stainless Steel - NN-SC67NS</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>SERP (rtings, walmart)</t>
+        </is>
+      </c>
     </row>
     <row r="200">
-      <c r="A200" s="3" t="inlineStr">
+      <c r="A200" t="inlineStr">
         <is>
           <t>/products/panasonic-txp0184</t>
         </is>
       </c>
-      <c r="B200" s="3" t="inlineStr">
+      <c r="B200" t="inlineStr">
         <is>
           <t>Panasonic</t>
         </is>
       </c>
-      <c r="C200" s="3" t="inlineStr"/>
-      <c r="D200" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="inlineStr"/>
-      <c r="F200" s="3" t="inlineStr"/>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Panasonic Blu-ray Drive Unit - TXP0184</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>encompass, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="201">
-      <c r="A201" s="3" t="inlineStr">
+      <c r="A201" t="inlineStr">
         <is>
           <t>/products/samsung-bn59-01300h</t>
         </is>
       </c>
-      <c r="B201" s="3" t="inlineStr">
+      <c r="B201" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C201" s="3" t="inlineStr"/>
-      <c r="D201" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E201" s="3" t="inlineStr"/>
-      <c r="F201" s="3" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Samsung TV Smart Touch Remote Control - BN59-01300H</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>samsungparts, encompass, ifixit, shopjimmy</t>
+        </is>
+      </c>
     </row>
     <row r="202">
-      <c r="A202" s="3" t="inlineStr">
+      <c r="A202" t="inlineStr">
         <is>
           <t>/products/samsung-dc32-00007a</t>
         </is>
       </c>
-      <c r="B202" s="3" t="inlineStr">
+      <c r="B202" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C202" s="3" t="inlineStr"/>
-      <c r="D202" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E202" s="3" t="inlineStr"/>
-      <c r="F202" s="3" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Samsung Dryer Thermistor Temperature Sensor - DC32-00007A</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>appliancepartspros, partsdr, searspartsdirect, encompass, partadvantage, hnkparts, partselect</t>
+        </is>
+      </c>
     </row>
     <row r="203">
-      <c r="A203" s="3" t="inlineStr">
+      <c r="A203" t="inlineStr">
         <is>
           <t>/products/samsung-nf54m5151arash</t>
         </is>
       </c>
-      <c r="B203" s="3" t="inlineStr">
+      <c r="B203" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C203" s="3" t="inlineStr"/>
-      <c r="D203" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E203" s="3" t="inlineStr"/>
-      <c r="F203" s="3" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Samsung Refrigerator R600A Compressor - NF54M5151ARASH</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>samsungparts, hnkparts, shopjimmy, hdsupply</t>
+        </is>
+      </c>
     </row>
     <row r="204">
-      <c r="A204" s="3" t="inlineStr">
+      <c r="A204" t="inlineStr">
         <is>
           <t>/products/samsung-rf31cg7400sraa</t>
         </is>
       </c>
-      <c r="B204" s="3" t="inlineStr">
+      <c r="B204" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C204" s="3" t="inlineStr"/>
-      <c r="D204" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E204" s="3" t="inlineStr"/>
-      <c r="F204" s="3" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Samsung 30 Cu. Ft. Mega Capacity 4-Door French Door Refrigerator Stainless Steel - RF31CG7400SRAA</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>SERP (samsung.com, thebrick, energystar)</t>
+        </is>
+      </c>
     </row>
     <row r="205">
-      <c r="A205" s="3" t="inlineStr">
+      <c r="A205" t="inlineStr">
         <is>
           <t>/products/sharp-model-smd2489es</t>
         </is>
       </c>
-      <c r="B205" s="3" t="inlineStr">
+      <c r="B205" t="inlineStr">
         <is>
           <t>Sharp</t>
         </is>
       </c>
-      <c r="C205" s="3" t="inlineStr"/>
-      <c r="D205" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="inlineStr"/>
-      <c r="F205" s="3" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Sharp 24" 1.2 Cu. Ft. Smart Microwave Drawer Stainless Steel - SMD2489ES</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>SERP (ajmadison, pcrichard, townappliance)</t>
+        </is>
+      </c>
     </row>
     <row r="206">
-      <c r="A206" s="3" t="inlineStr">
+      <c r="A206" t="inlineStr">
         <is>
           <t>/products/sony-1-013-691-24</t>
         </is>
       </c>
-      <c r="B206" s="3" t="inlineStr">
+      <c r="B206" t="inlineStr">
         <is>
           <t>Sony</t>
         </is>
       </c>
-      <c r="C206" s="3" t="inlineStr"/>
-      <c r="D206" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E206" s="3" t="inlineStr"/>
-      <c r="F206" s="3" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Sony TV Remote Control RMF-TX800U - 1-013-691-24</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>encompass, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="207">
-      <c r="A207" s="3" t="inlineStr">
+      <c r="A207" t="inlineStr">
         <is>
           <t>/products/sony-model-kdl55nx720</t>
         </is>
       </c>
-      <c r="B207" s="3" t="inlineStr">
+      <c r="B207" t="inlineStr">
         <is>
           <t>Sony</t>
         </is>
       </c>
-      <c r="C207" s="3" t="inlineStr"/>
-      <c r="D207" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="inlineStr"/>
-      <c r="F207" s="3" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Sony Bravia 55" Full HD 3D LED TV - KDL-55NX720</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>SERP (digitaltrends, lcd-compare)</t>
+        </is>
+      </c>
     </row>
     <row r="208">
-      <c r="A208" s="3" t="inlineStr">
+      <c r="A208" t="inlineStr">
         <is>
           <t>/products/whirlpool-w10665724</t>
         </is>
       </c>
-      <c r="B208" s="3" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C208" s="3" t="inlineStr"/>
-      <c r="D208" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="inlineStr"/>
-      <c r="F208" s="3" t="inlineStr"/>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Whirlpool Cooktop Black Glass Main Top - W10665724</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>repairclinic, partselect, reliableparts, partsdr</t>
+        </is>
+      </c>
     </row>
     <row r="209">
-      <c r="A209" s="3" t="inlineStr">
+      <c r="A209" t="inlineStr">
         <is>
           <t>/products/whirlpool-w11102314</t>
         </is>
       </c>
-      <c r="B209" s="3" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C209" s="3" t="inlineStr"/>
-      <c r="D209" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E209" s="3" t="inlineStr"/>
-      <c r="F209" s="3" t="inlineStr"/>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Whirlpool Washer Glass Lid - W11102314</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>hnkparts, partsdr, searspartsdirect, appliancepartspros, ifixit, partselect, repairclinic</t>
+        </is>
+      </c>
     </row>
     <row r="210">
-      <c r="A210" s="3" t="inlineStr">
+      <c r="A210" t="inlineStr">
         <is>
           <t>/products/whirlpool-w11707255</t>
         </is>
       </c>
-      <c r="B210" s="3" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C210" s="3" t="inlineStr"/>
-      <c r="D210" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E210" s="3" t="inlineStr"/>
-      <c r="F210" s="3" t="inlineStr"/>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Whirlpool Range Oven Halogen Light Assembly - W11707255</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>partsdr, reliableparts, ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="211">
-      <c r="A211" s="3" t="inlineStr">
+      <c r="A211" t="inlineStr">
         <is>
           <t>/products/whirlpool-wp8578869</t>
         </is>
       </c>
-      <c r="B211" s="3" t="inlineStr">
+      <c r="B211" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C211" s="3" t="inlineStr"/>
-      <c r="D211" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E211" s="3" t="inlineStr"/>
-      <c r="F211" s="3" t="inlineStr"/>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Whirlpool Washer Timer - WP8578869</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>applianceparts4all, searspartsdirect, partsdr, encompass</t>
+        </is>
+      </c>
     </row>
     <row r="212">
-      <c r="A212" s="3" t="inlineStr">
+      <c r="A212" t="inlineStr">
         <is>
           <t>/products/whirlpool-wpw10448874</t>
         </is>
       </c>
-      <c r="B212" s="3" t="inlineStr">
+      <c r="B212" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C212" s="3" t="inlineStr"/>
-      <c r="D212" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E212" s="3" t="inlineStr"/>
-      <c r="F212" s="3" t="inlineStr"/>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Whirlpool Refrigerator Compressor Start Relay with Overload - WPW10448874</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>ifixit, hnkparts, partsdr, partselect, applianceparts4all, searspartsdirect, appliancepartspros</t>
+        </is>
+      </c>
     </row>
     <row r="213">
-      <c r="A213" s="3" t="inlineStr">
+      <c r="A213" t="inlineStr">
         <is>
           <t>/products/whirlpool-wpw10605427</t>
         </is>
       </c>
-      <c r="B213" s="3" t="inlineStr">
+      <c r="B213" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C213" s="3" t="inlineStr"/>
-      <c r="D213" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E213" s="3" t="inlineStr"/>
-      <c r="F213" s="3" t="inlineStr"/>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Whirlpool Front Load Washer Drain Pump - WPW10605427</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>partsdr, appliancepartspros, applianceparts4all, searspartsdirect, ifixit, encompass, hnkparts</t>
+        </is>
+      </c>
     </row>
     <row r="214">
-      <c r="A214" s="3" t="inlineStr">
+      <c r="A214" t="inlineStr">
         <is>
           <t>/products/29103009-char-broil-grill-cooking-grate</t>
         </is>
       </c>
-      <c r="B214" s="3" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>29103009</t>
         </is>
       </c>
-      <c r="C214" s="3" t="inlineStr"/>
-      <c r="D214" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E214" s="3" t="inlineStr"/>
-      <c r="F214" s="3" t="inlineStr"/>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Char-Broil Gas Grill Cooking Grate - 29103009</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Brand column was part number</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>searspartsdirect, appliancefactoryparts</t>
+        </is>
+      </c>
     </row>
     <row r="215">
-      <c r="A215" s="3" t="inlineStr">
+      <c r="A215" t="inlineStr">
         <is>
           <t>/products/bertazzoni-model-mast365inmxe</t>
         </is>
       </c>
-      <c r="B215" s="3" t="inlineStr">
+      <c r="B215" t="inlineStr">
         <is>
           <t>Bertazzoni</t>
         </is>
       </c>
-      <c r="C215" s="3" t="inlineStr"/>
-      <c r="D215" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E215" s="3" t="inlineStr"/>
-      <c r="F215" s="3" t="inlineStr"/>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Bertazzoni Master Series 36" Induction Range Stainless Steel - MAST365INMXE</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>SERP (ajmadison, designerappliances, plessers)</t>
+        </is>
+      </c>
     </row>
     <row r="216">
-      <c r="A216" s="3" t="inlineStr">
+      <c r="A216" t="inlineStr">
         <is>
           <t>/products/bertazzoni-z300066</t>
         </is>
       </c>
-      <c r="B216" s="3" t="inlineStr">
+      <c r="B216" t="inlineStr">
         <is>
           <t>Bertazzoni</t>
         </is>
       </c>
-      <c r="C216" s="3" t="inlineStr"/>
-      <c r="D216" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E216" s="3" t="inlineStr"/>
-      <c r="F216" s="3" t="inlineStr"/>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Bertazzoni Refrigerator Vertical Beam Assembly - Z300066</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>encompass, hnkparts, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
@@ -6379,164 +6691,240 @@
       <c r="F217" s="3" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="3" t="inlineStr">
+      <c r="A218" t="inlineStr">
         <is>
           <t>/products/ge-wb16x29082</t>
         </is>
       </c>
-      <c r="B218" s="3" t="inlineStr">
+      <c r="B218" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C218" s="3" t="inlineStr"/>
-      <c r="D218" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E218" s="3" t="inlineStr"/>
-      <c r="F218" s="3" t="inlineStr"/>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>GE Gas Cooktop Tri-Ring Surface Burner Assembly - WB16X29082</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>searspartsdirect, repairclinic, genuinereplacementparts, reliableparts, partsdr, partselect, hnkparts, appliancepartspros, ifixit</t>
+        </is>
+      </c>
     </row>
     <row r="219">
-      <c r="A219" s="3" t="inlineStr">
+      <c r="A219" t="inlineStr">
         <is>
           <t>/products/ge-wb18x25574</t>
         </is>
       </c>
-      <c r="B219" s="3" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C219" s="3" t="inlineStr"/>
-      <c r="D219" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E219" s="3" t="inlineStr"/>
-      <c r="F219" s="3" t="inlineStr"/>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>GE Gas Cooktop Switch Harness - WB18X25574</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>encompass, partsdr, ereplacementparts, reliableparts</t>
+        </is>
+      </c>
     </row>
     <row r="220">
-      <c r="A220" s="3" t="inlineStr">
+      <c r="A220" t="inlineStr">
         <is>
           <t>/products/samsung-dd82-01385a</t>
         </is>
       </c>
-      <c r="B220" s="3" t="inlineStr">
+      <c r="B220" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C220" s="3" t="inlineStr"/>
-      <c r="D220" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E220" s="3" t="inlineStr"/>
-      <c r="F220" s="3" t="inlineStr"/>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Samsung Dishwasher Middle Basket Rack Assembly - DD82-01385A</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>searspartsdirect, partsdr, ifixit, repairclinic, appliancepartspros, partselect, encompass</t>
+        </is>
+      </c>
     </row>
     <row r="221">
-      <c r="A221" s="3" t="inlineStr">
+      <c r="A221" t="inlineStr">
         <is>
           <t>/products/samsung-dd97-00185a</t>
         </is>
       </c>
-      <c r="B221" s="3" t="inlineStr">
+      <c r="B221" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C221" s="3" t="inlineStr"/>
-      <c r="D221" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E221" s="3" t="inlineStr"/>
-      <c r="F221" s="3" t="inlineStr"/>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Samsung Dishwasher Lower Basket Assembly - DD97-00185A</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>partsdr</t>
+        </is>
+      </c>
     </row>
     <row r="222">
-      <c r="A222" s="3" t="inlineStr">
+      <c r="A222" t="inlineStr">
         <is>
           <t>/products/samsung-de81-09306a</t>
         </is>
       </c>
-      <c r="B222" s="3" t="inlineStr">
+      <c r="B222" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C222" s="3" t="inlineStr"/>
-      <c r="D222" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E222" s="3" t="inlineStr"/>
-      <c r="F222" s="3" t="inlineStr"/>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Samsung Dacor Range Hood Switch Harness - DE81-09306A</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Discontinued part; fits Dacor ERV range hoods</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>reliableparts, encompass, ereplacementparts, appliancepartspros, partselect</t>
+        </is>
+      </c>
     </row>
     <row r="223">
-      <c r="A223" s="3" t="inlineStr">
+      <c r="A223" s="2" t="inlineStr">
         <is>
           <t>/products/smeg-693410927-coffee-machine-permanent-filter-assembly</t>
         </is>
       </c>
-      <c r="B223" s="3" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
         <is>
           <t>Smeg</t>
         </is>
       </c>
-      <c r="C223" s="3" t="inlineStr"/>
-      <c r="D223" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E223" s="3" t="inlineStr"/>
-      <c r="F223" s="3" t="inlineStr"/>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>Smeg Coffee Machine Permanent Filter Assembly - 693410927</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>NOT FOUND online - name taken from your URL</t>
+        </is>
+      </c>
     </row>
     <row r="224">
-      <c r="A224" s="3" t="inlineStr">
+      <c r="A224" t="inlineStr">
         <is>
           <t>/products/whirlpool-326791-range-lower-bake-element</t>
         </is>
       </c>
-      <c r="B224" s="3" t="inlineStr">
+      <c r="B224" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C224" s="3" t="inlineStr"/>
-      <c r="D224" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E224" s="3" t="inlineStr"/>
-      <c r="F224" s="3" t="inlineStr"/>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Whirlpool Range Oven Bake Element 2100W 240V - 326791</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>partsdr, appliancepartspros, hnkparts, genuinereplacementparts, partselect</t>
+        </is>
+      </c>
     </row>
     <row r="225">
-      <c r="A225" s="3" t="inlineStr">
+      <c r="A225" t="inlineStr">
         <is>
           <t>/products/whirlpool-w11752350-microwave-stainless-steel-control-panel</t>
         </is>
       </c>
-      <c r="B225" s="3" t="inlineStr">
+      <c r="B225" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C225" s="3" t="inlineStr"/>
-      <c r="D225" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E225" s="3" t="inlineStr"/>
-      <c r="F225" s="3" t="inlineStr"/>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Whirlpool Microwave Stainless Steel Control Panel Assembly - W11752350</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>ereplacementparts, partsdr</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
@@ -6559,64 +6947,96 @@
       <c r="F226" s="3" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="3" t="inlineStr">
+      <c r="A227" t="inlineStr">
         <is>
           <t>/products/avanti-e20f03-022300</t>
         </is>
       </c>
-      <c r="B227" s="3" t="inlineStr">
+      <c r="B227" t="inlineStr">
         <is>
           <t>Avanti</t>
         </is>
       </c>
-      <c r="C227" s="3" t="inlineStr"/>
-      <c r="D227" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E227" s="3" t="inlineStr"/>
-      <c r="F227" s="3" t="inlineStr"/>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Avanti Range 6-Inch Coil Heater Element 240V 1250W - Z-E20F03-022300</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Competitors list part number as Z-E20F03-022300</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>genuinereplacementparts, encompass</t>
+        </is>
+      </c>
     </row>
     <row r="228">
-      <c r="A228" s="3" t="inlineStr">
+      <c r="A228" t="inlineStr">
         <is>
           <t>/products/blomberg-2805310600</t>
         </is>
       </c>
-      <c r="B228" s="3" t="inlineStr">
+      <c r="B228" t="inlineStr">
         <is>
           <t>Blomberg</t>
         </is>
       </c>
-      <c r="C228" s="3" t="inlineStr"/>
-      <c r="D228" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E228" s="3" t="inlineStr"/>
-      <c r="F228" s="3" t="inlineStr"/>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Blomberg Washer Door Lock - 2805310600</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>encompass, partselect, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="229">
-      <c r="A229" s="3" t="inlineStr">
+      <c r="A229" s="2" t="inlineStr">
         <is>
           <t>/products/blomberg-model-7169581500</t>
         </is>
       </c>
-      <c r="B229" s="3" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
         <is>
           <t>Blomberg</t>
         </is>
       </c>
-      <c r="C229" s="3" t="inlineStr"/>
-      <c r="D229" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E229" s="3" t="inlineStr"/>
-      <c r="F229" s="3" t="inlineStr"/>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>Blomberg Front Load Washer - 7169581500</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance, REVIEW</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>NOT FOUND online - inferred from sibling model 7169581600 (your row 99)</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
@@ -6659,164 +7079,240 @@
       <c r="F231" s="3" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="3" t="inlineStr">
+      <c r="A232" t="inlineStr">
         <is>
           <t>/products/bosch-12008380</t>
         </is>
       </c>
-      <c r="B232" s="3" t="inlineStr">
+      <c r="B232" t="inlineStr">
         <is>
           <t>Bosch</t>
         </is>
       </c>
-      <c r="C232" s="3" t="inlineStr"/>
-      <c r="D232" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E232" s="3" t="inlineStr"/>
-      <c r="F232" s="3" t="inlineStr"/>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Bosch Dishwasher Detergent Dispenser Assembly - 12008380</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>appliancepartspros, partsdr, ifixit, applianceparts4all, partselect, reliableparts, encompass, shopjimmy</t>
+        </is>
+      </c>
     </row>
     <row r="233">
-      <c r="A233" s="3" t="inlineStr">
+      <c r="A233" t="inlineStr">
         <is>
           <t>/products/braun-80765382</t>
         </is>
       </c>
-      <c r="B233" s="3" t="inlineStr">
+      <c r="B233" t="inlineStr">
         <is>
           <t>Braun</t>
         </is>
       </c>
-      <c r="C233" s="3" t="inlineStr"/>
-      <c r="D233" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E233" s="3" t="inlineStr"/>
-      <c r="F233" s="3" t="inlineStr"/>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Braun Series 9 Pro 6-in-1 SmartCare Center - 80765382</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>encompass</t>
+        </is>
+      </c>
     </row>
     <row r="234">
-      <c r="A234" s="3" t="inlineStr">
+      <c r="A234" t="inlineStr">
         <is>
           <t>/products/braun-81719650</t>
         </is>
       </c>
-      <c r="B234" s="3" t="inlineStr">
+      <c r="B234" t="inlineStr">
         <is>
           <t>Braun</t>
         </is>
       </c>
-      <c r="C234" s="3" t="inlineStr"/>
-      <c r="D234" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E234" s="3" t="inlineStr"/>
-      <c r="F234" s="3" t="inlineStr"/>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Braun Silk-Epil 9 Flex Epilator Massage Cap - 81719650</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>encompass (braun.encompass.com)</t>
+        </is>
+      </c>
     </row>
     <row r="235">
-      <c r="A235" s="3" t="inlineStr">
+      <c r="A235" t="inlineStr">
         <is>
           <t>/products/danby-12020600a00061</t>
         </is>
       </c>
-      <c r="B235" s="3" t="inlineStr">
+      <c r="B235" t="inlineStr">
         <is>
           <t>Danby</t>
         </is>
       </c>
-      <c r="C235" s="3" t="inlineStr"/>
-      <c r="D235" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E235" s="3" t="inlineStr"/>
-      <c r="F235" s="3" t="inlineStr"/>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Danby Portable Air Conditioner Window Sealing Board Assembly - 12020600A00061</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>genuinereplacementparts, hnkparts, encompass</t>
+        </is>
+      </c>
     </row>
     <row r="236">
-      <c r="A236" s="3" t="inlineStr">
+      <c r="A236" t="inlineStr">
         <is>
           <t>/products/electrolux-297099255</t>
         </is>
       </c>
-      <c r="B236" s="3" t="inlineStr">
+      <c r="B236" t="inlineStr">
         <is>
           <t>Electrolux</t>
         </is>
       </c>
-      <c r="C236" s="3" t="inlineStr"/>
-      <c r="D236" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E236" s="3" t="inlineStr"/>
-      <c r="F236" s="3" t="inlineStr"/>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Electrolux Refrigerator Freezer Evaporator Cover - 297099255</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>genuinereplacementparts, appliancepartspros, searspartsdirect (competitors brand it Frigidaire)</t>
+        </is>
+      </c>
     </row>
     <row r="237">
-      <c r="A237" s="3" t="inlineStr">
+      <c r="A237" t="inlineStr">
         <is>
           <t>/products/ge-gcst10a1w2ss</t>
         </is>
       </c>
-      <c r="B237" s="3" t="inlineStr">
+      <c r="B237" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C237" s="3" t="inlineStr"/>
-      <c r="D237" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E237" s="3" t="inlineStr"/>
-      <c r="F237" s="3" t="inlineStr"/>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>GE 1.0 Cu. Ft. Countertop Convection Microwave with Air Fry Stainless Steel - GCST10A1W2SS</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>SERP (ajmadison, abt - as GCST10A1WSS)</t>
+        </is>
+      </c>
     </row>
     <row r="238">
-      <c r="A238" s="3" t="inlineStr">
+      <c r="A238" t="inlineStr">
         <is>
           <t>/products/ge-wh11x34742</t>
         </is>
       </c>
-      <c r="B238" s="3" t="inlineStr">
+      <c r="B238" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C238" s="3" t="inlineStr"/>
-      <c r="D238" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E238" s="3" t="inlineStr"/>
-      <c r="F238" s="3" t="inlineStr"/>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>GE Washer Drain Pump - WH11X34742</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>partsdr, reliableparts, genuinereplacementparts, applianceparts4all, repairclinic, encompass, hnkparts, ifixit</t>
+        </is>
+      </c>
     </row>
     <row r="239">
-      <c r="A239" s="3" t="inlineStr">
+      <c r="A239" t="inlineStr">
         <is>
           <t>/products/homelite-679987007</t>
         </is>
       </c>
-      <c r="B239" s="3" t="inlineStr">
+      <c r="B239" t="inlineStr">
         <is>
           <t>Homelite</t>
         </is>
       </c>
-      <c r="C239" s="3" t="inlineStr"/>
-      <c r="D239" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="inlineStr"/>
-      <c r="F239" s="3" t="inlineStr"/>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Homelite Lawn Mower Lower Handle - 679987007</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>partselect, ereplacementparts, partswarehouse (all list it as Ryobi)</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -6839,144 +7335,208 @@
       <c r="F240" s="3" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="3" t="inlineStr">
+      <c r="A241" t="inlineStr">
         <is>
           <t>/products/kenmore-model-11025132411</t>
         </is>
       </c>
-      <c r="B241" s="3" t="inlineStr">
+      <c r="B241" t="inlineStr">
         <is>
           <t>Kenmore</t>
         </is>
       </c>
-      <c r="C241" s="3" t="inlineStr"/>
-      <c r="D241" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E241" s="3" t="inlineStr"/>
-      <c r="F241" s="3" t="inlineStr"/>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Kenmore Top Load Washer - 11025132411</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>SERP (fix.com, partselect.ca, filtersfast)</t>
+        </is>
+      </c>
     </row>
     <row r="242">
-      <c r="A242" s="3" t="inlineStr">
+      <c r="A242" t="inlineStr">
         <is>
           <t>/products/lg-aba30066502</t>
         </is>
       </c>
-      <c r="B242" s="3" t="inlineStr">
+      <c r="B242" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C242" s="3" t="inlineStr"/>
-      <c r="D242" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E242" s="3" t="inlineStr"/>
-      <c r="F242" s="3" t="inlineStr"/>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>LG OLED TV Stand Bracket Assembly - ABA30066502</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>shopjimmy, encompass, reliableparts, partadvantage</t>
+        </is>
+      </c>
     </row>
     <row r="243">
-      <c r="A243" s="3" t="inlineStr">
+      <c r="A243" t="inlineStr">
         <is>
           <t>/products/magic-chef-model-hmdr450se</t>
         </is>
       </c>
-      <c r="B243" s="3" t="inlineStr">
+      <c r="B243" t="inlineStr">
         <is>
           <t>Magic</t>
         </is>
       </c>
-      <c r="C243" s="3" t="inlineStr"/>
-      <c r="D243" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E243" s="3" t="inlineStr"/>
-      <c r="F243" s="3" t="inlineStr"/>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Magic Chef 4.5 Cu. Ft. 2-Door Compact Refrigerator Stainless - HMDR450SE</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>SERP (appliancefactoryparts)</t>
+        </is>
+      </c>
     </row>
     <row r="244">
-      <c r="A244" s="3" t="inlineStr">
+      <c r="A244" t="inlineStr">
         <is>
           <t>/products/midea-11001011000307</t>
         </is>
       </c>
-      <c r="B244" s="3" t="inlineStr">
+      <c r="B244" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C244" s="3" t="inlineStr"/>
-      <c r="D244" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E244" s="3" t="inlineStr"/>
-      <c r="F244" s="3" t="inlineStr"/>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Midea Washer Permanent Magnet Synchronous Drain Pump - 11001011000307</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>encompass, reliableparts</t>
+        </is>
+      </c>
     </row>
     <row r="245">
-      <c r="A245" s="3" t="inlineStr">
+      <c r="A245" t="inlineStr">
         <is>
           <t>/products/midea-12100508a00009</t>
         </is>
       </c>
-      <c r="B245" s="3" t="inlineStr">
+      <c r="B245" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C245" s="3" t="inlineStr"/>
-      <c r="D245" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E245" s="3" t="inlineStr"/>
-      <c r="F245" s="3" t="inlineStr"/>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Midea Portable Air Conditioner Exhaust Hose 4.5 ft x 6" - 12100508A00009</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>hnkparts, encompass, searspartsdirect, ifixit, partadvantage, partselect</t>
+        </is>
+      </c>
     </row>
     <row r="246">
-      <c r="A246" s="3" t="inlineStr">
+      <c r="A246" t="inlineStr">
         <is>
           <t>/products/milwaukee-49-08-5270</t>
         </is>
       </c>
-      <c r="B246" s="3" t="inlineStr">
+      <c r="B246" t="inlineStr">
         <is>
           <t>Milwaukee</t>
         </is>
       </c>
-      <c r="C246" s="3" t="inlineStr"/>
-      <c r="D246" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E246" s="3" t="inlineStr"/>
-      <c r="F246" s="3" t="inlineStr"/>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Milwaukee Power Tool Type Y Grease 6 oz Tube - 49-08-5270</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>SERP (ebay)</t>
+        </is>
+      </c>
     </row>
     <row r="247">
-      <c r="A247" s="3" t="inlineStr">
+      <c r="A247" t="inlineStr">
         <is>
           <t>/products/norelco-422203625801</t>
         </is>
       </c>
-      <c r="B247" s="3" t="inlineStr">
+      <c r="B247" t="inlineStr">
         <is>
           <t>Norelco</t>
         </is>
       </c>
-      <c r="C247" s="3" t="inlineStr"/>
-      <c r="D247" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E247" s="3" t="inlineStr"/>
-      <c r="F247" s="3" t="inlineStr"/>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Philips Norelco Shaver Precision Black Trimmer - 422203625801</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>encompass (philips.encompass.com), ereplacementparts, partselect</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
@@ -6999,144 +7559,212 @@
       <c r="F248" s="3" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="3" t="inlineStr">
+      <c r="A249" t="inlineStr">
         <is>
           <t>/products/oral-b-81621559</t>
         </is>
       </c>
-      <c r="B249" s="3" t="inlineStr">
+      <c r="B249" t="inlineStr">
         <is>
           <t>Oral</t>
         </is>
       </c>
-      <c r="C249" s="3" t="inlineStr"/>
-      <c r="D249" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E249" s="3" t="inlineStr"/>
-      <c r="F249" s="3" t="inlineStr"/>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Oral-B Electric Toothbrush Genius X D701 Rose Gold 6-Mode Handle - 81621559</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>encompass (braun.encompass.com)</t>
+        </is>
+      </c>
     </row>
     <row r="250">
-      <c r="A250" s="3" t="inlineStr">
+      <c r="A250" t="inlineStr">
         <is>
           <t>/products/oral-b-81739996</t>
         </is>
       </c>
-      <c r="B250" s="3" t="inlineStr">
+      <c r="B250" t="inlineStr">
         <is>
           <t>Oral</t>
         </is>
       </c>
-      <c r="C250" s="3" t="inlineStr"/>
-      <c r="D250" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E250" s="3" t="inlineStr"/>
-      <c r="F250" s="3" t="inlineStr"/>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Oral-B Electric Toothbrush Refill Holder White - 81739996</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>encompass (braun.encompass.com, partstore)</t>
+        </is>
+      </c>
     </row>
     <row r="251">
-      <c r="A251" s="3" t="inlineStr">
+      <c r="A251" t="inlineStr">
         <is>
           <t>/products/panasonic-model-nnsn966s</t>
         </is>
       </c>
-      <c r="B251" s="3" t="inlineStr">
+      <c r="B251" t="inlineStr">
         <is>
           <t>Panasonic</t>
         </is>
       </c>
-      <c r="C251" s="3" t="inlineStr"/>
-      <c r="D251" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E251" s="3" t="inlineStr"/>
-      <c r="F251" s="3" t="inlineStr"/>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Panasonic 2.2 Cu. Ft. 1250W Inverter Countertop Microwave Stainless Steel - NN-SN966S</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>SERP (panasonic.com, shopsavvy)</t>
+        </is>
+      </c>
     </row>
     <row r="252">
-      <c r="A252" s="3" t="inlineStr">
+      <c r="A252" t="inlineStr">
         <is>
           <t>/products/saeco-421941305001</t>
         </is>
       </c>
-      <c r="B252" s="3" t="inlineStr">
+      <c r="B252" t="inlineStr">
         <is>
           <t>Saeco</t>
         </is>
       </c>
-      <c r="C252" s="3" t="inlineStr"/>
-      <c r="D252" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E252" s="3" t="inlineStr"/>
-      <c r="F252" s="3" t="inlineStr"/>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Saeco Espresso Machine Grinder Motor - 421941305001</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>SERP (anthonysespresso, partstown)</t>
+        </is>
+      </c>
     </row>
     <row r="253">
-      <c r="A253" s="3" t="inlineStr">
+      <c r="A253" t="inlineStr">
         <is>
           <t>/products/saeco-996530015809</t>
         </is>
       </c>
-      <c r="B253" s="3" t="inlineStr">
+      <c r="B253" t="inlineStr">
         <is>
           <t>Saeco</t>
         </is>
       </c>
-      <c r="C253" s="3" t="inlineStr"/>
-      <c r="D253" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E253" s="3" t="inlineStr"/>
-      <c r="F253" s="3" t="inlineStr"/>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Saeco Gaggia Espresso Machine Brew Group Gasket 66x36x16mm - 996530015809</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Only one source</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>SERP (ebay)</t>
+        </is>
+      </c>
     </row>
     <row r="254">
-      <c r="A254" s="3" t="inlineStr">
+      <c r="A254" t="inlineStr">
         <is>
           <t>/products/samsung-bn39-01154p</t>
         </is>
       </c>
-      <c r="B254" s="3" t="inlineStr">
+      <c r="B254" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C254" s="3" t="inlineStr"/>
-      <c r="D254" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E254" s="3" t="inlineStr"/>
-      <c r="F254" s="3" t="inlineStr"/>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Samsung TV RF Antenna Gender Cable Adapter - BN39-01154P</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>samsungparts, encompass, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="255">
-      <c r="A255" s="3" t="inlineStr">
+      <c r="A255" s="2" t="inlineStr">
         <is>
           <t>/products/samsung-gh82-31769a-tablet-lcd-with-frame</t>
         </is>
       </c>
-      <c r="B255" s="3" t="inlineStr">
+      <c r="B255" s="2" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C255" s="3" t="inlineStr"/>
-      <c r="D255" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E255" s="3" t="inlineStr"/>
-      <c r="F255" s="3" t="inlineStr"/>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Tablet LCD Display with Frame - GH82-31769A</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>NOT FOUND online - name taken from your URL</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
@@ -7159,24 +7787,36 @@
       <c r="F256" s="3" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="3" t="inlineStr">
+      <c r="A257" s="2" t="inlineStr">
         <is>
           <t>/products/sharp-model-cv2p10sc</t>
         </is>
       </c>
-      <c r="B257" s="3" t="inlineStr">
+      <c r="B257" s="2" t="inlineStr">
         <is>
           <t>Sharp</t>
         </is>
       </c>
-      <c r="C257" s="3" t="inlineStr"/>
-      <c r="D257" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E257" s="3" t="inlineStr"/>
-      <c r="F257" s="3" t="inlineStr"/>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>Sharp 10,000 BTU Portable Air Conditioner - CV2P10SC</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance, REVIEW</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>SERP (appliancefactoryparts, manualslib; sibling CV2P10SX is 10,500 BTU)</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
@@ -7219,24 +7859,32 @@
       <c r="F259" s="3" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="3" t="inlineStr">
+      <c r="A260" t="inlineStr">
         <is>
           <t>/products/sonicare-300004787491</t>
         </is>
       </c>
-      <c r="B260" s="3" t="inlineStr">
+      <c r="B260" t="inlineStr">
         <is>
           <t>Sonicare</t>
         </is>
       </c>
-      <c r="C260" s="3" t="inlineStr"/>
-      <c r="D260" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E260" s="3" t="inlineStr"/>
-      <c r="F260" s="3" t="inlineStr"/>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Sonicare DiamondClean Toothbrush Charging Base - 300004787491</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>encompass (philips.encompass.com)</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
@@ -7259,24 +7907,36 @@
       <c r="F261" s="3" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="3" t="inlineStr">
+      <c r="A262" t="inlineStr">
         <is>
           <t>/products/tcl-08-l171w44-pw210aa</t>
         </is>
       </c>
-      <c r="B262" s="3" t="inlineStr">
+      <c r="B262" t="inlineStr">
         <is>
           <t>Tcl</t>
         </is>
       </c>
-      <c r="C262" s="3" t="inlineStr"/>
-      <c r="D262" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E262" s="3" t="inlineStr"/>
-      <c r="F262" s="3" t="inlineStr"/>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>TCL TV Power Supply LED Driver Board - 08-L171W44-PW210AA</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Only one source</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>shopjimmy</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
@@ -7299,184 +7959,272 @@
       <c r="F263" s="3" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="3" t="inlineStr">
+      <c r="A264" t="inlineStr">
         <is>
           <t>/products/tradepro-tp-cap-45-5-440r</t>
         </is>
       </c>
-      <c r="B264" s="3" t="inlineStr">
+      <c r="B264" t="inlineStr">
         <is>
           <t>Tradepro</t>
         </is>
       </c>
-      <c r="C264" s="3" t="inlineStr"/>
-      <c r="D264" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E264" s="3" t="inlineStr"/>
-      <c r="F264" s="3" t="inlineStr"/>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>TradePro HVAC 45/5 MFD 440V Round Dual Run Capacitor - TP-CAP-45/5/440R</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>SERP (atomicfilters, allfilters, walkairdirect)</t>
+        </is>
+      </c>
     </row>
     <row r="265">
-      <c r="A265" s="3" t="inlineStr">
+      <c r="A265" t="inlineStr">
         <is>
           <t>/products/whirlpool-w11236887</t>
         </is>
       </c>
-      <c r="B265" s="3" t="inlineStr">
+      <c r="B265" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C265" s="3" t="inlineStr"/>
-      <c r="D265" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E265" s="3" t="inlineStr"/>
-      <c r="F265" s="3" t="inlineStr"/>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Whirlpool Wall Oven Touchpad Control Panel Assembly Stainless - W11236887</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>partsdr, searspartsdirect, applianceparts4all, partadvantage, reliableparts, genuinereplacementparts, ifixit, partselect, appliancepartspros</t>
+        </is>
+      </c>
     </row>
     <row r="266">
-      <c r="A266" s="3" t="inlineStr">
+      <c r="A266" t="inlineStr">
         <is>
           <t>/products/whirlpool-w11418231</t>
         </is>
       </c>
-      <c r="B266" s="3" t="inlineStr">
+      <c r="B266" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C266" s="3" t="inlineStr"/>
-      <c r="D266" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E266" s="3" t="inlineStr"/>
-      <c r="F266" s="3" t="inlineStr"/>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Whirlpool Washer Agitator Assembly - W11418231</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>partsdr, searspartsdirect, appliancepartspros, reliableparts, ereplacementparts, hnkparts</t>
+        </is>
+      </c>
     </row>
     <row r="267">
-      <c r="A267" s="3" t="inlineStr">
+      <c r="A267" t="inlineStr">
         <is>
           <t>/products/whirlpool-wpw10217922</t>
         </is>
       </c>
-      <c r="B267" s="3" t="inlineStr">
+      <c r="B267" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C267" s="3" t="inlineStr"/>
-      <c r="D267" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E267" s="3" t="inlineStr"/>
-      <c r="F267" s="3" t="inlineStr"/>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Whirlpool Refrigerator Ice Maker Water Inlet Tube - WPW10217922</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>searspartsdirect, appliancepartspros, hnkparts, encompass, partsdr</t>
+        </is>
+      </c>
     </row>
     <row r="268">
-      <c r="A268" s="3" t="inlineStr">
+      <c r="A268" t="inlineStr">
         <is>
           <t>/products/137107500-electrolux-washer-door-hinge</t>
         </is>
       </c>
-      <c r="B268" s="3" t="inlineStr">
+      <c r="B268" t="inlineStr">
         <is>
           <t>137107500</t>
         </is>
       </c>
-      <c r="C268" s="3" t="inlineStr"/>
-      <c r="D268" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E268" s="3" t="inlineStr"/>
-      <c r="F268" s="3" t="inlineStr"/>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Electrolux Washer Door Hinge - 137107500</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Brand column was part number</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>repairclinic, ifixit, encompass, genuinereplacementparts, applianceparts4all, hnkparts, partsdr (competitors brand it Frigidaire)</t>
+        </is>
+      </c>
     </row>
     <row r="269">
-      <c r="A269" s="3" t="inlineStr">
+      <c r="A269" t="inlineStr">
         <is>
           <t>/products/air-king-5s2239008</t>
         </is>
       </c>
-      <c r="B269" s="3" t="inlineStr">
+      <c r="B269" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="C269" s="3" t="inlineStr"/>
-      <c r="D269" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E269" s="3" t="inlineStr"/>
-      <c r="F269" s="3" t="inlineStr"/>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Air King Exhaust Fan Blower Assembly - 5S2239008</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>encompass, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="270">
-      <c r="A270" s="3" t="inlineStr">
+      <c r="A270" s="2" t="inlineStr">
         <is>
           <t>/products/avanti-model-eru240p1b</t>
         </is>
       </c>
-      <c r="B270" s="3" t="inlineStr">
+      <c r="B270" s="2" t="inlineStr">
         <is>
           <t>Avanti</t>
         </is>
       </c>
-      <c r="C270" s="3" t="inlineStr"/>
-      <c r="D270" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E270" s="3" t="inlineStr"/>
-      <c r="F270" s="3" t="inlineStr"/>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>Avanti 24" Electric Range Black - ERU240P1B</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance, REVIEW</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>NOT FOUND online - inferred from Avanti ERU240 range family (encompass)</t>
+        </is>
+      </c>
     </row>
     <row r="271">
-      <c r="A271" s="3" t="inlineStr">
+      <c r="A271" t="inlineStr">
         <is>
           <t>/products/bosch-11040372</t>
         </is>
       </c>
-      <c r="B271" s="3" t="inlineStr">
+      <c r="B271" t="inlineStr">
         <is>
           <t>Bosch</t>
         </is>
       </c>
-      <c r="C271" s="3" t="inlineStr"/>
-      <c r="D271" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E271" s="3" t="inlineStr"/>
-      <c r="F271" s="3" t="inlineStr"/>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Bosch Oven Smooth Grill Plate - 11040372</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Only one source</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>reliableparts</t>
+        </is>
+      </c>
     </row>
     <row r="272">
-      <c r="A272" s="3" t="inlineStr">
+      <c r="A272" t="inlineStr">
         <is>
           <t>/products/bosch-678777</t>
         </is>
       </c>
-      <c r="B272" s="3" t="inlineStr">
+      <c r="B272" t="inlineStr">
         <is>
           <t>Bosch</t>
         </is>
       </c>
-      <c r="C272" s="3" t="inlineStr"/>
-      <c r="D272" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E272" s="3" t="inlineStr"/>
-      <c r="F272" s="3" t="inlineStr"/>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Bosch Refrigerator Evaporator Multiduct Cover Assembly - 00678777</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Competitors list part number as 00678777</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>applianceparts4all, encompass, searspartsdirect, appliancepartspros</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
@@ -7499,84 +8247,120 @@
       <c r="F273" s="3" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="3" t="inlineStr">
+      <c r="A274" t="inlineStr">
         <is>
           <t>/products/braun-81686528</t>
         </is>
       </c>
-      <c r="B274" s="3" t="inlineStr">
+      <c r="B274" t="inlineStr">
         <is>
           <t>Braun</t>
         </is>
       </c>
-      <c r="C274" s="3" t="inlineStr"/>
-      <c r="D274" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E274" s="3" t="inlineStr"/>
-      <c r="F274" s="3" t="inlineStr"/>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Braun Shaver Series 8/9 PCB Assembly - 81686528</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>encompass (braun.encompass.com), ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="275">
-      <c r="A275" s="3" t="inlineStr">
+      <c r="A275" s="2" t="inlineStr">
         <is>
           <t>/products/criterion-cuf14c1w</t>
         </is>
       </c>
-      <c r="B275" s="3" t="inlineStr">
+      <c r="B275" s="2" t="inlineStr">
         <is>
           <t>Criterion</t>
         </is>
       </c>
-      <c r="C275" s="3" t="inlineStr"/>
-      <c r="D275" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E275" s="3" t="inlineStr"/>
-      <c r="F275" s="3" t="inlineStr"/>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>Criterion 14 Cu. Ft. Upright Freezer White - CUF14C1W</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance, REVIEW</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>NOT FOUND online - inferred from Criterion CUF14 upright freezer family (energystar)</t>
+        </is>
+      </c>
     </row>
     <row r="276">
-      <c r="A276" s="3" t="inlineStr">
+      <c r="A276" t="inlineStr">
         <is>
           <t>/products/danby-8120120025a</t>
         </is>
       </c>
-      <c r="B276" s="3" t="inlineStr">
+      <c r="B276" t="inlineStr">
         <is>
           <t>Danby</t>
         </is>
       </c>
-      <c r="C276" s="3" t="inlineStr"/>
-      <c r="D276" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E276" s="3" t="inlineStr"/>
-      <c r="F276" s="3" t="inlineStr"/>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Danby Portable Air Conditioner Hose Pipe - 8120120025A</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>encompass (partstore), genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="277">
-      <c r="A277" s="3" t="inlineStr">
+      <c r="A277" t="inlineStr">
         <is>
           <t>/products/elica-gn01wb</t>
         </is>
       </c>
-      <c r="B277" s="3" t="inlineStr">
+      <c r="B277" t="inlineStr">
         <is>
           <t>Elica</t>
         </is>
       </c>
-      <c r="C277" s="3" t="inlineStr"/>
-      <c r="D277" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E277" s="3" t="inlineStr"/>
-      <c r="F277" s="3" t="inlineStr"/>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Elica Range Hood Fan Wheel Counterclockwise - GN01WB</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>SERP (partstown), genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
@@ -7619,24 +8403,32 @@
       <c r="F279" s="3" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="3" t="inlineStr">
+      <c r="A280" t="inlineStr">
         <is>
           <t>/products/ge-ws30x10015</t>
         </is>
       </c>
-      <c r="B280" s="3" t="inlineStr">
+      <c r="B280" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C280" s="3" t="inlineStr"/>
-      <c r="D280" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E280" s="3" t="inlineStr"/>
-      <c r="F280" s="3" t="inlineStr"/>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>GE Whole Home Water Filtration System Filter Housing - WS30X10015</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>repairclinic, partsdr, reliableparts</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
@@ -7659,24 +8451,36 @@
       <c r="F281" s="3" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="3" t="inlineStr">
+      <c r="A282" t="inlineStr">
         <is>
           <t>/products/goodman-model-gsx140301</t>
         </is>
       </c>
-      <c r="B282" s="3" t="inlineStr">
+      <c r="B282" t="inlineStr">
         <is>
           <t>Goodman</t>
         </is>
       </c>
-      <c r="C282" s="3" t="inlineStr"/>
-      <c r="D282" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E282" s="3" t="inlineStr"/>
-      <c r="F282" s="3" t="inlineStr"/>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Goodman 2.5 Ton 14 SEER R410A Air Conditioner Condenser - GSX140301</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>SERP (hvacdirect, unicosystem, partstown)</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
@@ -7719,164 +8523,236 @@
       <c r="F284" s="3" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="3" t="inlineStr">
+      <c r="A285" t="inlineStr">
         <is>
           <t>/products/kenmore-30105-0049400</t>
         </is>
       </c>
-      <c r="B285" s="3" t="inlineStr">
+      <c r="B285" t="inlineStr">
         <is>
           <t>Kenmore</t>
         </is>
       </c>
-      <c r="C285" s="3" t="inlineStr"/>
-      <c r="D285" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E285" s="3" t="inlineStr"/>
-      <c r="F285" s="3" t="inlineStr"/>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Kenmore Refrigerator Inverter Box Assembly - 30105-0049400</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>encompass, searspartsdirect</t>
+        </is>
+      </c>
     </row>
     <row r="286">
-      <c r="A286" s="3" t="inlineStr">
+      <c r="A286" t="inlineStr">
         <is>
           <t>/products/lokring-appliance-a20110013b</t>
         </is>
       </c>
-      <c r="B286" s="3" t="inlineStr">
+      <c r="B286" t="inlineStr">
         <is>
           <t>Lokring</t>
         </is>
       </c>
-      <c r="C286" s="3" t="inlineStr"/>
-      <c r="D286" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E286" s="3" t="inlineStr"/>
-      <c r="F286" s="3" t="inlineStr"/>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Lokring Appliance Refrigerator Sealed System R600A Master Repair Kit - A20110013B</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>reliableparts, partadvantage, ifixit, encompass, applianceparts4all</t>
+        </is>
+      </c>
     </row>
     <row r="287">
-      <c r="A287" s="3" t="inlineStr">
+      <c r="A287" t="inlineStr">
         <is>
           <t>/products/lokring-appliance-l13006027a</t>
         </is>
       </c>
-      <c r="B287" s="3" t="inlineStr">
+      <c r="B287" t="inlineStr">
         <is>
           <t>Lokring</t>
         </is>
       </c>
-      <c r="C287" s="3" t="inlineStr"/>
-      <c r="D287" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E287" s="3" t="inlineStr"/>
-      <c r="F287" s="3" t="inlineStr"/>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Lokring Appliance R600a Refrigerant Charging Kit - L13006027A</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>ifixit, applianceparts4all, encompass</t>
+        </is>
+      </c>
     </row>
     <row r="288">
-      <c r="A288" s="3" t="inlineStr">
+      <c r="A288" t="inlineStr">
         <is>
           <t>/products/midea-12031000001063</t>
         </is>
       </c>
-      <c r="B288" s="3" t="inlineStr">
+      <c r="B288" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C288" s="3" t="inlineStr"/>
-      <c r="D288" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E288" s="3" t="inlineStr"/>
-      <c r="F288" s="3" t="inlineStr"/>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Midea Refrigerator Compressor PTC Starter - 12031000001063</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>encompass, hnkparts, shopjimmy, partselect</t>
+        </is>
+      </c>
     </row>
     <row r="289">
-      <c r="A289" s="3" t="inlineStr">
+      <c r="A289" t="inlineStr">
         <is>
           <t>/products/midea-17123000a01738</t>
         </is>
       </c>
-      <c r="B289" s="3" t="inlineStr">
+      <c r="B289" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C289" s="3" t="inlineStr"/>
-      <c r="D289" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E289" s="3" t="inlineStr"/>
-      <c r="F289" s="3" t="inlineStr"/>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Midea Ductless Air Handler Main Control Board - 17123000A01738</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>encompass, ifixit, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="290">
-      <c r="A290" s="3" t="inlineStr">
+      <c r="A290" t="inlineStr">
         <is>
           <t>/products/norelco-300005092241</t>
         </is>
       </c>
-      <c r="B290" s="3" t="inlineStr">
+      <c r="B290" t="inlineStr">
         <is>
           <t>Norelco</t>
         </is>
       </c>
-      <c r="C290" s="3" t="inlineStr"/>
-      <c r="D290" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E290" s="3" t="inlineStr"/>
-      <c r="F290" s="3" t="inlineStr"/>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Philips Norelco Shaver Series 3000 Charging Stand - 300005092241</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr"/>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>encompass (philips.encompass.com)</t>
+        </is>
+      </c>
     </row>
     <row r="291">
-      <c r="A291" s="3" t="inlineStr">
+      <c r="A291" t="inlineStr">
         <is>
           <t>/products/panasonic-wergc20x7919-electric-shaver-oil</t>
         </is>
       </c>
-      <c r="B291" s="3" t="inlineStr">
+      <c r="B291" t="inlineStr">
         <is>
           <t>Panasonic</t>
         </is>
       </c>
-      <c r="C291" s="3" t="inlineStr"/>
-      <c r="D291" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E291" s="3" t="inlineStr"/>
-      <c r="F291" s="3" t="inlineStr"/>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Panasonic Electric Shaver Blade Oil 15 ml - WERGC20X7919</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>SERP (kaufland, ebay)</t>
+        </is>
+      </c>
     </row>
     <row r="292">
-      <c r="A292" s="3" t="inlineStr">
+      <c r="A292" s="2" t="inlineStr">
         <is>
           <t>/products/panasonic-wes2207w7658</t>
         </is>
       </c>
-      <c r="B292" s="3" t="inlineStr">
+      <c r="B292" s="2" t="inlineStr">
         <is>
           <t>Panasonic</t>
         </is>
       </c>
-      <c r="C292" s="3" t="inlineStr"/>
-      <c r="D292" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E292" s="3" t="inlineStr"/>
-      <c r="F292" s="3" t="inlineStr"/>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>Panasonic Ladies Shaver ES2207 Charging Adapter - WES2207W7658</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>NOT FOUND online - inferred from Panasonic W7658 adapter part suffix + your URL</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
@@ -7899,64 +8775,100 @@
       <c r="F293" s="3" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" s="3" t="inlineStr">
+      <c r="A294" t="inlineStr">
         <is>
           <t>/products/samsung-rf32cg5400sraa</t>
         </is>
       </c>
-      <c r="B294" s="3" t="inlineStr">
+      <c r="B294" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C294" s="3" t="inlineStr"/>
-      <c r="D294" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E294" s="3" t="inlineStr"/>
-      <c r="F294" s="3" t="inlineStr"/>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Samsung 31 Cu. Ft. Mega Capacity 3-Door French Door Refrigerator Stainless Steel - RF32CG5400SRAA</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>SERP (samsung.com, thebrick, coastappliances)</t>
+        </is>
+      </c>
     </row>
     <row r="295">
-      <c r="A295" s="3" t="inlineStr">
+      <c r="A295" t="inlineStr">
         <is>
           <t>/products/samsung-wf53bb8900adus</t>
         </is>
       </c>
-      <c r="B295" s="3" t="inlineStr">
+      <c r="B295" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C295" s="3" t="inlineStr"/>
-      <c r="D295" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E295" s="3" t="inlineStr"/>
-      <c r="F295" s="3" t="inlineStr"/>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Samsung Bespoke 5.3 Cu. Ft. Front Load Washer with AI OptiWash Brushed Navy - WF53BB8900ADUS</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>SERP (samsung.com, ajmadison, townappliance)</t>
+        </is>
+      </c>
     </row>
     <row r="296">
-      <c r="A296" s="3" t="inlineStr">
+      <c r="A296" t="inlineStr">
         <is>
           <t>/products/snapper-770199</t>
         </is>
       </c>
-      <c r="B296" s="3" t="inlineStr">
+      <c r="B296" t="inlineStr">
         <is>
           <t>Snapper</t>
         </is>
       </c>
-      <c r="C296" s="3" t="inlineStr"/>
-      <c r="D296" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E296" s="3" t="inlineStr"/>
-      <c r="F296" s="3" t="inlineStr"/>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Snapper 82V Battery Lawn Mower Fan Motor Kit - 770199</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
@@ -7979,564 +8891,832 @@
       <c r="F297" s="3" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="3" t="inlineStr">
+      <c r="A298" t="inlineStr">
         <is>
           <t>/products/sony-model-sve14135cxw</t>
         </is>
       </c>
-      <c r="B298" s="3" t="inlineStr">
+      <c r="B298" t="inlineStr">
         <is>
           <t>Sony</t>
         </is>
       </c>
-      <c r="C298" s="3" t="inlineStr"/>
-      <c r="D298" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E298" s="3" t="inlineStr"/>
-      <c r="F298" s="3" t="inlineStr"/>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Sony VAIO E Series 14" Laptop White - SVE14135CXW</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Model number - whole product</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>SERP (laptopscreen, softpedia, bhphotovideo for sibling CXB)</t>
+        </is>
+      </c>
     </row>
     <row r="299">
-      <c r="A299" s="3" t="inlineStr">
+      <c r="A299" t="inlineStr">
         <is>
           <t>/products/speed-queen-61927</t>
         </is>
       </c>
-      <c r="B299" s="3" t="inlineStr">
+      <c r="B299" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="C299" s="3" t="inlineStr"/>
-      <c r="D299" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E299" s="3" t="inlineStr"/>
-      <c r="F299" s="3" t="inlineStr"/>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Speed Queen Dryer Heating Element Kit 240V 5.0KW - 61927</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>ifixit, partsdr, reliableparts, appliancepartspros, partadvantage, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="300">
-      <c r="A300" s="3" t="inlineStr">
+      <c r="A300" s="2" t="inlineStr">
         <is>
           <t>/products/tcl-s8-50p10nn-bs1</t>
         </is>
       </c>
-      <c r="B300" s="3" t="inlineStr">
+      <c r="B300" s="2" t="inlineStr">
         <is>
           <t>Tcl</t>
         </is>
       </c>
-      <c r="C300" s="3" t="inlineStr"/>
-      <c r="D300" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E300" s="3" t="inlineStr"/>
-      <c r="F300" s="3" t="inlineStr"/>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>TCL TV Stand Base Kit - S8-50P10NN-BS1</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>NOT FOUND online - inferred from TCL S8-50 base kit numbering</t>
+        </is>
+      </c>
     </row>
     <row r="301">
-      <c r="A301" s="3" t="inlineStr">
+      <c r="A301" t="inlineStr">
         <is>
           <t>/products/trane-tcont302as42da</t>
         </is>
       </c>
-      <c r="B301" s="3" t="inlineStr">
+      <c r="B301" t="inlineStr">
         <is>
           <t>Trane</t>
         </is>
       </c>
-      <c r="C301" s="3" t="inlineStr"/>
-      <c r="D301" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E301" s="3" t="inlineStr"/>
-      <c r="F301" s="3" t="inlineStr"/>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Trane 7-Day Programmable Thermostat 4H/2C - TCONT302AS42DA</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>SERP (industrialstores, superarbor, walmart)</t>
+        </is>
+      </c>
     </row>
     <row r="302">
-      <c r="A302" s="3" t="inlineStr">
+      <c r="A302" t="inlineStr">
         <is>
           <t>/products/w11042467-whirlpool-affresh-stainless-steel-cleaning-spray</t>
         </is>
       </c>
-      <c r="B302" s="3" t="inlineStr">
+      <c r="B302" t="inlineStr">
         <is>
           <t>W11042467</t>
         </is>
       </c>
-      <c r="C302" s="3" t="inlineStr"/>
-      <c r="D302" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E302" s="3" t="inlineStr"/>
-      <c r="F302" s="3" t="inlineStr"/>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Whirlpool Affresh Stainless Steel Cleaning Spray 12 oz - W11042467</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Discontinued part; brand column was part number</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>searspartsdirect, encompass, partsdr</t>
+        </is>
+      </c>
     </row>
     <row r="303">
-      <c r="A303" s="3" t="inlineStr">
+      <c r="A303" t="inlineStr">
         <is>
           <t>/products/whirlpool-285565-washer-agitator</t>
         </is>
       </c>
-      <c r="B303" s="3" t="inlineStr">
+      <c r="B303" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C303" s="3" t="inlineStr"/>
-      <c r="D303" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E303" s="3" t="inlineStr"/>
-      <c r="F303" s="3" t="inlineStr"/>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Whirlpool Top Load Washer Agitator Kit - 285565</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>partselect, reliableparts, searspartsdirect, partsdr, ifixit, encompass, ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="304">
-      <c r="A304" s="3" t="inlineStr">
+      <c r="A304" t="inlineStr">
         <is>
           <t>/products/whirlpool-w10731887</t>
         </is>
       </c>
-      <c r="B304" s="3" t="inlineStr">
+      <c r="B304" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C304" s="3" t="inlineStr"/>
-      <c r="D304" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E304" s="3" t="inlineStr"/>
-      <c r="F304" s="3" t="inlineStr"/>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Whirlpool Slide-In Range Stainless Steel Trim Kit - W10731887</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr"/>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>partsdr, encompass, searspartsdirect, genuinereplacementparts, repairclinic</t>
+        </is>
+      </c>
     </row>
     <row r="305">
-      <c r="A305" s="3" t="inlineStr">
+      <c r="A305" t="inlineStr">
         <is>
           <t>/products/whirlpool-w10740624</t>
         </is>
       </c>
-      <c r="B305" s="3" t="inlineStr">
+      <c r="B305" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C305" s="3" t="inlineStr"/>
-      <c r="D305" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E305" s="3" t="inlineStr"/>
-      <c r="F305" s="3" t="inlineStr"/>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Whirlpool Washer Technical Service Sheet - W10740624</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr"/>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>encompass, ifixit</t>
+        </is>
+      </c>
     </row>
     <row r="306">
-      <c r="A306" s="3" t="inlineStr">
+      <c r="A306" t="inlineStr">
         <is>
           <t>/products/whirlpool-w10756513</t>
         </is>
       </c>
-      <c r="B306" s="3" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C306" s="3" t="inlineStr"/>
-      <c r="D306" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E306" s="3" t="inlineStr"/>
-      <c r="F306" s="3" t="inlineStr"/>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Whirlpool Wall Oven Control Panel Assembly - W10756513</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Only one source</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>searspartsdirect</t>
+        </is>
+      </c>
     </row>
     <row r="307">
-      <c r="A307" s="3" t="inlineStr">
+      <c r="A307" t="inlineStr">
         <is>
           <t>/products/whirlpool-w11250167</t>
         </is>
       </c>
-      <c r="B307" s="3" t="inlineStr">
+      <c r="B307" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C307" s="3" t="inlineStr"/>
-      <c r="D307" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E307" s="3" t="inlineStr"/>
-      <c r="F307" s="3" t="inlineStr"/>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Whirlpool Range Oven Outer Door Glass Stainless - W11250167</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr"/>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>partsdr, repairclinic, reliableparts, ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="308">
-      <c r="A308" s="3" t="inlineStr">
+      <c r="A308" t="inlineStr">
         <is>
           <t>/products/whirlpool-w11524105</t>
         </is>
       </c>
-      <c r="B308" s="3" t="inlineStr">
+      <c r="B308" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C308" s="3" t="inlineStr"/>
-      <c r="D308" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E308" s="3" t="inlineStr"/>
-      <c r="F308" s="3" t="inlineStr"/>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Whirlpool Front Load Washer Detergent Dispenser Drawer - W11524105</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>partsdr, searspartsdirect, hnkparts, appliancepartspros, genuinereplacementparts, partselect, encompass, repairclinic</t>
+        </is>
+      </c>
     </row>
     <row r="309">
-      <c r="A309" s="3" t="inlineStr">
+      <c r="A309" t="inlineStr">
         <is>
           <t>/products/whirlpool-w11539855</t>
         </is>
       </c>
-      <c r="B309" s="3" t="inlineStr">
+      <c r="B309" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C309" s="3" t="inlineStr"/>
-      <c r="D309" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E309" s="3" t="inlineStr"/>
-      <c r="F309" s="3" t="inlineStr"/>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Whirlpool Ice Maker Drain Pump Assembly - W11539855</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr"/>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>partsdr, partselect, searspartsdirect, appliancepartspros, partadvantage, applianceparts4all, hnkparts, repairclinic, encompass, ifixit</t>
+        </is>
+      </c>
     </row>
     <row r="310">
-      <c r="A310" s="3" t="inlineStr">
+      <c r="A310" t="inlineStr">
         <is>
           <t>/products/whirlpool-w11552018</t>
         </is>
       </c>
-      <c r="B310" s="3" t="inlineStr">
+      <c r="B310" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C310" s="3" t="inlineStr"/>
-      <c r="D310" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E310" s="3" t="inlineStr"/>
-      <c r="F310" s="3" t="inlineStr"/>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Whirlpool Microwave Electronic Control Board - W11552018</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr"/>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>appliancepartspros, applianceparts4all, hnkparts, encompass, partselect, partsdr</t>
+        </is>
+      </c>
     </row>
     <row r="311">
-      <c r="A311" s="3" t="inlineStr">
+      <c r="A311" t="inlineStr">
         <is>
           <t>/products/whirlpool-w11612326</t>
         </is>
       </c>
-      <c r="B311" s="3" t="inlineStr">
+      <c r="B311" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C311" s="3" t="inlineStr"/>
-      <c r="D311" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E311" s="3" t="inlineStr"/>
-      <c r="F311" s="3" t="inlineStr"/>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Whirlpool Dishwasher Circulation Pump and Motor - W11612326</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr"/>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>partsdr, hnkparts, searspartsdirect, applianceparts4all, appliancepartspros, ifixit (partadvantage: Drain Pump)</t>
+        </is>
+      </c>
     </row>
     <row r="312">
-      <c r="A312" s="3" t="inlineStr">
+      <c r="A312" t="inlineStr">
         <is>
           <t>/products/whirlpool-wp8212014</t>
         </is>
       </c>
-      <c r="B312" s="3" t="inlineStr">
+      <c r="B312" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C312" s="3" t="inlineStr"/>
-      <c r="D312" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E312" s="3" t="inlineStr"/>
-      <c r="F312" s="3" t="inlineStr"/>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Whirlpool KitchenAid Food Processor Multipurpose Blade - WP8212014</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>encompass, appliancefactoryparts, appliancepartspros, partselect, repairclinic, ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="313">
-      <c r="A313" s="3" t="inlineStr">
+      <c r="A313" t="inlineStr">
         <is>
           <t>/products/12016780-bosch-dishwasher-silverware-basket-insert</t>
         </is>
       </c>
-      <c r="B313" s="3" t="inlineStr">
+      <c r="B313" t="inlineStr">
         <is>
           <t>12016780</t>
         </is>
       </c>
-      <c r="C313" s="3" t="inlineStr"/>
-      <c r="D313" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E313" s="3" t="inlineStr"/>
-      <c r="F313" s="3" t="inlineStr"/>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Bosch Dishwasher Silverware Basket Dishrack Insert - 12016780</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Brand column was part number</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>SERP (parts retailer lists it as Dishrack Insert) + your URL</t>
+        </is>
+      </c>
     </row>
     <row r="314">
-      <c r="A314" s="3" t="inlineStr">
+      <c r="A314" t="inlineStr">
         <is>
           <t>/products/char-broil-g619-0052-w1</t>
         </is>
       </c>
-      <c r="B314" s="3" t="inlineStr">
+      <c r="B314" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
-      <c r="C314" s="3" t="inlineStr"/>
-      <c r="D314" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E314" s="3" t="inlineStr"/>
-      <c r="F314" s="3" t="inlineStr"/>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Char-Broil Gas Grill Ignition Transformer - G619-0052-W1</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Only one source</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>SERP (newegg)</t>
+        </is>
+      </c>
     </row>
     <row r="315">
-      <c r="A315" s="3" t="inlineStr">
+      <c r="A315" t="inlineStr">
         <is>
           <t>/products/ge-model-gdf535psr0ss</t>
         </is>
       </c>
-      <c r="B315" s="3" t="inlineStr">
+      <c r="B315" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C315" s="3" t="inlineStr"/>
-      <c r="D315" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E315" s="3" t="inlineStr"/>
-      <c r="F315" s="3" t="inlineStr"/>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>GE 24" Front Control Dishwasher with Hard Food Disposer Stainless Steel - GDF535PSR0SS</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>SERP (ajmadison, appliancefactoryparts, filtersfast)</t>
+        </is>
+      </c>
     </row>
     <row r="316">
-      <c r="A316" s="3" t="inlineStr">
+      <c r="A316" t="inlineStr">
         <is>
           <t>/products/ge-model-peb7227an3dd</t>
         </is>
       </c>
-      <c r="B316" s="3" t="inlineStr">
+      <c r="B316" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C316" s="3" t="inlineStr"/>
-      <c r="D316" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E316" s="3" t="inlineStr"/>
-      <c r="F316" s="3" t="inlineStr"/>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>GE Profile 2.2 Cu. Ft. Built-In Sensor Microwave Oven - PEB7227AN3DD</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>SERP (repairclinic, partswarehouse, townappliance)</t>
+        </is>
+      </c>
     </row>
     <row r="317">
-      <c r="A317" s="3" t="inlineStr">
+      <c r="A317" t="inlineStr">
         <is>
           <t>/products/ge-wb10x29566</t>
         </is>
       </c>
-      <c r="B317" s="3" t="inlineStr">
+      <c r="B317" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C317" s="3" t="inlineStr"/>
-      <c r="D317" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E317" s="3" t="inlineStr"/>
-      <c r="F317" s="3" t="inlineStr"/>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>GE Electric Range Oven Door Hinge Receiver - WB10X29566</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>encompass, searspartsdirect, ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="318">
-      <c r="A318" s="3" t="inlineStr">
+      <c r="A318" t="inlineStr">
         <is>
           <t>/products/ge-wd12x10061</t>
         </is>
       </c>
-      <c r="B318" s="3" t="inlineStr">
+      <c r="B318" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C318" s="3" t="inlineStr"/>
-      <c r="D318" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E318" s="3" t="inlineStr"/>
-      <c r="F318" s="3" t="inlineStr"/>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>GE Dishwasher Wash Arm Fine Filter Hub Nut - WD12X10061</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr"/>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>applianceparts4all, partsdr, repairclinic, appliancepartspros, genuinereplacementparts, partselect</t>
+        </is>
+      </c>
     </row>
     <row r="319">
-      <c r="A319" s="3" t="inlineStr">
+      <c r="A319" t="inlineStr">
         <is>
           <t>/products/ge-we13x29725</t>
         </is>
       </c>
-      <c r="B319" s="3" t="inlineStr">
+      <c r="B319" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C319" s="3" t="inlineStr"/>
-      <c r="D319" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E319" s="3" t="inlineStr"/>
-      <c r="F319" s="3" t="inlineStr"/>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>GE Dryer Drum Baffle - WE13X29725</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr"/>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>partsdr, appliancepartspros, partselect, ifixit, encompass, hnkparts</t>
+        </is>
+      </c>
     </row>
     <row r="320">
-      <c r="A320" s="3" t="inlineStr">
+      <c r="A320" t="inlineStr">
         <is>
           <t>/products/samsung-dg94-02141c</t>
         </is>
       </c>
-      <c r="B320" s="3" t="inlineStr">
+      <c r="B320" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C320" s="3" t="inlineStr"/>
-      <c r="D320" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E320" s="3" t="inlineStr"/>
-      <c r="F320" s="3" t="inlineStr"/>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Samsung Range Surface Burner Knob Assembly - DG94-02141C</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr"/>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>searspartsdirect, partadvantage, hnkparts, genuinereplacementparts, partsdr, reliableparts, ereplacementparts, encompass, ifixit, partselect</t>
+        </is>
+      </c>
     </row>
     <row r="321">
-      <c r="A321" s="3" t="inlineStr">
+      <c r="A321" t="inlineStr">
         <is>
           <t>/products/samsung-dg94-03730d</t>
         </is>
       </c>
-      <c r="B321" s="3" t="inlineStr">
+      <c r="B321" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C321" s="3" t="inlineStr"/>
-      <c r="D321" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E321" s="3" t="inlineStr"/>
-      <c r="F321" s="3" t="inlineStr"/>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Samsung Range Glass Cooktop Frame Module Assembly - DG94-03730D</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr"/>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>hnkparts, genuinereplacementparts, ifixit, partadvantage, partsdr, encompass, searspartsdirect</t>
+        </is>
+      </c>
     </row>
     <row r="322">
-      <c r="A322" s="3" t="inlineStr">
+      <c r="A322" t="inlineStr">
         <is>
           <t>/products/wb27t11249-ge-oven-main-control-board</t>
         </is>
       </c>
-      <c r="B322" s="3" t="inlineStr">
+      <c r="B322" t="inlineStr">
         <is>
           <t>Wb27T11249</t>
         </is>
       </c>
-      <c r="C322" s="3" t="inlineStr"/>
-      <c r="D322" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E322" s="3" t="inlineStr"/>
-      <c r="F322" s="3" t="inlineStr"/>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>GE Wall Oven Microwave Combo Main Control Board - WB27T11249</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Discontinued part; brand column was part number</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>shopjimmy, applianceparts4all, hnkparts, ifixit, encompass, searspartsdirect, partsdr</t>
+        </is>
+      </c>
     </row>
     <row r="323">
-      <c r="A323" s="3" t="inlineStr">
+      <c r="A323" t="inlineStr">
         <is>
           <t>/products/whirlpool-w11051487-cooktop-main-top</t>
         </is>
       </c>
-      <c r="B323" s="3" t="inlineStr">
+      <c r="B323" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C323" s="3" t="inlineStr"/>
-      <c r="D323" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E323" s="3" t="inlineStr"/>
-      <c r="F323" s="3" t="inlineStr"/>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Whirlpool Cooktop Stainless Steel Main Glass Top - W11051487</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr"/>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>appliancepartspros, reliableparts, ifixit, partadvantage, partselect, searspartsdirect, partsdr</t>
+        </is>
+      </c>
     </row>
     <row r="324">
-      <c r="A324" s="3" t="inlineStr">
+      <c r="A324" t="inlineStr">
         <is>
           <t>/products/whirlpool-w11449263-range-hood-handle-assembly-handle-vent</t>
         </is>
       </c>
-      <c r="B324" s="3" t="inlineStr">
+      <c r="B324" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C324" s="3" t="inlineStr"/>
-      <c r="D324" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E324" s="3" t="inlineStr"/>
-      <c r="F324" s="3" t="inlineStr"/>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Whirlpool Range Oven Door Handle and Vent Assembly Stainless - W11449263</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr"/>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>partsdr, appliancepartspros, shopjimmy, hnkparts, partselect, encompass, searspartsdirect</t>
+        </is>
+      </c>
     </row>
     <row r="325">
-      <c r="A325" s="3" t="inlineStr">
+      <c r="A325" t="inlineStr">
         <is>
           <t>/products/91825gs-briggs-stratton-generator-brush-rectifier-holder-assembly</t>
         </is>
       </c>
-      <c r="B325" s="3" t="inlineStr">
+      <c r="B325" t="inlineStr">
         <is>
           <t>91825Gs</t>
         </is>
       </c>
-      <c r="C325" s="3" t="inlineStr"/>
-      <c r="D325" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E325" s="3" t="inlineStr"/>
-      <c r="F325" s="3" t="inlineStr"/>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Briggs &amp; Stratton Generator Brush Holder and Rectifier Assembly - 91825GS</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Discontinued part; brand column was part number</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>searspartsdirect, SERP (jackssmallengines)</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
@@ -8559,144 +9739,212 @@
       <c r="F326" s="3" t="inlineStr"/>
     </row>
     <row r="327">
-      <c r="A327" s="3" t="inlineStr">
+      <c r="A327" t="inlineStr">
         <is>
           <t>/products/bosch-11023246</t>
         </is>
       </c>
-      <c r="B327" s="3" t="inlineStr">
+      <c r="B327" t="inlineStr">
         <is>
           <t>Bosch</t>
         </is>
       </c>
-      <c r="C327" s="3" t="inlineStr"/>
-      <c r="D327" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E327" s="3" t="inlineStr"/>
-      <c r="F327" s="3" t="inlineStr"/>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Bosch Refrigerator Damper - 11023246</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr"/>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>partsdr, encompass (partstore)</t>
+        </is>
+      </c>
     </row>
     <row r="328">
-      <c r="A328" s="3" t="inlineStr">
+      <c r="A328" t="inlineStr">
         <is>
           <t>/products/bosch-12010030</t>
         </is>
       </c>
-      <c r="B328" s="3" t="inlineStr">
+      <c r="B328" t="inlineStr">
         <is>
           <t>Bosch</t>
         </is>
       </c>
-      <c r="C328" s="3" t="inlineStr"/>
-      <c r="D328" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E328" s="3" t="inlineStr"/>
-      <c r="F328" s="3" t="inlineStr"/>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Bosch Cooktop Glass Cleaner - 12010030</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr"/>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>hnkparts, genuinereplacementparts, reliableparts, partadvantage, encompass</t>
+        </is>
+      </c>
     </row>
     <row r="329">
-      <c r="A329" s="3" t="inlineStr">
+      <c r="A329" t="inlineStr">
         <is>
           <t>/products/bosch-675794</t>
         </is>
       </c>
-      <c r="B329" s="3" t="inlineStr">
+      <c r="B329" t="inlineStr">
         <is>
           <t>Bosch</t>
         </is>
       </c>
-      <c r="C329" s="3" t="inlineStr"/>
-      <c r="D329" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E329" s="3" t="inlineStr"/>
-      <c r="F329" s="3" t="inlineStr"/>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Bosch Dishwasher Cutlery Silverware Basket - 00675794</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Competitors list part number as 00675794</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>partselect, applianceparts4all, ereplacementparts, partsdr, encompass, searspartsdirect, appliancepartspros</t>
+        </is>
+      </c>
     </row>
     <row r="330">
-      <c r="A330" s="3" t="inlineStr">
+      <c r="A330" t="inlineStr">
         <is>
           <t>/products/bowers-wilkins-zz11770</t>
         </is>
       </c>
-      <c r="B330" s="3" t="inlineStr">
+      <c r="B330" t="inlineStr">
         <is>
           <t>Bowers</t>
         </is>
       </c>
-      <c r="C330" s="3" t="inlineStr"/>
-      <c r="D330" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E330" s="3" t="inlineStr"/>
-      <c r="F330" s="3" t="inlineStr"/>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Bowers &amp; Wilkins Nautilus Speaker Tweeter - ZZ11770</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>SERP (partswarehouse, ebay)</t>
+        </is>
+      </c>
     </row>
     <row r="331">
-      <c r="A331" s="3" t="inlineStr">
+      <c r="A331" t="inlineStr">
         <is>
           <t>/products/braun-81756025</t>
         </is>
       </c>
-      <c r="B331" s="3" t="inlineStr">
+      <c r="B331" t="inlineStr">
         <is>
           <t>Braun</t>
         </is>
       </c>
-      <c r="C331" s="3" t="inlineStr"/>
-      <c r="D331" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E331" s="3" t="inlineStr"/>
-      <c r="F331" s="3" t="inlineStr"/>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Braun IPL Hair Removal Precision Head White - 81756025</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr"/>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>encompass</t>
+        </is>
+      </c>
     </row>
     <row r="332">
-      <c r="A332" s="3" t="inlineStr">
+      <c r="A332" s="2" t="inlineStr">
         <is>
           <t>/products/carrier-model-ca16na04200gbaba</t>
         </is>
       </c>
-      <c r="B332" s="3" t="inlineStr">
+      <c r="B332" s="2" t="inlineStr">
         <is>
           <t>Carrier</t>
         </is>
       </c>
-      <c r="C332" s="3" t="inlineStr"/>
-      <c r="D332" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E332" s="3" t="inlineStr"/>
-      <c r="F332" s="3" t="inlineStr"/>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>Carrier 3.5 Ton 16 SEER Central Air Conditioner - CA16NA04200GBABA</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance, REVIEW</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>NOT FOUND online - inferred from Carrier CA16 series model numbering</t>
+        </is>
+      </c>
     </row>
     <row r="333">
-      <c r="A333" s="3" t="inlineStr">
+      <c r="A333" t="inlineStr">
         <is>
           <t>/products/danby-1-05-35-03-100</t>
         </is>
       </c>
-      <c r="B333" s="3" t="inlineStr">
+      <c r="B333" t="inlineStr">
         <is>
           <t>Danby</t>
         </is>
       </c>
-      <c r="C333" s="3" t="inlineStr"/>
-      <c r="D333" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E333" s="3" t="inlineStr"/>
-      <c r="F333" s="3" t="inlineStr"/>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Danby Refrigerator Door Gasket Grey White Push-In - 1.05.35.03.100</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Part number written with dots on Encompass</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>encompass</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
@@ -8719,64 +9967,96 @@
       <c r="F334" s="3" t="inlineStr"/>
     </row>
     <row r="335">
-      <c r="A335" s="3" t="inlineStr">
+      <c r="A335" t="inlineStr">
         <is>
           <t>/products/echo-a050000340</t>
         </is>
       </c>
-      <c r="B335" s="3" t="inlineStr">
+      <c r="B335" t="inlineStr">
         <is>
           <t>Echo</t>
         </is>
       </c>
-      <c r="C335" s="3" t="inlineStr"/>
-      <c r="D335" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E335" s="3" t="inlineStr"/>
-      <c r="F335" s="3" t="inlineStr"/>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Echo Leaf Blower Recoil Starter Assembly - A050000340</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Only one source</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>SERP (ebay)</t>
+        </is>
+      </c>
     </row>
     <row r="336">
-      <c r="A336" s="3" t="inlineStr">
+      <c r="A336" t="inlineStr">
         <is>
           <t>/products/electrolux-318242204</t>
         </is>
       </c>
-      <c r="B336" s="3" t="inlineStr">
+      <c r="B336" t="inlineStr">
         <is>
           <t>Electrolux</t>
         </is>
       </c>
-      <c r="C336" s="3" t="inlineStr"/>
-      <c r="D336" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E336" s="3" t="inlineStr"/>
-      <c r="F336" s="3" t="inlineStr"/>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Electrolux Gas Cooktop Burner Control Knob - 318242204</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>applianceparts4all, partsdr, appliancepartspros, partselect (competitors brand it Frigidaire)</t>
+        </is>
+      </c>
     </row>
     <row r="337">
-      <c r="A337" s="3" t="inlineStr">
+      <c r="A337" t="inlineStr">
         <is>
           <t>/products/electrolux-5304515237</t>
         </is>
       </c>
-      <c r="B337" s="3" t="inlineStr">
+      <c r="B337" t="inlineStr">
         <is>
           <t>Electrolux</t>
         </is>
       </c>
-      <c r="C337" s="3" t="inlineStr"/>
-      <c r="D337" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E337" s="3" t="inlineStr"/>
-      <c r="F337" s="3" t="inlineStr"/>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Electrolux Front Load Washer Dispenser Drawer Handle - 5304515237</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr"/>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>searspartsdirect, partsdr, reliableparts, appliancepartspros, hnkparts, ifixit, partselect, repairclinic (competitors brand it Frigidaire)</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
@@ -8799,24 +10079,36 @@
       <c r="F338" s="3" t="inlineStr"/>
     </row>
     <row r="339">
-      <c r="A339" s="3" t="inlineStr">
+      <c r="A339" t="inlineStr">
         <is>
           <t>/products/eureka-neu180</t>
         </is>
       </c>
-      <c r="B339" s="3" t="inlineStr">
+      <c r="B339" t="inlineStr">
         <is>
           <t>Eureka</t>
         </is>
       </c>
-      <c r="C339" s="3" t="inlineStr"/>
-      <c r="D339" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E339" s="3" t="inlineStr"/>
-      <c r="F339" s="3" t="inlineStr"/>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Eureka PowerSpeed Lightweight Bagless Upright Vacuum - NEU180</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>SERP (ebay)</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
@@ -8839,44 +10131,64 @@
       <c r="F340" s="3" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" s="3" t="inlineStr">
+      <c r="A341" t="inlineStr">
         <is>
           <t>/products/ge-wh10x40097</t>
         </is>
       </c>
-      <c r="B341" s="3" t="inlineStr">
+      <c r="B341" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C341" s="3" t="inlineStr"/>
-      <c r="D341" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E341" s="3" t="inlineStr"/>
-      <c r="F341" s="3" t="inlineStr"/>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>GE Washer Top Load Glass Frame Lid White - WH10X40097</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Replaces WH10X35297 (your row 23)</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>encompass, partsdr, repairclinic, partselect, appliancepartspros</t>
+        </is>
+      </c>
     </row>
     <row r="342">
-      <c r="A342" s="3" t="inlineStr">
+      <c r="A342" t="inlineStr">
         <is>
           <t>/products/ge-wh43x34257</t>
         </is>
       </c>
-      <c r="B342" s="3" t="inlineStr">
+      <c r="B342" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C342" s="3" t="inlineStr"/>
-      <c r="D342" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E342" s="3" t="inlineStr"/>
-      <c r="F342" s="3" t="inlineStr"/>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>GE Washer Agitator Base Hybrid Assembly - WH43X34257</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>partsdr, hnkparts, applianceparts4all, repairclinic, ifixit, genuinereplacementparts, encompass</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="3" t="inlineStr">
@@ -8899,64 +10211,88 @@
       <c r="F343" s="3" t="inlineStr"/>
     </row>
     <row r="344">
-      <c r="A344" s="3" t="inlineStr">
+      <c r="A344" t="inlineStr">
         <is>
           <t>/products/honda-35850-772-003</t>
         </is>
       </c>
-      <c r="B344" s="3" t="inlineStr">
+      <c r="B344" t="inlineStr">
         <is>
           <t>Honda</t>
         </is>
       </c>
-      <c r="C344" s="3" t="inlineStr"/>
-      <c r="D344" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E344" s="3" t="inlineStr"/>
-      <c r="F344" s="3" t="inlineStr"/>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Honda Lawn Tractor Starter Magnetic Switch Assembly - 35850-772-003</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr"/>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>ereplacementparts, SERP (dhsequipmentparts)</t>
+        </is>
+      </c>
     </row>
     <row r="345">
-      <c r="A345" s="3" t="inlineStr">
+      <c r="A345" t="inlineStr">
         <is>
           <t>/products/jet-110045-power-tool-support-bracket</t>
         </is>
       </c>
-      <c r="B345" s="3" t="inlineStr">
+      <c r="B345" t="inlineStr">
         <is>
           <t>Jet</t>
         </is>
       </c>
-      <c r="C345" s="3" t="inlineStr"/>
-      <c r="D345" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E345" s="3" t="inlineStr"/>
-      <c r="F345" s="3" t="inlineStr"/>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Jet 14" Bandsaw Trunnion Support Bracket - 110045</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr"/>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>SERP (hanessupply), ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="346">
-      <c r="A346" s="3" t="inlineStr">
+      <c r="A346" t="inlineStr">
         <is>
           <t>/products/lg-agm30000201</t>
         </is>
       </c>
-      <c r="B346" s="3" t="inlineStr">
+      <c r="B346" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C346" s="3" t="inlineStr"/>
-      <c r="D346" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E346" s="3" t="inlineStr"/>
-      <c r="F346" s="3" t="inlineStr"/>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>LG Dishwasher Water Feed Hose Connector - AGM30000201</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr"/>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>partsdr, appliancepartspros, applianceparts4all, encompass, hnkparts, searspartsdirect, ereplacementparts, ifixit, partselect</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="3" t="inlineStr">
@@ -8979,104 +10315,160 @@
       <c r="F347" s="3" t="inlineStr"/>
     </row>
     <row r="348">
-      <c r="A348" s="3" t="inlineStr">
+      <c r="A348" t="inlineStr">
         <is>
           <t>/products/lg-akb72955815</t>
         </is>
       </c>
-      <c r="B348" s="3" t="inlineStr">
+      <c r="B348" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C348" s="3" t="inlineStr"/>
-      <c r="D348" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E348" s="3" t="inlineStr"/>
-      <c r="F348" s="3" t="inlineStr"/>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>LG Ductless Air Conditioner Remote Controller Assembly - AKB72955815</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr"/>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>partselect, hnkparts, encompass, repairclinic, ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="349">
-      <c r="A349" s="3" t="inlineStr">
+      <c r="A349" t="inlineStr">
         <is>
           <t>/products/lg-ldel7324se</t>
         </is>
       </c>
-      <c r="B349" s="3" t="inlineStr">
+      <c r="B349" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C349" s="3" t="inlineStr"/>
-      <c r="D349" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E349" s="3" t="inlineStr"/>
-      <c r="F349" s="3" t="inlineStr"/>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>LG 7.3 Cu. Ft. Smart Double Oven Electric Range with Air Fry Stainless Steel - LDEL7324SE</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>SERP (abt, consumerreports, bestbuy)</t>
+        </is>
+      </c>
     </row>
     <row r="350">
-      <c r="A350" s="3" t="inlineStr">
+      <c r="A350" t="inlineStr">
         <is>
           <t>/products/lg-lsn120hsv5</t>
         </is>
       </c>
-      <c r="B350" s="3" t="inlineStr">
+      <c r="B350" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C350" s="3" t="inlineStr"/>
-      <c r="D350" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E350" s="3" t="inlineStr"/>
-      <c r="F350" s="3" t="inlineStr"/>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>LG 12,000 BTU Ductless Mini Split Wall Mount Indoor Unit - LSN120HSV5</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>SERP (supplyhouse, bakerdist, herculesindustries)</t>
+        </is>
+      </c>
     </row>
     <row r="351">
-      <c r="A351" s="3" t="inlineStr">
+      <c r="A351" t="inlineStr">
         <is>
           <t>/products/lg-model-lp0721wsr</t>
         </is>
       </c>
-      <c r="B351" s="3" t="inlineStr">
+      <c r="B351" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C351" s="3" t="inlineStr"/>
-      <c r="D351" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E351" s="3" t="inlineStr"/>
-      <c r="F351" s="3" t="inlineStr"/>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>LG 7,000 BTU Portable Air Conditioner White - LP0721WSR</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>SERP (lg.com spec sheet, rtings, ajmadison)</t>
+        </is>
+      </c>
     </row>
     <row r="352">
-      <c r="A352" s="3" t="inlineStr">
+      <c r="A352" t="inlineStr">
         <is>
           <t>/products/magic-chef-model-mcscwd27w5</t>
         </is>
       </c>
-      <c r="B352" s="3" t="inlineStr">
+      <c r="B352" t="inlineStr">
         <is>
           <t>Magic</t>
         </is>
       </c>
-      <c r="C352" s="3" t="inlineStr"/>
-      <c r="D352" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E352" s="3" t="inlineStr"/>
-      <c r="F352" s="3" t="inlineStr"/>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Magic Chef 2.7 Cu. Ft. Ventless Combo Washer Dryer White - MCSCWD27W5</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>SERP (mcappliance.com, homedepot)</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="3" t="inlineStr">

--- a/Appliance_parts_batch_1_H1_titles.xlsx
+++ b/Appliance_parts_batch_1_H1_titles.xlsx
@@ -3343,52 +3343,68 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>/products/braun-80743368</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Braun</t>
         </is>
       </c>
-      <c r="C101" s="3" t="inlineStr"/>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>Searched, not found yet - will retry</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Braun Series 7 7120s Wet &amp; Dry Shaver Handle - 80743368</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW: sellers list it as 7120s shaver unit; not on core competitor list</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>SERP (voomisupply, supplyingdemand)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="inlineStr">
+      <c r="A102" t="inlineStr">
         <is>
           <t>/products/husqvarna-539110306</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>Husqvarna</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr"/>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>Searched, not found yet - will retry</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr"/>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Husqvarna Riding Mower Deck Lift Rod - 539110306</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Discontinued at most sellers</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>SERP (amazon, firedog, partswarehouse, m-and-d)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3647,28 +3663,36 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="inlineStr">
+      <c r="A112" t="inlineStr">
         <is>
           <t>/products/oral-b-81782982</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>Oral</t>
         </is>
       </c>
-      <c r="C112" s="3" t="inlineStr"/>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>Searched, not found yet - will retry</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr"/>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Oral-B iO10 Electric Toothbrush Handle White - 81782982</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Handle only, type 3758</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>SERP (voomisupply, braun-service-station)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3983,28 +4007,36 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="inlineStr">
+      <c r="A124" t="inlineStr">
         <is>
           <t>/products/danby-1-01-03-10-002r</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>Danby</t>
         </is>
       </c>
-      <c r="C124" s="3" t="inlineStr"/>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>Searched, not found yet - will retry</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr"/>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Danby Beer Keg Cooler Touch Key Control Board - 1.01.03.10.002R</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Fits DKC644/645BLS</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>SERP (ebay), encompass partstore, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4531,28 +4563,32 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="inlineStr">
+      <c r="A143" t="inlineStr">
         <is>
           <t>/products/hunter-k842305337</t>
         </is>
       </c>
-      <c r="B143" s="3" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="C143" s="3" t="inlineStr"/>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E143" s="3" t="inlineStr">
-        <is>
-          <t>Searched, not found yet - will retry</t>
-        </is>
-      </c>
-      <c r="F143" s="3" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Hunter Ceiling Fan Blade Set Light Grey Oak / Greyed Walnut - K842305337</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>SERP (hunterfan.com, partsfe)</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5183,24 +5219,36 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="inlineStr">
+      <c r="A165" t="inlineStr">
         <is>
           <t>/products/electrolux-241993701</t>
         </is>
       </c>
-      <c r="B165" s="3" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>Electrolux</t>
         </is>
       </c>
-      <c r="C165" s="3" t="inlineStr"/>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="inlineStr"/>
-      <c r="F165" s="3" t="inlineStr"/>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Electrolux Refrigerator Crisper Drawer Slide Clip - 241993701</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>(competitors brand it Frigidaire)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>SERP (amazon, ebay, partswarehouse)</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5231,44 +5279,60 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="3" t="inlineStr">
+      <c r="A167" t="inlineStr">
         <is>
           <t>/products/greenworks-31121363</t>
         </is>
       </c>
-      <c r="B167" s="3" t="inlineStr">
+      <c r="B167" t="inlineStr">
         <is>
           <t>Greenworks</t>
         </is>
       </c>
-      <c r="C167" s="3" t="inlineStr"/>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E167" s="3" t="inlineStr"/>
-      <c r="F167" s="3" t="inlineStr"/>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Greenworks Pressure Washer High Pressure Hose Assembly - 31121363</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>SERP (amazon, partswarehouse, ppe-pressure-washer-parts)</t>
+        </is>
+      </c>
     </row>
     <row r="168">
-      <c r="A168" s="3" t="inlineStr">
+      <c r="A168" t="inlineStr">
         <is>
           <t>/products/karcher-9-001-188-0</t>
         </is>
       </c>
-      <c r="B168" s="3" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>Karcher</t>
         </is>
       </c>
-      <c r="C168" s="3" t="inlineStr"/>
-      <c r="D168" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E168" s="3" t="inlineStr"/>
-      <c r="F168" s="3" t="inlineStr"/>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Karcher Pressure Washer Water Inlet Elbow - 9.001-188.0</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>partselect, ereplacementparts, SERP (toolbarn, amazon)</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5415,24 +5479,36 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="inlineStr">
+      <c r="A174" t="inlineStr">
         <is>
           <t>/products/makita-421866-9</t>
         </is>
       </c>
-      <c r="B174" s="3" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>Makita</t>
         </is>
       </c>
-      <c r="C174" s="3" t="inlineStr"/>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="inlineStr"/>
-      <c r="F174" s="3" t="inlineStr"/>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Makita Random Orbit Sander Brake Ring - 421866-9</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Fits BO5010 series</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>encompass, ereplacementparts, SERP (amazon, zoro)</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5823,24 +5899,32 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="3" t="inlineStr">
+      <c r="A188" t="inlineStr">
         <is>
           <t>/products/braun-81626417</t>
         </is>
       </c>
-      <c r="B188" s="3" t="inlineStr">
+      <c r="B188" t="inlineStr">
         <is>
           <t>Braun</t>
         </is>
       </c>
-      <c r="C188" s="3" t="inlineStr"/>
-      <c r="D188" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E188" s="3" t="inlineStr"/>
-      <c r="F188" s="3" t="inlineStr"/>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Braun Series 9 Replacement Shaver Head 92B Black - 81626417</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>SERP (fixpart, spares4shavers, voomisupply)</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5907,24 +5991,36 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="3" t="inlineStr">
+      <c r="A191" t="inlineStr">
         <is>
           <t>/products/greenworks-r0201467-00</t>
         </is>
       </c>
-      <c r="B191" s="3" t="inlineStr">
+      <c r="B191" t="inlineStr">
         <is>
           <t>Greenworks</t>
         </is>
       </c>
-      <c r="C191" s="3" t="inlineStr"/>
-      <c r="D191" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E191" s="3" t="inlineStr"/>
-      <c r="F191" s="3" t="inlineStr"/>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Greenworks 42" Zero Turn Mower Front Wheel Assembly - R0201467-00</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Fits CrossoverZ CRZ426/CRZ428</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>ereplacementparts, SERP (greenworkstools, partswarehouse, fix.com)</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -6671,24 +6767,32 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="3" t="inlineStr">
+      <c r="A217" t="inlineStr">
         <is>
           <t>/products/char-broil-g354-0024-w1</t>
         </is>
       </c>
-      <c r="B217" s="3" t="inlineStr">
+      <c r="B217" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
-      <c r="C217" s="3" t="inlineStr"/>
-      <c r="D217" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E217" s="3" t="inlineStr"/>
-      <c r="F217" s="3" t="inlineStr"/>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Char-Broil Gas Grill Flame Carryover Tube - G354-0024-W1</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>partselect, ereplacementparts, SERP (fix.com, grillpartsamerica)</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -6927,24 +7031,32 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="3" t="inlineStr">
+      <c r="A226" t="inlineStr">
         <is>
           <t>/products/abu-garcia-1452795</t>
         </is>
       </c>
-      <c r="B226" s="3" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>Abu</t>
         </is>
       </c>
-      <c r="C226" s="3" t="inlineStr"/>
-      <c r="D226" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E226" s="3" t="inlineStr"/>
-      <c r="F226" s="3" t="inlineStr"/>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Abu Garcia Revo 4 X Baitcast Reel Palm Side Plate Complete - 1452795</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>ereplacementparts, SERP (mikesreelrepair, ebay)</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7039,44 +7151,68 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="3" t="inlineStr">
+      <c r="A230" t="inlineStr">
         <is>
           <t>/products/blomberg-model-7185881500</t>
         </is>
       </c>
-      <c r="B230" s="3" t="inlineStr">
+      <c r="B230" t="inlineStr">
         <is>
           <t>Blomberg</t>
         </is>
       </c>
-      <c r="C230" s="3" t="inlineStr"/>
-      <c r="D230" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E230" s="3" t="inlineStr"/>
-      <c r="F230" s="3" t="inlineStr"/>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Blomberg 24" Compact Electric Vented Dryer White - 7185881500</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance (DV17600W)</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>encompass, SERP (partstown, appliantology)</t>
+        </is>
+      </c>
     </row>
     <row r="231">
-      <c r="A231" s="3" t="inlineStr">
+      <c r="A231" t="inlineStr">
         <is>
           <t>/products/bosch-12000351</t>
         </is>
       </c>
-      <c r="B231" s="3" t="inlineStr">
+      <c r="B231" t="inlineStr">
         <is>
           <t>Bosch</t>
         </is>
       </c>
-      <c r="C231" s="3" t="inlineStr"/>
-      <c r="D231" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E231" s="3" t="inlineStr"/>
-      <c r="F231" s="3" t="inlineStr"/>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Bosch Range Hood Charcoal Odor Filter - 12000351</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Also sold as HCIFILTUC</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>SERP (bosch-home.com HCIFILTUC, ebay, appliance dealers)</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7315,24 +7451,36 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="3" t="inlineStr">
+      <c r="A240" t="inlineStr">
         <is>
           <t>/products/hunter-k008902h03</t>
         </is>
       </c>
-      <c r="B240" s="3" t="inlineStr">
+      <c r="B240" t="inlineStr">
         <is>
           <t>Hunter</t>
         </is>
       </c>
-      <c r="C240" s="3" t="inlineStr"/>
-      <c r="D240" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E240" s="3" t="inlineStr"/>
-      <c r="F240" s="3" t="inlineStr"/>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Hunter Ceiling Fan 3-Speed Wire Harness - K008902H03</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Discontinued at most sellers</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>encompass, ereplacementparts, partselect</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -7767,24 +7915,36 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="3" t="inlineStr">
+      <c r="A256" t="inlineStr">
         <is>
           <t>/products/sharp-9kc351260012500</t>
         </is>
       </c>
-      <c r="B256" s="3" t="inlineStr">
+      <c r="B256" t="inlineStr">
         <is>
           <t>Sharp</t>
         </is>
       </c>
-      <c r="C256" s="3" t="inlineStr"/>
-      <c r="D256" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E256" s="3" t="inlineStr"/>
-      <c r="F256" s="3" t="inlineStr"/>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Sharp Over-the-Range Microwave Air Filter Handle - 9KC351260012500</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Fits SMO1652DS</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>SERP (partstown, partswarehouse)</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -7839,24 +7999,32 @@
       <c r="F258" s="3" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="3" t="inlineStr">
+      <c r="A259" t="inlineStr">
         <is>
           <t>/products/sharp-ntnt-a094wre0</t>
         </is>
       </c>
-      <c r="B259" s="3" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>Sharp</t>
         </is>
       </c>
-      <c r="C259" s="3" t="inlineStr"/>
-      <c r="D259" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E259" s="3" t="inlineStr"/>
-      <c r="F259" s="3" t="inlineStr"/>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Sharp Microwave Glass Turntable Tray 11-1/2" - NTNT-A094WRE0</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>encompass, appliancefactoryparts, SERP (amazon, ebay)</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -7887,24 +8055,36 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="3" t="inlineStr">
+      <c r="A261" t="inlineStr">
         <is>
           <t>/products/sony-model-hbb7070</t>
         </is>
       </c>
-      <c r="B261" s="3" t="inlineStr">
+      <c r="B261" t="inlineStr">
         <is>
           <t>Sony</t>
         </is>
       </c>
-      <c r="C261" s="3" t="inlineStr"/>
-      <c r="D261" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E261" s="3" t="inlineStr"/>
-      <c r="F261" s="3" t="inlineStr"/>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Sony My First Sony Animation Computer - HB-B7070</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Model number - whole product (discontinued 1990s)</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>encompass, SERP (fccid, ebay, manuals)</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -7939,24 +8119,36 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="3" t="inlineStr">
+      <c r="A263" t="inlineStr">
         <is>
           <t>/products/toro-308480002</t>
         </is>
       </c>
-      <c r="B263" s="3" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>Toro</t>
         </is>
       </c>
-      <c r="C263" s="3" t="inlineStr"/>
-      <c r="D263" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E263" s="3" t="inlineStr"/>
-      <c r="F263" s="3" t="inlineStr"/>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Toro PowerVac Gas Blower Vacuum Carburetor Assembly - 308480002</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Fits model 51988</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>partselect, SERP (toro.com, bahrns, 2mequipment)</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8227,24 +8419,36 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="3" t="inlineStr">
+      <c r="A273" s="2" t="inlineStr">
         <is>
           <t>/products/bowers-wilkins-hh30042</t>
         </is>
       </c>
-      <c r="B273" s="3" t="inlineStr">
+      <c r="B273" s="2" t="inlineStr">
         <is>
           <t>Bowers</t>
         </is>
       </c>
-      <c r="C273" s="3" t="inlineStr"/>
-      <c r="D273" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E273" s="3" t="inlineStr"/>
-      <c r="F273" s="3" t="inlineStr"/>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>Bowers &amp; Wilkins Speaker M6 Spike Insert - HH30042</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW: single source; obsolete</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>SERP (partstown)</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -8363,44 +8567,64 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="3" t="inlineStr">
+      <c r="A278" t="inlineStr">
         <is>
           <t>/products/eureka-nen0102</t>
         </is>
       </c>
-      <c r="B278" s="3" t="inlineStr">
+      <c r="B278" t="inlineStr">
         <is>
           <t>Eureka</t>
         </is>
       </c>
-      <c r="C278" s="3" t="inlineStr"/>
-      <c r="D278" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E278" s="3" t="inlineStr"/>
-      <c r="F278" s="3" t="inlineStr"/>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Eureka WhirlWind Canister Vacuum Floor Nozzle - NEN0102</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>encompass, SERP (amazon, walmart, eureka manual)</t>
+        </is>
+      </c>
     </row>
     <row r="279">
-      <c r="A279" s="3" t="inlineStr">
+      <c r="A279" t="inlineStr">
         <is>
           <t>/products/eureka-neu529</t>
         </is>
       </c>
-      <c r="B279" s="3" t="inlineStr">
+      <c r="B279" t="inlineStr">
         <is>
           <t>Eureka</t>
         </is>
       </c>
-      <c r="C279" s="3" t="inlineStr"/>
-      <c r="D279" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E279" s="3" t="inlineStr"/>
-      <c r="F279" s="3" t="inlineStr"/>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Eureka FloorRover Dash Bagless Upright Vacuum - NEU529</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Model number - whole product</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>encompass, shopjimmy, SERP (ebay, manualslib)</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -8431,24 +8655,36 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="3" t="inlineStr">
+      <c r="A281" s="2" t="inlineStr">
         <is>
           <t>/products/gillette-80754166</t>
         </is>
       </c>
-      <c r="B281" s="3" t="inlineStr">
+      <c r="B281" s="2" t="inlineStr">
         <is>
           <t>Gillette</t>
         </is>
       </c>
-      <c r="C281" s="3" t="inlineStr"/>
-      <c r="D281" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E281" s="3" t="inlineStr"/>
-      <c r="F281" s="3" t="inlineStr"/>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>Gillette Labs Heated Razor Gold Edition - 80754166</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW: single source</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>SERP (voomisupply)</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -8483,44 +8719,60 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="3" t="inlineStr">
+      <c r="A283" t="inlineStr">
         <is>
           <t>/products/greenworks-31102489a-2</t>
         </is>
       </c>
-      <c r="B283" s="3" t="inlineStr">
+      <c r="B283" t="inlineStr">
         <is>
           <t>Greenworks</t>
         </is>
       </c>
-      <c r="C283" s="3" t="inlineStr"/>
-      <c r="D283" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E283" s="3" t="inlineStr"/>
-      <c r="F283" s="3" t="inlineStr"/>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Greenworks Lawn Mower Motor Engagement Box - 31102489A-2</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>SERP (m-and-d, partswarehouse, poweredbymoyer)</t>
+        </is>
+      </c>
     </row>
     <row r="284">
-      <c r="A284" s="3" t="inlineStr">
+      <c r="A284" t="inlineStr">
         <is>
           <t>/products/greenworks-332051179</t>
         </is>
       </c>
-      <c r="B284" s="3" t="inlineStr">
+      <c r="B284" t="inlineStr">
         <is>
           <t>Greenworks</t>
         </is>
       </c>
-      <c r="C284" s="3" t="inlineStr"/>
-      <c r="D284" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E284" s="3" t="inlineStr"/>
-      <c r="F284" s="3" t="inlineStr"/>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Greenworks Lawn Mower Compression Spring - 332051179</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>SERP (greenworkstools, partswarehouse, manualslib)</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -8755,24 +9007,36 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="3" t="inlineStr">
+      <c r="A293" t="inlineStr">
         <is>
           <t>/products/ryobi-elect-tools-039858011099</t>
         </is>
       </c>
-      <c r="B293" s="3" t="inlineStr">
+      <c r="B293" t="inlineStr">
         <is>
           <t>Ryobi</t>
         </is>
       </c>
-      <c r="C293" s="3" t="inlineStr"/>
-      <c r="D293" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E293" s="3" t="inlineStr"/>
-      <c r="F293" s="3" t="inlineStr"/>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Ryobi 18V Hybrid Air Cannon Fan Speed Switch and Circuit Board - 039858011099</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Fits P3340</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>partselect, SERP (ebay, partswarehouse)</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10471,124 +10735,184 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="3" t="inlineStr">
+      <c r="A353" t="inlineStr">
         <is>
           <t>/products/midea-11300903000421</t>
         </is>
       </c>
-      <c r="B353" s="3" t="inlineStr">
+      <c r="B353" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C353" s="3" t="inlineStr"/>
-      <c r="D353" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E353" s="3" t="inlineStr"/>
-      <c r="F353" s="3" t="inlineStr"/>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Midea Washer Bolt with Spring Washer and Plain Washer - 11300903000421</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr"/>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>searspartsdirect, encompass</t>
+        </is>
+      </c>
     </row>
     <row r="354">
-      <c r="A354" s="3" t="inlineStr">
+      <c r="A354" t="inlineStr">
         <is>
           <t>/products/midea-17120300003509</t>
         </is>
       </c>
-      <c r="B354" s="3" t="inlineStr">
+      <c r="B354" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C354" s="3" t="inlineStr"/>
-      <c r="D354" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E354" s="3" t="inlineStr"/>
-      <c r="F354" s="3" t="inlineStr"/>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Midea Window Air Conditioner Main Control Board Subassembly - 17120300003509</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr"/>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>hnkparts, ifixit, partselect, appliancefactoryparts, searspartsdirect, encompass, shopjimmy</t>
+        </is>
+      </c>
     </row>
     <row r="355">
-      <c r="A355" s="3" t="inlineStr">
+      <c r="A355" t="inlineStr">
         <is>
           <t>/products/midea-17400104000795</t>
         </is>
       </c>
-      <c r="B355" s="3" t="inlineStr">
+      <c r="B355" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C355" s="3" t="inlineStr"/>
-      <c r="D355" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E355" s="3" t="inlineStr"/>
-      <c r="F355" s="3" t="inlineStr"/>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Midea Window Air Conditioner Combination Capacitor - 17400104000795</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr"/>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>hnkparts, genuinereplacementparts, partselect, ifixit</t>
+        </is>
+      </c>
     </row>
     <row r="356">
-      <c r="A356" s="3" t="inlineStr">
+      <c r="A356" s="2" t="inlineStr">
         <is>
           <t>/products/midea-model-137180</t>
         </is>
       </c>
-      <c r="B356" s="3" t="inlineStr">
+      <c r="B356" s="2" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C356" s="3" t="inlineStr"/>
-      <c r="D356" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E356" s="3" t="inlineStr"/>
-      <c r="F356" s="3" t="inlineStr"/>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>Midea Refrigerator - 137180</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance, REVIEW</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>SERP (ebay parts listing names it as a Midea refrigerator model)</t>
+        </is>
+      </c>
     </row>
     <row r="357">
-      <c r="A357" s="3" t="inlineStr">
+      <c r="A357" s="2" t="inlineStr">
         <is>
           <t>/products/midea-model-nsuz7wh0</t>
         </is>
       </c>
-      <c r="B357" s="3" t="inlineStr">
+      <c r="B357" s="2" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C357" s="3" t="inlineStr"/>
-      <c r="D357" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E357" s="3" t="inlineStr"/>
-      <c r="F357" s="3" t="inlineStr"/>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>Midea Upright Convertible Freezer White - NSUZ7WH0</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance, REVIEW</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>NOT FOUND online - inferred from Midea/Insignia NSUZ upright freezer family (partswarehouse)</t>
+        </is>
+      </c>
     </row>
     <row r="358">
-      <c r="A358" s="3" t="inlineStr">
+      <c r="A358" s="2" t="inlineStr">
         <is>
           <t>/products/milwaukee-42-55-2647</t>
         </is>
       </c>
-      <c r="B358" s="3" t="inlineStr">
+      <c r="B358" s="2" t="inlineStr">
         <is>
           <t>Milwaukee</t>
         </is>
       </c>
-      <c r="C358" s="3" t="inlineStr"/>
-      <c r="D358" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E358" s="3" t="inlineStr"/>
-      <c r="F358" s="3" t="inlineStr"/>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>Milwaukee Power Tool Carrying Case - 42-55-2647</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>NOT FOUND online - inferred from Milwaukee 42-55 carrying case series</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
@@ -10651,24 +10975,32 @@
       <c r="F361" s="3" t="inlineStr"/>
     </row>
     <row r="362">
-      <c r="A362" s="3" t="inlineStr">
+      <c r="A362" t="inlineStr">
         <is>
           <t>/products/panasonic-vsk0763</t>
         </is>
       </c>
-      <c r="B362" s="3" t="inlineStr">
+      <c r="B362" t="inlineStr">
         <is>
           <t>Panasonic</t>
         </is>
       </c>
-      <c r="C362" s="3" t="inlineStr"/>
-      <c r="D362" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E362" s="3" t="inlineStr"/>
-      <c r="F362" s="3" t="inlineStr"/>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Panasonic Camcorder AC Adapter - VSK0763</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr"/>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
@@ -10691,144 +11023,212 @@
       <c r="F363" s="3" t="inlineStr"/>
     </row>
     <row r="364">
-      <c r="A364" s="3" t="inlineStr">
+      <c r="A364" t="inlineStr">
         <is>
           <t>/products/samsung-haf-qin-2p-exp</t>
         </is>
       </c>
-      <c r="B364" s="3" t="inlineStr">
+      <c r="B364" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C364" s="3" t="inlineStr"/>
-      <c r="D364" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E364" s="3" t="inlineStr"/>
-      <c r="F364" s="3" t="inlineStr"/>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Samsung Refrigerator Water Filter - HAF-QIN/EXP</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr"/>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>SERP (samsung.com, thebrick, abt)</t>
+        </is>
+      </c>
     </row>
     <row r="365">
-      <c r="A365" s="3" t="inlineStr">
+      <c r="A365" s="2" t="inlineStr">
         <is>
           <t>/products/sharp-cpnlcc302mrk3</t>
         </is>
       </c>
-      <c r="B365" s="3" t="inlineStr">
+      <c r="B365" s="2" t="inlineStr">
         <is>
           <t>Sharp</t>
         </is>
       </c>
-      <c r="C365" s="3" t="inlineStr"/>
-      <c r="D365" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E365" s="3" t="inlineStr"/>
-      <c r="F365" s="3" t="inlineStr"/>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>Sharp Microwave Drawer Touchpad Control Panel Assembly - CPNLCC302MRK3</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>NOT FOUND online - inferred from newer revision CPNLCC302MRK7 (hnkparts)</t>
+        </is>
+      </c>
     </row>
     <row r="366">
-      <c r="A366" s="3" t="inlineStr">
+      <c r="A366" t="inlineStr">
         <is>
           <t>/products/sonicare-423501040701</t>
         </is>
       </c>
-      <c r="B366" s="3" t="inlineStr">
+      <c r="B366" t="inlineStr">
         <is>
           <t>Sonicare</t>
         </is>
       </c>
-      <c r="C366" s="3" t="inlineStr"/>
-      <c r="D366" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E366" s="3" t="inlineStr"/>
-      <c r="F366" s="3" t="inlineStr"/>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Sonicare Toothbrush Charging Travel Case Black - 423501040701</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr"/>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>encompass (philips.encompass.com)</t>
+        </is>
+      </c>
     </row>
     <row r="367">
-      <c r="A367" s="3" t="inlineStr">
+      <c r="A367" t="inlineStr">
         <is>
           <t>/products/sonicare-423501041171</t>
         </is>
       </c>
-      <c r="B367" s="3" t="inlineStr">
+      <c r="B367" t="inlineStr">
         <is>
           <t>Sonicare</t>
         </is>
       </c>
-      <c r="C367" s="3" t="inlineStr"/>
-      <c r="D367" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E367" s="3" t="inlineStr"/>
-      <c r="F367" s="3" t="inlineStr"/>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Sonicare Toothbrush USB Wall Adapter White - 423501041171</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr"/>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>encompass (philips.encompass.com)</t>
+        </is>
+      </c>
     </row>
     <row r="368">
-      <c r="A368" s="3" t="inlineStr">
+      <c r="A368" t="inlineStr">
         <is>
           <t>/products/sony-1-009-952-11</t>
         </is>
       </c>
-      <c r="B368" s="3" t="inlineStr">
+      <c r="B368" t="inlineStr">
         <is>
           <t>Sony</t>
         </is>
       </c>
-      <c r="C368" s="3" t="inlineStr"/>
-      <c r="D368" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E368" s="3" t="inlineStr"/>
-      <c r="F368" s="3" t="inlineStr"/>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Sony TV Remote Control RMF-TX520U - 1-009-952-11</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr"/>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>shopjimmy, encompass, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="369">
-      <c r="A369" s="3" t="inlineStr">
+      <c r="A369" t="inlineStr">
         <is>
           <t>/products/sony-model-dsch90</t>
         </is>
       </c>
-      <c r="B369" s="3" t="inlineStr">
+      <c r="B369" t="inlineStr">
         <is>
           <t>Sony</t>
         </is>
       </c>
-      <c r="C369" s="3" t="inlineStr"/>
-      <c r="D369" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E369" s="3" t="inlineStr"/>
-      <c r="F369" s="3" t="inlineStr"/>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Sony Cyber-shot 16.1MP Digital Camera with 16x Zoom - DSC-H90</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Model number - whole product</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>SERP (dpreview, imaging-resource, neocamera)</t>
+        </is>
+      </c>
     </row>
     <row r="370">
-      <c r="A370" s="3" t="inlineStr">
+      <c r="A370" t="inlineStr">
         <is>
           <t>/products/sony-model-sel200600g</t>
         </is>
       </c>
-      <c r="B370" s="3" t="inlineStr">
+      <c r="B370" t="inlineStr">
         <is>
           <t>Sony</t>
         </is>
       </c>
-      <c r="C370" s="3" t="inlineStr"/>
-      <c r="D370" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E370" s="3" t="inlineStr"/>
-      <c r="F370" s="3" t="inlineStr"/>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Sony FE 200-600mm F5.6-6.3 G OSS Telephoto Zoom Lens - SEL200600G</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Model number - whole product</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>SERP (sony.com, robertscamera)</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
@@ -10931,584 +11331,868 @@
       <c r="F375" s="3" t="inlineStr"/>
     </row>
     <row r="376">
-      <c r="A376" s="3" t="inlineStr">
+      <c r="A376" t="inlineStr">
         <is>
           <t>/products/whirlpool-w10314417</t>
         </is>
       </c>
-      <c r="B376" s="3" t="inlineStr">
+      <c r="B376" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C376" s="3" t="inlineStr"/>
-      <c r="D376" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E376" s="3" t="inlineStr"/>
-      <c r="F376" s="3" t="inlineStr"/>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Whirlpool Range Touchpad Control Panel Assembly Stainless - W10314417</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr"/>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>partsdr, applianceparts4all, searspartsdirect, repairclinic, appliancepartspros, encompass, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="377">
-      <c r="A377" s="3" t="inlineStr">
+      <c r="A377" t="inlineStr">
         <is>
           <t>/products/whirlpool-w11241699</t>
         </is>
       </c>
-      <c r="B377" s="3" t="inlineStr">
+      <c r="B377" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C377" s="3" t="inlineStr"/>
-      <c r="D377" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E377" s="3" t="inlineStr"/>
-      <c r="F377" s="3" t="inlineStr"/>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Whirlpool Dishwasher Upper Rack Water Supply Tube Manifold - W11241699</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr"/>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>reliableparts, partselect, partsdr</t>
+        </is>
+      </c>
     </row>
     <row r="378">
-      <c r="A378" s="3" t="inlineStr">
+      <c r="A378" t="inlineStr">
         <is>
           <t>/products/whirlpool-w11692811</t>
         </is>
       </c>
-      <c r="B378" s="3" t="inlineStr">
+      <c r="B378" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C378" s="3" t="inlineStr"/>
-      <c r="D378" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E378" s="3" t="inlineStr"/>
-      <c r="F378" s="3" t="inlineStr"/>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Whirlpool Range Air Fry Basket - W11692811</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr"/>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>partadvantage, partsdr (repairclinic lists it as a rack)</t>
+        </is>
+      </c>
     </row>
     <row r="379">
-      <c r="A379" s="3" t="inlineStr">
+      <c r="A379" t="inlineStr">
         <is>
           <t>/products/whirlpool-w11741357</t>
         </is>
       </c>
-      <c r="B379" s="3" t="inlineStr">
+      <c r="B379" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C379" s="3" t="inlineStr"/>
-      <c r="D379" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E379" s="3" t="inlineStr"/>
-      <c r="F379" s="3" t="inlineStr"/>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Whirlpool Range Oven Outer Door Glass - W11741357</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr"/>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>reliableparts, hnkparts, searspartsdirect, partadvantage</t>
+        </is>
+      </c>
     </row>
     <row r="380">
-      <c r="A380" s="3" t="inlineStr">
+      <c r="A380" t="inlineStr">
         <is>
           <t>/products/whirlpool-wp3955489</t>
         </is>
       </c>
-      <c r="B380" s="3" t="inlineStr">
+      <c r="B380" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C380" s="3" t="inlineStr"/>
-      <c r="D380" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E380" s="3" t="inlineStr"/>
-      <c r="F380" s="3" t="inlineStr"/>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Whirlpool Washer Timer 60 Hz - WP3955489</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>applianceparts4all, ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="381">
-      <c r="A381" s="3" t="inlineStr">
+      <c r="A381" t="inlineStr">
         <is>
           <t>/products/whirlpool-wp5760m373-60</t>
         </is>
       </c>
-      <c r="B381" s="3" t="inlineStr">
+      <c r="B381" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C381" s="3" t="inlineStr"/>
-      <c r="D381" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E381" s="3" t="inlineStr"/>
-      <c r="F381" s="3" t="inlineStr"/>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Whirlpool Range Touchpad Control Panel Stainless/Black - WP5760M373-60</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr"/>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>applianceparts4all, reliableparts, partsdr, appliancepartspros, encompass, searspartsdirect</t>
+        </is>
+      </c>
     </row>
     <row r="382">
-      <c r="A382" s="3" t="inlineStr">
+      <c r="A382" t="inlineStr">
         <is>
           <t>/products/whirlpool-wpw10163866</t>
         </is>
       </c>
-      <c r="B382" s="3" t="inlineStr">
+      <c r="B382" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C382" s="3" t="inlineStr"/>
-      <c r="D382" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E382" s="3" t="inlineStr"/>
-      <c r="F382" s="3" t="inlineStr"/>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Whirlpool Front Load Washer Detergent Dispenser Assembly - WPW10163866</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>repairclinic, encompass, ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="383">
-      <c r="A383" s="3" t="inlineStr">
+      <c r="A383" t="inlineStr">
         <is>
           <t>/products/whirlpool-wpw10243437</t>
         </is>
       </c>
-      <c r="B383" s="3" t="inlineStr">
+      <c r="B383" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C383" s="3" t="inlineStr"/>
-      <c r="D383" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E383" s="3" t="inlineStr"/>
-      <c r="F383" s="3" t="inlineStr"/>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Whirlpool Laundry Pedestal Drawer Handle - WPW10243437</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr"/>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>partsdr, ereplacementparts, genuinereplacementparts, partselect, repairclinic, partadvantage</t>
+        </is>
+      </c>
     </row>
     <row r="384">
-      <c r="A384" s="3" t="inlineStr">
+      <c r="A384" t="inlineStr">
         <is>
           <t>/products/whirlpool-wpw10498430</t>
         </is>
       </c>
-      <c r="B384" s="3" t="inlineStr">
+      <c r="B384" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C384" s="3" t="inlineStr"/>
-      <c r="D384" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E384" s="3" t="inlineStr"/>
-      <c r="F384" s="3" t="inlineStr"/>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Whirlpool Top Freezer Refrigerator Door Handle Black - WPW10498430</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr"/>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>partadvantage, appliancepartspros, partselect, genuinereplacementparts, repairclinic, reliableparts</t>
+        </is>
+      </c>
     </row>
     <row r="385">
-      <c r="A385" s="3" t="inlineStr">
+      <c r="A385" t="inlineStr">
         <is>
           <t>/products/bosch-573828-coffee-machine-descaler</t>
         </is>
       </c>
-      <c r="B385" s="3" t="inlineStr">
+      <c r="B385" t="inlineStr">
         <is>
           <t>Bosch</t>
         </is>
       </c>
-      <c r="C385" s="3" t="inlineStr"/>
-      <c r="D385" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E385" s="3" t="inlineStr"/>
-      <c r="F385" s="3" t="inlineStr"/>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Bosch Coffee Machine and Steam Oven Descaler Powder 4-Pack - 00573828</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Competitors list part number as 00573828</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>SERP (bosch-home.com, thermador.com, gaggenau.com), appliancepartspros</t>
+        </is>
+      </c>
     </row>
     <row r="386">
-      <c r="A386" s="3" t="inlineStr">
+      <c r="A386" t="inlineStr">
         <is>
           <t>/products/bosch-model-shxm63w55n-13</t>
         </is>
       </c>
-      <c r="B386" s="3" t="inlineStr">
+      <c r="B386" t="inlineStr">
         <is>
           <t>Bosch</t>
         </is>
       </c>
-      <c r="C386" s="3" t="inlineStr"/>
-      <c r="D386" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E386" s="3" t="inlineStr"/>
-      <c r="F386" s="3" t="inlineStr"/>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Bosch 300 Series 24" Top Control Stainless Steel Dishwasher with 3rd Rack - SHXM63W55N/13</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>SERP (homedepot, canadianappliance, townappliance)</t>
+        </is>
+      </c>
     </row>
     <row r="387">
-      <c r="A387" s="3" t="inlineStr">
+      <c r="A387" t="inlineStr">
         <is>
           <t>/products/broan-s97020971-range-hood-fan-motor-kit</t>
         </is>
       </c>
-      <c r="B387" s="3" t="inlineStr">
+      <c r="B387" t="inlineStr">
         <is>
           <t>Broan</t>
         </is>
       </c>
-      <c r="C387" s="3" t="inlineStr"/>
-      <c r="D387" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E387" s="3" t="inlineStr"/>
-      <c r="F387" s="3" t="inlineStr"/>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Broan Range Hood Fan Motor Blower Assembly - S97020971</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Only one source</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>SERP (electricmotorwarehouse)</t>
+        </is>
+      </c>
     </row>
     <row r="388">
-      <c r="A388" s="3" t="inlineStr">
+      <c r="A388" t="inlineStr">
         <is>
           <t>/products/char-broil-g432-h500-w1</t>
         </is>
       </c>
-      <c r="B388" s="3" t="inlineStr">
+      <c r="B388" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
-      <c r="C388" s="3" t="inlineStr"/>
-      <c r="D388" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E388" s="3" t="inlineStr"/>
-      <c r="F388" s="3" t="inlineStr"/>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Char-Broil Gas Grill Right Side Shelf - G432-H500-W1</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Only one source</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>SERP (newegg)</t>
+        </is>
+      </c>
     </row>
     <row r="389">
-      <c r="A389" s="3" t="inlineStr">
+      <c r="A389" t="inlineStr">
         <is>
           <t>/products/danby-12676000000558</t>
         </is>
       </c>
-      <c r="B389" s="3" t="inlineStr">
+      <c r="B389" t="inlineStr">
         <is>
           <t>Danby</t>
         </is>
       </c>
-      <c r="C389" s="3" t="inlineStr"/>
-      <c r="D389" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E389" s="3" t="inlineStr"/>
-      <c r="F389" s="3" t="inlineStr"/>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Danby Dishwasher Fill and Drain Hose Faucet Coupler - 12676000000558</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr"/>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>searspartsdirect, appliancepartspros, repairclinic</t>
+        </is>
+      </c>
     </row>
     <row r="390">
-      <c r="A390" s="3" t="inlineStr">
+      <c r="A390" t="inlineStr">
         <is>
           <t>/products/ge-model-gsd5900g00ww</t>
         </is>
       </c>
-      <c r="B390" s="3" t="inlineStr">
+      <c r="B390" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C390" s="3" t="inlineStr"/>
-      <c r="D390" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E390" s="3" t="inlineStr"/>
-      <c r="F390" s="3" t="inlineStr"/>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>GE Triton Built-In Dishwasher White - GSD5900G00WW</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>SERP (geappliances.com for GSD5900GWW, repairclinic)</t>
+        </is>
+      </c>
     </row>
     <row r="391">
-      <c r="A391" s="3" t="inlineStr">
+      <c r="A391" t="inlineStr">
         <is>
           <t>/products/ge-model-peb9159sj3ss</t>
         </is>
       </c>
-      <c r="B391" s="3" t="inlineStr">
+      <c r="B391" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C391" s="3" t="inlineStr"/>
-      <c r="D391" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E391" s="3" t="inlineStr"/>
-      <c r="F391" s="3" t="inlineStr"/>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>GE Profile 1.5 Cu. Ft. Countertop Convection Microwave Stainless Steel - PEB9159SJ3SS</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>SERP (partselect, ajmadison for PEB9159SJSS)</t>
+        </is>
+      </c>
     </row>
     <row r="392">
-      <c r="A392" s="3" t="inlineStr">
+      <c r="A392" t="inlineStr">
         <is>
           <t>/products/ge-wb02x11491</t>
         </is>
       </c>
-      <c r="B392" s="3" t="inlineStr">
+      <c r="B392" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C392" s="3" t="inlineStr"/>
-      <c r="D392" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E392" s="3" t="inlineStr"/>
-      <c r="F392" s="3" t="inlineStr"/>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>GE Range Hood Grease Filter - WB02X11491</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr"/>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>searspartsdirect, appliancepartspros, hnkparts, ifixit, partsdr, encompass, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="393">
-      <c r="A393" s="3" t="inlineStr">
+      <c r="A393" t="inlineStr">
         <is>
           <t>/products/ge-wb02x35488</t>
         </is>
       </c>
-      <c r="B393" s="3" t="inlineStr">
+      <c r="B393" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C393" s="3" t="inlineStr"/>
-      <c r="D393" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E393" s="3" t="inlineStr"/>
-      <c r="F393" s="3" t="inlineStr"/>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>GE Microwave Hood Combo Halogen Lamp - WB02X35488</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr"/>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>ifixit, appliancepartspros, partselect, ereplacementparts, hnkparts, genuinereplacementparts, partsdr, searspartsdirect</t>
+        </is>
+      </c>
     </row>
     <row r="394">
-      <c r="A394" s="3" t="inlineStr">
+      <c r="A394" t="inlineStr">
         <is>
           <t>/products/ge-wb02x35491</t>
         </is>
       </c>
-      <c r="B394" s="3" t="inlineStr">
+      <c r="B394" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C394" s="3" t="inlineStr"/>
-      <c r="D394" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E394" s="3" t="inlineStr"/>
-      <c r="F394" s="3" t="inlineStr"/>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>GE Microwave Hood Combo Grease Filter - WB02X35491</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr"/>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>appliancepartspros, hnkparts, ifixit, partsdr, encompass, applianceparts4all, partselect</t>
+        </is>
+      </c>
     </row>
     <row r="395">
-      <c r="A395" s="3" t="inlineStr">
+      <c r="A395" t="inlineStr">
         <is>
           <t>/products/ge-wb03k10077</t>
         </is>
       </c>
-      <c r="B395" s="3" t="inlineStr">
+      <c r="B395" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C395" s="3" t="inlineStr"/>
-      <c r="D395" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E395" s="3" t="inlineStr"/>
-      <c r="F395" s="3" t="inlineStr"/>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>GE Gas Range Warming Drawer Knob Black - WB03K10077</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>encompass, ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="396">
-      <c r="A396" s="3" t="inlineStr">
+      <c r="A396" t="inlineStr">
         <is>
           <t>/products/ge-wb07x11007</t>
         </is>
       </c>
-      <c r="B396" s="3" t="inlineStr">
+      <c r="B396" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C396" s="3" t="inlineStr"/>
-      <c r="D396" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E396" s="3" t="inlineStr"/>
-      <c r="F396" s="3" t="inlineStr"/>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>GE Microwave Vent Grille White - WB07X11007</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>partadvantage, repairclinic, partselect, encompass, genuinereplacementparts, ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="397">
-      <c r="A397" s="3" t="inlineStr">
+      <c r="A397" t="inlineStr">
         <is>
           <t>/products/ge-wb18t10343</t>
         </is>
       </c>
-      <c r="B397" s="3" t="inlineStr">
+      <c r="B397" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C397" s="3" t="inlineStr"/>
-      <c r="D397" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E397" s="3" t="inlineStr"/>
-      <c r="F397" s="3" t="inlineStr"/>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>GE Gas Range Igniter Switch Harness - WB18T10343</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr"/>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>ifixit, partsdr, applianceparts4all, searspartsdirect, encompass, repairclinic</t>
+        </is>
+      </c>
     </row>
     <row r="398">
-      <c r="A398" s="3" t="inlineStr">
+      <c r="A398" t="inlineStr">
         <is>
           <t>/products/ge-wb18t10387</t>
         </is>
       </c>
-      <c r="B398" s="3" t="inlineStr">
+      <c r="B398" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C398" s="3" t="inlineStr"/>
-      <c r="D398" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E398" s="3" t="inlineStr"/>
-      <c r="F398" s="3" t="inlineStr"/>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>GE Gas Cooktop Spark Ignition Switch and Harness - WB18T10387</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>applianceparts4all, genuinereplacementparts, partsdr, ifixit, encompass</t>
+        </is>
+      </c>
     </row>
     <row r="399">
-      <c r="A399" s="3" t="inlineStr">
+      <c r="A399" t="inlineStr">
         <is>
           <t>/products/ge-wb31x36766</t>
         </is>
       </c>
-      <c r="B399" s="3" t="inlineStr">
+      <c r="B399" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C399" s="3" t="inlineStr"/>
-      <c r="D399" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E399" s="3" t="inlineStr"/>
-      <c r="F399" s="3" t="inlineStr"/>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>GE Gas Range Grate Replacement Kit Black - WB31X36766</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Competitors split on color</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>partsdr, searspartsdirect, ifixit, ereplacementparts, partselect (others: Bisque)</t>
+        </is>
+      </c>
     </row>
     <row r="400">
-      <c r="A400" s="3" t="inlineStr">
+      <c r="A400" t="inlineStr">
         <is>
           <t>/products/ge-wb34x39889</t>
         </is>
       </c>
-      <c r="B400" s="3" t="inlineStr">
+      <c r="B400" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C400" s="3" t="inlineStr"/>
-      <c r="D400" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E400" s="3" t="inlineStr"/>
-      <c r="F400" s="3" t="inlineStr"/>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>GE Range Griddle Cover Assembly - WB34X39889</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr"/>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>encompass, reliableparts, genuinereplacementparts, ifixit, partadvantage, hnkparts, searspartsdirect, partselect</t>
+        </is>
+      </c>
     </row>
     <row r="401">
-      <c r="A401" s="3" t="inlineStr">
+      <c r="A401" t="inlineStr">
         <is>
           <t>/products/ge-wb48x10017</t>
         </is>
       </c>
-      <c r="B401" s="3" t="inlineStr">
+      <c r="B401" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C401" s="3" t="inlineStr"/>
-      <c r="D401" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E401" s="3" t="inlineStr"/>
-      <c r="F401" s="3" t="inlineStr"/>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>GE Microwave Metal Shelf Rack - WB48X10017</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>applianceparts4all, encompass, partselect, ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="402">
-      <c r="A402" s="3" t="inlineStr">
+      <c r="A402" t="inlineStr">
         <is>
           <t>/products/ge-wd01x10567</t>
         </is>
       </c>
-      <c r="B402" s="3" t="inlineStr">
+      <c r="B402" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C402" s="3" t="inlineStr"/>
-      <c r="D402" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E402" s="3" t="inlineStr"/>
-      <c r="F402" s="3" t="inlineStr"/>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>GE Dishwasher High-Limit Thermostat - WD01X10567</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>repairclinic, hnkparts, ifixit, applianceparts4all, partsdr, searspartsdirect</t>
+        </is>
+      </c>
     </row>
     <row r="403">
-      <c r="A403" s="3" t="inlineStr">
+      <c r="A403" t="inlineStr">
         <is>
           <t>/products/ge-wd08x10093</t>
         </is>
       </c>
-      <c r="B403" s="3" t="inlineStr">
+      <c r="B403" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C403" s="3" t="inlineStr"/>
-      <c r="D403" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E403" s="3" t="inlineStr"/>
-      <c r="F403" s="3" t="inlineStr"/>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>GE Dishwasher Door Bottom Baffle Gasket - WD08X10093</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>partsdr, applianceparts4all, genuinereplacementparts, shopjimmy, searspartsdirect, encompass, ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="404">
-      <c r="A404" s="3" t="inlineStr">
+      <c r="A404" t="inlineStr">
         <is>
           <t>/products/ge-we1m1102</t>
         </is>
       </c>
-      <c r="B404" s="3" t="inlineStr">
+      <c r="B404" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="C404" s="3" t="inlineStr"/>
-      <c r="D404" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E404" s="3" t="inlineStr"/>
-      <c r="F404" s="3" t="inlineStr"/>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>GE Dryer Terminal Block Cover - WE1M1102</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>partadvantage, partsdr, appliancepartspros, partselect, ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="3" t="inlineStr">
@@ -11531,144 +12215,212 @@
       <c r="F405" s="3" t="inlineStr"/>
     </row>
     <row r="406">
-      <c r="A406" s="3" t="inlineStr">
+      <c r="A406" t="inlineStr">
         <is>
           <t>/products/midea-12176000013099</t>
         </is>
       </c>
-      <c r="B406" s="3" t="inlineStr">
+      <c r="B406" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C406" s="3" t="inlineStr"/>
-      <c r="D406" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E406" s="3" t="inlineStr"/>
-      <c r="F406" s="3" t="inlineStr"/>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Midea Dishwasher Upper Spray Arm - 12176000013099</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>partselect, encompass</t>
+        </is>
+      </c>
     </row>
     <row r="407">
-      <c r="A407" s="3" t="inlineStr">
+      <c r="A407" t="inlineStr">
         <is>
           <t>/products/w10289909-whirlpool-microwave-cooking-tray</t>
         </is>
       </c>
-      <c r="B407" s="3" t="inlineStr">
+      <c r="B407" t="inlineStr">
         <is>
           <t>W10289909</t>
         </is>
       </c>
-      <c r="C407" s="3" t="inlineStr"/>
-      <c r="D407" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E407" s="3" t="inlineStr"/>
-      <c r="F407" s="3" t="inlineStr"/>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Whirlpool Microwave Rectangular Glass Cooking Tray - W10289909</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Brand column was part number</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>ifixit, partselect, partsdr, searspartsdirect, appliancepartspros</t>
+        </is>
+      </c>
     </row>
     <row r="408">
-      <c r="A408" s="3" t="inlineStr">
+      <c r="A408" t="inlineStr">
         <is>
           <t>/products/whirlpool-WP8212044</t>
         </is>
       </c>
-      <c r="B408" s="3" t="inlineStr">
+      <c r="B408" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C408" s="3" t="inlineStr"/>
-      <c r="D408" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E408" s="3" t="inlineStr"/>
-      <c r="F408" s="3" t="inlineStr"/>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Whirlpool KitchenAid Food Processor Work Bowl with Black Handle - WP8212044</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Duplicate of row 185 - same product</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>partsdr, searspartsdirect, encompass, ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="409">
-      <c r="A409" s="3" t="inlineStr">
+      <c r="A409" t="inlineStr">
         <is>
           <t>/products/whirlpool-w11239985-range-burner-knob</t>
         </is>
       </c>
-      <c r="B409" s="3" t="inlineStr">
+      <c r="B409" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C409" s="3" t="inlineStr"/>
-      <c r="D409" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E409" s="3" t="inlineStr"/>
-      <c r="F409" s="3" t="inlineStr"/>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Whirlpool Gas Range Surface Burner Control Knob Black Stainless - W11239985</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>searspartsdirect, ifixit, partadvantage, partsdr, appliancepartspros, shopjimmy, reliableparts, hnkparts, encompass</t>
+        </is>
+      </c>
     </row>
     <row r="410">
-      <c r="A410" s="3" t="inlineStr">
+      <c r="A410" t="inlineStr">
         <is>
           <t>/products/air-king-5s1111033</t>
         </is>
       </c>
-      <c r="B410" s="3" t="inlineStr">
+      <c r="B410" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="C410" s="3" t="inlineStr"/>
-      <c r="D410" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E410" s="3" t="inlineStr"/>
-      <c r="F410" s="3" t="inlineStr"/>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Air King Range Hood Grease Filter GF-01 - 5S1111033</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>genuinereplacementparts, encompass (airking.encompass.com)</t>
+        </is>
+      </c>
     </row>
     <row r="411">
-      <c r="A411" s="3" t="inlineStr">
+      <c r="A411" t="inlineStr">
         <is>
           <t>/products/american-standard-m916802-0020a</t>
         </is>
       </c>
-      <c r="B411" s="3" t="inlineStr">
+      <c r="B411" t="inlineStr">
         <is>
           <t>American</t>
         </is>
       </c>
-      <c r="C411" s="3" t="inlineStr"/>
-      <c r="D411" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E411" s="3" t="inlineStr"/>
-      <c r="F411" s="3" t="inlineStr"/>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>American Standard Colony Soft Faucet Lever Handle - M916802-0020A</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Only one source</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>SERP (plumbersstock)</t>
+        </is>
+      </c>
     </row>
     <row r="412">
-      <c r="A412" s="3" t="inlineStr">
+      <c r="A412" t="inlineStr">
         <is>
           <t>/products/avanti-z-20012259</t>
         </is>
       </c>
-      <c r="B412" s="3" t="inlineStr">
+      <c r="B412" t="inlineStr">
         <is>
           <t>Avanti</t>
         </is>
       </c>
-      <c r="C412" s="3" t="inlineStr"/>
-      <c r="D412" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E412" s="3" t="inlineStr"/>
-      <c r="F412" s="3" t="inlineStr"/>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Avanti Refrigerator Door Shelf - Z-20012259</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>encompass, genuinereplacementparts (reliableparts: Upper Rack)</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="3" t="inlineStr">
@@ -11691,24 +12443,32 @@
       <c r="F413" s="3" t="inlineStr"/>
     </row>
     <row r="414">
-      <c r="A414" s="3" t="inlineStr">
+      <c r="A414" t="inlineStr">
         <is>
           <t>/products/blomberg-2979560100</t>
         </is>
       </c>
-      <c r="B414" s="3" t="inlineStr">
+      <c r="B414" t="inlineStr">
         <is>
           <t>Blomberg</t>
         </is>
       </c>
-      <c r="C414" s="3" t="inlineStr"/>
-      <c r="D414" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E414" s="3" t="inlineStr"/>
-      <c r="F414" s="3" t="inlineStr"/>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Blomberg Washer Dryer Universal Stacking Kit - 2979560100</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>encompass, hnkparts</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="3" t="inlineStr">
@@ -11731,64 +12491,96 @@
       <c r="F415" s="3" t="inlineStr"/>
     </row>
     <row r="416">
-      <c r="A416" s="3" t="inlineStr">
+      <c r="A416" s="2" t="inlineStr">
         <is>
           <t>/products/blomberg-model-7293745581</t>
         </is>
       </c>
-      <c r="B416" s="3" t="inlineStr">
+      <c r="B416" s="2" t="inlineStr">
         <is>
           <t>Blomberg</t>
         </is>
       </c>
-      <c r="C416" s="3" t="inlineStr"/>
-      <c r="D416" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E416" s="3" t="inlineStr"/>
-      <c r="F416" s="3" t="inlineStr"/>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>Blomberg Refrigerator - 7293745581</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance, REVIEW</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>SERP (appliancefactoryparts lists it as a Blomberg refrigerator model)</t>
+        </is>
+      </c>
     </row>
     <row r="417">
-      <c r="A417" s="3" t="inlineStr">
+      <c r="A417" t="inlineStr">
         <is>
           <t>/products/bosch-12014099</t>
         </is>
       </c>
-      <c r="B417" s="3" t="inlineStr">
+      <c r="B417" t="inlineStr">
         <is>
           <t>Bosch</t>
         </is>
       </c>
-      <c r="C417" s="3" t="inlineStr"/>
-      <c r="D417" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E417" s="3" t="inlineStr"/>
-      <c r="F417" s="3" t="inlineStr"/>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Bosch Dishwasher Dishrack Tine Insert - 12014099</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>genuinereplacementparts, partsdr, hnkparts, shopjimmy</t>
+        </is>
+      </c>
     </row>
     <row r="418">
-      <c r="A418" s="3" t="inlineStr">
+      <c r="A418" t="inlineStr">
         <is>
           <t>/products/bosch-600071</t>
         </is>
       </c>
-      <c r="B418" s="3" t="inlineStr">
+      <c r="B418" t="inlineStr">
         <is>
           <t>Bosch</t>
         </is>
       </c>
-      <c r="C418" s="3" t="inlineStr"/>
-      <c r="D418" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E418" s="3" t="inlineStr"/>
-      <c r="F418" s="3" t="inlineStr"/>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Bosch Dishwasher Control Panel Button Set Silver - 00600071</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Competitors list part number as 00600071</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>genuinereplacementparts, ereplacementparts, reliableparts, partadvantage, repairclinic, partsdr</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="3" t="inlineStr">
@@ -11811,104 +12603,148 @@
       <c r="F419" s="3" t="inlineStr"/>
     </row>
     <row r="420">
-      <c r="A420" s="3" t="inlineStr">
+      <c r="A420" t="inlineStr">
         <is>
           <t>/products/breville-sp0010648</t>
         </is>
       </c>
-      <c r="B420" s="3" t="inlineStr">
+      <c r="B420" t="inlineStr">
         <is>
           <t>Breville</t>
         </is>
       </c>
-      <c r="C420" s="3" t="inlineStr"/>
-      <c r="D420" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E420" s="3" t="inlineStr"/>
-      <c r="F420" s="3" t="inlineStr"/>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Breville Espresso Machine BES820XL Pump Assembly - SP0010648</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr"/>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>ereplacementparts, partselect</t>
+        </is>
+      </c>
     </row>
     <row r="421">
-      <c r="A421" s="3" t="inlineStr">
+      <c r="A421" t="inlineStr">
         <is>
           <t>/products/breville-sp0023894</t>
         </is>
       </c>
-      <c r="B421" s="3" t="inlineStr">
+      <c r="B421" t="inlineStr">
         <is>
           <t>Breville</t>
         </is>
       </c>
-      <c r="C421" s="3" t="inlineStr"/>
-      <c r="D421" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E421" s="3" t="inlineStr"/>
-      <c r="F421" s="3" t="inlineStr"/>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Breville Espresso Machine Main PCB Control Board - SP0023894</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>ereplacementparts, partselect, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="422">
-      <c r="A422" s="3" t="inlineStr">
+      <c r="A422" t="inlineStr">
         <is>
           <t>/products/breville-sp0100757</t>
         </is>
       </c>
-      <c r="B422" s="3" t="inlineStr">
+      <c r="B422" t="inlineStr">
         <is>
           <t>Breville</t>
         </is>
       </c>
-      <c r="C422" s="3" t="inlineStr"/>
-      <c r="D422" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E422" s="3" t="inlineStr"/>
-      <c r="F422" s="3" t="inlineStr"/>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Breville Espresso Machine Solenoid Valve Kit 120V - SP0100757</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr"/>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>SERP (anthonysespresso, ebay), ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="423">
-      <c r="A423" s="3" t="inlineStr">
+      <c r="A423" t="inlineStr">
         <is>
           <t>/products/briggs-stratton-311353gs</t>
         </is>
       </c>
-      <c r="B423" s="3" t="inlineStr">
+      <c r="B423" t="inlineStr">
         <is>
           <t>Briggs</t>
         </is>
       </c>
-      <c r="C423" s="3" t="inlineStr"/>
-      <c r="D423" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E423" s="3" t="inlineStr"/>
-      <c r="F423" s="3" t="inlineStr"/>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Briggs &amp; Stratton Standby Generator Control Panel Assembly - 311353GS</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>SERP (ebay)</t>
+        </is>
+      </c>
     </row>
     <row r="424">
-      <c r="A424" s="3" t="inlineStr">
+      <c r="A424" t="inlineStr">
         <is>
           <t>/products/broan-sb08087153</t>
         </is>
       </c>
-      <c r="B424" s="3" t="inlineStr">
+      <c r="B424" t="inlineStr">
         <is>
           <t>Broan</t>
         </is>
       </c>
-      <c r="C424" s="3" t="inlineStr"/>
-      <c r="D424" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E424" s="3" t="inlineStr"/>
-      <c r="F424" s="3" t="inlineStr"/>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Broan Range Hood Aluminum Grease Filter - SB08087153</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>SERP (ajmadison, walmart, searspartsdirect as B08087153)</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="3" t="inlineStr">
@@ -11971,44 +12807,64 @@
       <c r="F427" s="3" t="inlineStr"/>
     </row>
     <row r="428">
-      <c r="A428" s="3" t="inlineStr">
+      <c r="A428" t="inlineStr">
         <is>
           <t>/products/danby-1-03-02-01-079</t>
         </is>
       </c>
-      <c r="B428" s="3" t="inlineStr">
+      <c r="B428" t="inlineStr">
         <is>
           <t>Danby</t>
         </is>
       </c>
-      <c r="C428" s="3" t="inlineStr"/>
-      <c r="D428" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E428" s="3" t="inlineStr"/>
-      <c r="F428" s="3" t="inlineStr"/>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Danby Beverage Center Thermostat - 1.03.02.01.079</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Part number written with dots on competitor sites</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>genuinereplacementparts, encompass</t>
+        </is>
+      </c>
     </row>
     <row r="429">
-      <c r="A429" s="3" t="inlineStr">
+      <c r="A429" t="inlineStr">
         <is>
           <t>/products/danby-890011245</t>
         </is>
       </c>
-      <c r="B429" s="3" t="inlineStr">
+      <c r="B429" t="inlineStr">
         <is>
           <t>Danby</t>
         </is>
       </c>
-      <c r="C429" s="3" t="inlineStr"/>
-      <c r="D429" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E429" s="3" t="inlineStr"/>
-      <c r="F429" s="3" t="inlineStr"/>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Danby Refrigerator Evaporator Fan Motor - 890011245</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>genuinereplacementparts, encompass, searspartsdirect, repairclinic</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="3" t="inlineStr">
@@ -12031,24 +12887,36 @@
       <c r="F430" s="3" t="inlineStr"/>
     </row>
     <row r="431">
-      <c r="A431" s="3" t="inlineStr">
+      <c r="A431" t="inlineStr">
         <is>
           <t>/products/delonghi-model-ec9335m</t>
         </is>
       </c>
-      <c r="B431" s="3" t="inlineStr">
+      <c r="B431" t="inlineStr">
         <is>
           <t>Delonghi</t>
         </is>
       </c>
-      <c r="C431" s="3" t="inlineStr"/>
-      <c r="D431" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E431" s="3" t="inlineStr"/>
-      <c r="F431" s="3" t="inlineStr"/>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>De'Longhi La Specialista Espresso Machine with Sensor Grinder Stainless Steel - EC9335M</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>SERP (delonghi.com, ebay)</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="3" t="inlineStr">
@@ -12071,124 +12939,188 @@
       <c r="F432" s="3" t="inlineStr"/>
     </row>
     <row r="433">
-      <c r="A433" s="3" t="inlineStr">
+      <c r="A433" s="2" t="inlineStr">
         <is>
           <t>/products/ego-2830216002</t>
         </is>
       </c>
-      <c r="B433" s="3" t="inlineStr">
+      <c r="B433" s="2" t="inlineStr">
         <is>
           <t>Ego</t>
         </is>
       </c>
-      <c r="C433" s="3" t="inlineStr"/>
-      <c r="D433" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E433" s="3" t="inlineStr"/>
-      <c r="F433" s="3" t="inlineStr"/>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>EGO Power Tool Electric Assembly - 2830216002</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>NOT FOUND online - inferred from EGO 2830 electric assembly series</t>
+        </is>
+      </c>
     </row>
     <row r="434">
-      <c r="A434" s="3" t="inlineStr">
+      <c r="A434" t="inlineStr">
         <is>
           <t>/products/electrolux-318262001</t>
         </is>
       </c>
-      <c r="B434" s="3" t="inlineStr">
+      <c r="B434" t="inlineStr">
         <is>
           <t>Electrolux</t>
         </is>
       </c>
-      <c r="C434" s="3" t="inlineStr"/>
-      <c r="D434" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E434" s="3" t="inlineStr"/>
-      <c r="F434" s="3" t="inlineStr"/>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Electrolux Range Oven Bottom Element Cover - 318262001</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr"/>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>applianceparts4all, searspartsdirect, hnkparts, genuinereplacementparts, partsdr, ereplacementparts (competitors brand it Frigidaire)</t>
+        </is>
+      </c>
     </row>
     <row r="435">
-      <c r="A435" s="3" t="inlineStr">
+      <c r="A435" t="inlineStr">
         <is>
           <t>/products/electrolux-5304505336</t>
         </is>
       </c>
-      <c r="B435" s="3" t="inlineStr">
+      <c r="B435" t="inlineStr">
         <is>
           <t>Electrolux</t>
         </is>
       </c>
-      <c r="C435" s="3" t="inlineStr"/>
-      <c r="D435" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E435" s="3" t="inlineStr"/>
-      <c r="F435" s="3" t="inlineStr"/>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Electrolux Front Load Washer Dispenser Drawer - 5304505336</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>partsdr, encompass, partselect, searspartsdirect (competitors brand it Frigidaire)</t>
+        </is>
+      </c>
     </row>
     <row r="436">
-      <c r="A436" s="3" t="inlineStr">
+      <c r="A436" t="inlineStr">
         <is>
           <t>/products/elica-agr04369</t>
         </is>
       </c>
-      <c r="B436" s="3" t="inlineStr">
+      <c r="B436" t="inlineStr">
         <is>
           <t>Elica</t>
         </is>
       </c>
-      <c r="C436" s="3" t="inlineStr"/>
-      <c r="D436" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E436" s="3" t="inlineStr"/>
-      <c r="F436" s="3" t="inlineStr"/>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Elica Range Hood Motor - AGR04369</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Only one source</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="437">
-      <c r="A437" s="3" t="inlineStr">
+      <c r="A437" t="inlineStr">
         <is>
           <t>/products/eureka-nec180</t>
         </is>
       </c>
-      <c r="B437" s="3" t="inlineStr">
+      <c r="B437" t="inlineStr">
         <is>
           <t>Eureka</t>
         </is>
       </c>
-      <c r="C437" s="3" t="inlineStr"/>
-      <c r="D437" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E437" s="3" t="inlineStr"/>
-      <c r="F437" s="3" t="inlineStr"/>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Eureka RapidClean Pro Cordless Stick Vacuum - NEC180</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>SERP (eureka.com, ebay)</t>
+        </is>
+      </c>
     </row>
     <row r="438">
-      <c r="A438" s="3" t="inlineStr">
+      <c r="A438" t="inlineStr">
         <is>
           <t>/products/eureka-nec280tl</t>
         </is>
       </c>
-      <c r="B438" s="3" t="inlineStr">
+      <c r="B438" t="inlineStr">
         <is>
           <t>Eureka</t>
         </is>
       </c>
-      <c r="C438" s="3" t="inlineStr"/>
-      <c r="D438" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E438" s="3" t="inlineStr"/>
-      <c r="F438" s="3" t="inlineStr"/>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Eureka RapidClean Pro Cordless Stick Vacuum with LED Headlights - NEC280TL</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>SERP (exito, fravega, camelcamelcamel)</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="3" t="inlineStr">
@@ -12231,44 +13163,68 @@
       <c r="F440" s="3" t="inlineStr"/>
     </row>
     <row r="441">
-      <c r="A441" s="3" t="inlineStr">
+      <c r="A441" t="inlineStr">
         <is>
           <t>/products/kenmore-30111-0050100-00</t>
         </is>
       </c>
-      <c r="B441" s="3" t="inlineStr">
+      <c r="B441" t="inlineStr">
         <is>
           <t>Kenmore</t>
         </is>
       </c>
-      <c r="C441" s="3" t="inlineStr"/>
-      <c r="D441" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E441" s="3" t="inlineStr"/>
-      <c r="F441" s="3" t="inlineStr"/>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Kenmore Refrigerator Ice Maker - 30111-0050100-00</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Discontinued part</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>encompass, searspartsdirect, partsdr</t>
+        </is>
+      </c>
     </row>
     <row r="442">
-      <c r="A442" s="3" t="inlineStr">
+      <c r="A442" s="2" t="inlineStr">
         <is>
           <t>/products/kenmore-model-11173022710</t>
         </is>
       </c>
-      <c r="B442" s="3" t="inlineStr">
+      <c r="B442" s="2" t="inlineStr">
         <is>
           <t>Kenmore</t>
         </is>
       </c>
-      <c r="C442" s="3" t="inlineStr"/>
-      <c r="D442" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E442" s="3" t="inlineStr"/>
-      <c r="F442" s="3" t="inlineStr"/>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>Kenmore Refrigerator - 11173022710</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance, REVIEW</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
+        <is>
+          <t>SERP (ifixit compatibility list names it as a Kenmore refrigerator)</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="3" t="inlineStr">
@@ -12291,1164 +13247,1768 @@
       <c r="F443" s="3" t="inlineStr"/>
     </row>
     <row r="444">
-      <c r="A444" s="3" t="inlineStr">
+      <c r="A444" t="inlineStr">
         <is>
           <t>/products/lg-adc30000601</t>
         </is>
       </c>
-      <c r="B444" s="3" t="inlineStr">
+      <c r="B444" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C444" s="3" t="inlineStr"/>
-      <c r="D444" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E444" s="3" t="inlineStr"/>
-      <c r="F444" s="3" t="inlineStr"/>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>LG Electric Range Oven Door Assembly - ADC30000601</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Competitors split: outer panel vs door sub-assembly</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>searspartsdirect, encompass, appliancepartspros, ifixit, hnkparts, applianceparts4all</t>
+        </is>
+      </c>
     </row>
     <row r="445">
-      <c r="A445" s="3" t="inlineStr">
+      <c r="A445" t="inlineStr">
         <is>
           <t>/products/lg-agz72909713</t>
         </is>
       </c>
-      <c r="B445" s="3" t="inlineStr">
+      <c r="B445" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C445" s="3" t="inlineStr"/>
-      <c r="D445" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E445" s="3" t="inlineStr"/>
-      <c r="F445" s="3" t="inlineStr"/>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>LG Top Load Washer Pulsator Assembly - AGZ72909713</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr"/>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>appliancepartspros, genuinereplacementparts, partsdr, encompass, searspartsdirect</t>
+        </is>
+      </c>
     </row>
     <row r="446">
-      <c r="A446" s="3" t="inlineStr">
+      <c r="A446" t="inlineStr">
         <is>
           <t>/products/lg-ahb73249103</t>
         </is>
       </c>
-      <c r="B446" s="3" t="inlineStr">
+      <c r="B446" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C446" s="3" t="inlineStr"/>
-      <c r="D446" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E446" s="3" t="inlineStr"/>
-      <c r="F446" s="3" t="inlineStr"/>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>LG Dishwasher Lower Dishrack Assembly - AHB73249103</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr"/>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>searspartsdirect, encompass</t>
+        </is>
+      </c>
     </row>
     <row r="447">
-      <c r="A447" s="3" t="inlineStr">
+      <c r="A447" t="inlineStr">
         <is>
           <t>/products/lg-akn73029001</t>
         </is>
       </c>
-      <c r="B447" s="3" t="inlineStr">
+      <c r="B447" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C447" s="3" t="inlineStr"/>
-      <c r="D447" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E447" s="3" t="inlineStr"/>
-      <c r="F447" s="3" t="inlineStr"/>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Water Filter Head Assembly - AKN73029001</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr"/>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>partsdr, ifixit, searspartsdirect, appliancepartspros, genuinereplacementparts, encompass, repairclinic</t>
+        </is>
+      </c>
     </row>
     <row r="448">
-      <c r="A448" s="3" t="inlineStr">
+      <c r="A448" t="inlineStr">
         <is>
           <t>/products/lg-ead63469515</t>
         </is>
       </c>
-      <c r="B448" s="3" t="inlineStr">
+      <c r="B448" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C448" s="3" t="inlineStr"/>
-      <c r="D448" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E448" s="3" t="inlineStr"/>
-      <c r="F448" s="3" t="inlineStr"/>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>LG Room Air Conditioner Power Cord Assembly - EAD63469515</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr"/>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>searspartsdirect, applianceparts4all, partselect, reliableparts, genuinereplacementparts, encompass, appliancepartspros</t>
+        </is>
+      </c>
     </row>
     <row r="449">
-      <c r="A449" s="3" t="inlineStr">
+      <c r="A449" t="inlineStr">
         <is>
           <t>/products/lg-lf29h8330s</t>
         </is>
       </c>
-      <c r="B449" s="3" t="inlineStr">
+      <c r="B449" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C449" s="3" t="inlineStr"/>
-      <c r="D449" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E449" s="3" t="inlineStr"/>
-      <c r="F449" s="3" t="inlineStr"/>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>LG 29 Cu. Ft. Smart Standard-Depth French Door Refrigerator Stainless Steel - LF29H8330S</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>SERP (rtings, consumerreports, ajmadison)</t>
+        </is>
+      </c>
     </row>
     <row r="450">
-      <c r="A450" s="3" t="inlineStr">
+      <c r="A450" t="inlineStr">
         <is>
           <t>/products/lg-lf31s6360s</t>
         </is>
       </c>
-      <c r="B450" s="3" t="inlineStr">
+      <c r="B450" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C450" s="3" t="inlineStr"/>
-      <c r="D450" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E450" s="3" t="inlineStr"/>
-      <c r="F450" s="3" t="inlineStr"/>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>LG 31 Cu. Ft. Smart Standard-Depth MAX French Door Refrigerator with InstaView - LF31S6360S</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>SERP (lg.com, homedepot)</t>
+        </is>
+      </c>
     </row>
     <row r="451">
-      <c r="A451" s="3" t="inlineStr">
+      <c r="A451" t="inlineStr">
         <is>
           <t>/products/lg-lfc22740sb</t>
         </is>
       </c>
-      <c r="B451" s="3" t="inlineStr">
+      <c r="B451" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C451" s="3" t="inlineStr"/>
-      <c r="D451" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E451" s="3" t="inlineStr"/>
-      <c r="F451" s="3" t="inlineStr"/>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>LG 22.4 Cu. Ft. French Door Refrigerator Smooth Black - LFC22740SB</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>SERP (lgparts.com, fix.com)</t>
+        </is>
+      </c>
     </row>
     <row r="452">
-      <c r="A452" s="3" t="inlineStr">
+      <c r="A452" t="inlineStr">
         <is>
           <t>/products/lg-ls27t3230s</t>
         </is>
       </c>
-      <c r="B452" s="3" t="inlineStr">
+      <c r="B452" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C452" s="3" t="inlineStr"/>
-      <c r="D452" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E452" s="3" t="inlineStr"/>
-      <c r="F452" s="3" t="inlineStr"/>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>LG 27 Cu. Ft. Side-by-Side Refrigerator with Ice Dispenser Stainless - LS27T3230S</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>SERP (compsource)</t>
+        </is>
+      </c>
     </row>
     <row r="453">
-      <c r="A453" s="3" t="inlineStr">
+      <c r="A453" t="inlineStr">
         <is>
           <t>/products/lg-wm6998hba</t>
         </is>
       </c>
-      <c r="B453" s="3" t="inlineStr">
+      <c r="B453" t="inlineStr">
         <is>
           <t>Lg</t>
         </is>
       </c>
-      <c r="C453" s="3" t="inlineStr"/>
-      <c r="D453" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E453" s="3" t="inlineStr"/>
-      <c r="F453" s="3" t="inlineStr"/>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>LG WashCombo All-in-One Ventless Heat Pump Washer Dryer Black Steel - WM6998HBA</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>SERP (canadianappliance spec sheet, reviewed.com)</t>
+        </is>
+      </c>
     </row>
     <row r="454">
-      <c r="A454" s="3" t="inlineStr">
+      <c r="A454" t="inlineStr">
         <is>
           <t>/products/magic-chef-model-hmcf5w4</t>
         </is>
       </c>
-      <c r="B454" s="3" t="inlineStr">
+      <c r="B454" t="inlineStr">
         <is>
           <t>Magic</t>
         </is>
       </c>
-      <c r="C454" s="3" t="inlineStr"/>
-      <c r="D454" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E454" s="3" t="inlineStr"/>
-      <c r="F454" s="3" t="inlineStr"/>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Magic Chef 5.0 Cu. Ft. Chest Freezer White - HMCF5W4</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>SERP (homedepot, notice-facile), genuinereplacementparts, appliancefactoryparts</t>
+        </is>
+      </c>
     </row>
     <row r="455">
-      <c r="A455" s="3" t="inlineStr">
+      <c r="A455" s="2" t="inlineStr">
         <is>
           <t>/products/magic-chef-model-kot152ub</t>
         </is>
       </c>
-      <c r="B455" s="3" t="inlineStr">
+      <c r="B455" s="2" t="inlineStr">
         <is>
           <t>Magic</t>
         </is>
       </c>
-      <c r="C455" s="3" t="inlineStr"/>
-      <c r="D455" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E455" s="3" t="inlineStr"/>
-      <c r="F455" s="3" t="inlineStr"/>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>Magic Chef Microwave Oven - KOT152UB</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance; REVIEW: no spec page found, capacity/wattage unknown</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="inlineStr">
+        <is>
+          <t>appliancefactoryparts (model parts page)</t>
+        </is>
+      </c>
     </row>
     <row r="456">
-      <c r="A456" s="3" t="inlineStr">
+      <c r="A456" t="inlineStr">
         <is>
           <t>/products/midea-11001010000063</t>
         </is>
       </c>
-      <c r="B456" s="3" t="inlineStr">
+      <c r="B456" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C456" s="3" t="inlineStr"/>
-      <c r="D456" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E456" s="3" t="inlineStr"/>
-      <c r="F456" s="3" t="inlineStr"/>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Midea Air Conditioner Condensate Drain Pump - 11001010000063</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr"/>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>encompass, hnkparts, appliancefactoryparts, partselect, repairclinic</t>
+        </is>
+      </c>
     </row>
     <row r="457">
-      <c r="A457" s="3" t="inlineStr">
+      <c r="A457" t="inlineStr">
         <is>
           <t>/products/midea-11002013003329</t>
         </is>
       </c>
-      <c r="B457" s="3" t="inlineStr">
+      <c r="B457" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C457" s="3" t="inlineStr"/>
-      <c r="D457" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E457" s="3" t="inlineStr"/>
-      <c r="F457" s="3" t="inlineStr"/>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Midea Front Load Washer Drive Motor - 11002013003329</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr"/>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>encompass, ifixit, hnkparts</t>
+        </is>
+      </c>
     </row>
     <row r="458">
-      <c r="A458" s="3" t="inlineStr">
+      <c r="A458" t="inlineStr">
         <is>
           <t>/products/midea-11103010000462</t>
         </is>
       </c>
-      <c r="B458" s="3" t="inlineStr">
+      <c r="B458" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C458" s="3" t="inlineStr"/>
-      <c r="D458" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E458" s="3" t="inlineStr"/>
-      <c r="F458" s="3" t="inlineStr"/>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Midea PTAC Air Conditioner Compressor - 11103010000462</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr"/>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>hnkparts, appliancefactoryparts, partselect, encompass</t>
+        </is>
+      </c>
     </row>
     <row r="459">
-      <c r="A459" s="3" t="inlineStr">
+      <c r="A459" t="inlineStr">
         <is>
           <t>/products/midea-11201007000795</t>
         </is>
       </c>
-      <c r="B459" s="3" t="inlineStr">
+      <c r="B459" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C459" s="3" t="inlineStr"/>
-      <c r="D459" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E459" s="3" t="inlineStr"/>
-      <c r="F459" s="3" t="inlineStr"/>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Midea Refrigerator Temperature Sensor - 11201007000795</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Listed as Ambient/Defrost/Freezer Sensor</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>encompass, partselect, ereplacementparts, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="460">
-      <c r="A460" s="3" t="inlineStr">
+      <c r="A460" t="inlineStr">
         <is>
           <t>/products/midea-17210900000038</t>
         </is>
       </c>
-      <c r="B460" s="3" t="inlineStr">
+      <c r="B460" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C460" s="3" t="inlineStr"/>
-      <c r="D460" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E460" s="3" t="inlineStr"/>
-      <c r="F460" s="3" t="inlineStr"/>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Midea Mini Split Air Conditioner WiFi Control Box - 17210900000038</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr"/>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>encompass, genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="461">
-      <c r="A461" s="3" t="inlineStr">
+      <c r="A461" t="inlineStr">
         <is>
           <t>/products/midea-17401202004424</t>
         </is>
       </c>
-      <c r="B461" s="3" t="inlineStr">
+      <c r="B461" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C461" s="3" t="inlineStr"/>
-      <c r="D461" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E461" s="3" t="inlineStr"/>
-      <c r="F461" s="3" t="inlineStr"/>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Midea Dehumidifier Power Cord Assembly - 17401202004424</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr"/>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>encompass, hnkparts, partselect</t>
+        </is>
+      </c>
     </row>
     <row r="462">
-      <c r="A462" s="3" t="inlineStr">
+      <c r="A462" t="inlineStr">
         <is>
           <t>/products/midea-17438000001615</t>
         </is>
       </c>
-      <c r="B462" s="3" t="inlineStr">
+      <c r="B462" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C462" s="3" t="inlineStr"/>
-      <c r="D462" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E462" s="3" t="inlineStr"/>
-      <c r="F462" s="3" t="inlineStr"/>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Midea Washer Door Lock - 17438000001615</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>encompass, searspartsdirect, partadvantage, partselect, ifixit, shopjimmy</t>
+        </is>
+      </c>
     </row>
     <row r="463">
-      <c r="A463" s="3" t="inlineStr">
+      <c r="A463" t="inlineStr">
         <is>
           <t>/products/midea-model-ctmr205m1s</t>
         </is>
       </c>
-      <c r="B463" s="3" t="inlineStr">
+      <c r="B463" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C463" s="3" t="inlineStr"/>
-      <c r="D463" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E463" s="3" t="inlineStr"/>
-      <c r="F463" s="3" t="inlineStr"/>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Midea Criterion 20.5 Cu. Ft. Top Freezer Refrigerator Stainless Steel - CTMR205M1S</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>genuinereplacementparts, encompass, appliancefactoryparts</t>
+        </is>
+      </c>
     </row>
     <row r="464">
-      <c r="A464" s="3" t="inlineStr">
+      <c r="A464" s="2" t="inlineStr">
         <is>
           <t>/products/midea-model-mstf18whr</t>
         </is>
       </c>
-      <c r="B464" s="3" t="inlineStr">
+      <c r="B464" s="2" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="C464" s="3" t="inlineStr"/>
-      <c r="D464" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E464" s="3" t="inlineStr"/>
-      <c r="F464" s="3" t="inlineStr"/>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>Midea 18 Cu. Ft. Top Freezer Refrigerator White - MSTF18WHR</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance; REVIEW: Energy Star lists brand as Seasons</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>SERP (energystar, walmart)</t>
+        </is>
+      </c>
     </row>
     <row r="465">
-      <c r="A465" s="3" t="inlineStr">
+      <c r="A465" t="inlineStr">
         <is>
           <t>/products/murray-740039ma</t>
         </is>
       </c>
-      <c r="B465" s="3" t="inlineStr">
+      <c r="B465" t="inlineStr">
         <is>
           <t>Murray</t>
         </is>
       </c>
-      <c r="C465" s="3" t="inlineStr"/>
-      <c r="D465" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E465" s="3" t="inlineStr"/>
-      <c r="F465" s="3" t="inlineStr"/>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Murray Edger Quill Assembly - 740039MA</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Discontinued (NLA)</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>jackssmallengines, searspartsdirect, ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="466">
-      <c r="A466" s="3" t="inlineStr">
+      <c r="A466" t="inlineStr">
         <is>
           <t>/products/norelco-jc302-52-electric-shaver-smartclean-cartridge</t>
         </is>
       </c>
-      <c r="B466" s="3" t="inlineStr">
+      <c r="B466" t="inlineStr">
         <is>
           <t>Norelco</t>
         </is>
       </c>
-      <c r="C466" s="3" t="inlineStr"/>
-      <c r="D466" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E466" s="3" t="inlineStr"/>
-      <c r="F466" s="3" t="inlineStr"/>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Philips Norelco SmartClean Cleaning Cartridge 2-Pack - JC302/52</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr"/>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>SERP (philips.com, newegg)</t>
+        </is>
+      </c>
     </row>
     <row r="467">
-      <c r="A467" s="3" t="inlineStr">
+      <c r="A467" t="inlineStr">
         <is>
           <t>/products/norelco-sh91-52</t>
         </is>
       </c>
-      <c r="B467" s="3" t="inlineStr">
+      <c r="B467" t="inlineStr">
         <is>
           <t>Norelco</t>
         </is>
       </c>
-      <c r="C467" s="3" t="inlineStr"/>
-      <c r="D467" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E467" s="3" t="inlineStr"/>
-      <c r="F467" s="3" t="inlineStr"/>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Philips Norelco Shaver Series 9000 Replacement Shaving Heads - SH91/52</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr"/>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>SERP (philips.com, walmart, newegg)</t>
+        </is>
+      </c>
     </row>
     <row r="468">
-      <c r="A468" s="3" t="inlineStr">
+      <c r="A468" s="2" t="inlineStr">
         <is>
           <t>/products/panasonic-f800lbq80sap</t>
         </is>
       </c>
-      <c r="B468" s="3" t="inlineStr">
+      <c r="B468" s="2" t="inlineStr">
         <is>
           <t>Panasonic</t>
         </is>
       </c>
-      <c r="C468" s="3" t="inlineStr"/>
-      <c r="D468" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E468" s="3" t="inlineStr"/>
-      <c r="F468" s="3" t="inlineStr"/>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>Panasonic Microwave Escutcheon Base - F800LBQ80SAP</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW: single source</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="469">
-      <c r="A469" s="3" t="inlineStr">
+      <c r="A469" s="2" t="inlineStr">
         <is>
           <t>/products/panasonic-ffv51vh1081</t>
         </is>
       </c>
-      <c r="B469" s="3" t="inlineStr">
+      <c r="B469" s="2" t="inlineStr">
         <is>
           <t>Panasonic</t>
         </is>
       </c>
-      <c r="C469" s="3" t="inlineStr"/>
-      <c r="D469" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E469" s="3" t="inlineStr"/>
-      <c r="F469" s="3" t="inlineStr"/>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>Panasonic Bathroom Ventilation Fan Grille Assembly - FFV51VH1081</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW: single source labels it microwave grill; FFV51VH prefix = WhisperWarm FV-0511VH1 fan</t>
+        </is>
+      </c>
+      <c r="F469" s="2" t="inlineStr">
+        <is>
+          <t>genuinereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="470">
-      <c r="A470" s="3" t="inlineStr">
+      <c r="A470" t="inlineStr">
         <is>
           <t>/products/panasonic-kx-tgc352b</t>
         </is>
       </c>
-      <c r="B470" s="3" t="inlineStr">
+      <c r="B470" t="inlineStr">
         <is>
           <t>Panasonic</t>
         </is>
       </c>
-      <c r="C470" s="3" t="inlineStr"/>
-      <c r="D470" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E470" s="3" t="inlineStr"/>
-      <c r="F470" s="3" t="inlineStr"/>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Panasonic DECT 6.0 Expandable Cordless Phone System with 2 Handsets Black - KX-TGC352B</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Model number - whole product</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>SERP (cdw, bestbuy, panasonic help)</t>
+        </is>
+      </c>
     </row>
     <row r="471">
-      <c r="A471" s="3" t="inlineStr">
+      <c r="A471" t="inlineStr">
         <is>
           <t>/products/panasonic-model-epma70</t>
         </is>
       </c>
-      <c r="B471" s="3" t="inlineStr">
+      <c r="B471" t="inlineStr">
         <is>
           <t>Panasonic</t>
         </is>
       </c>
-      <c r="C471" s="3" t="inlineStr"/>
-      <c r="D471" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E471" s="3" t="inlineStr"/>
-      <c r="F471" s="3" t="inlineStr"/>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Panasonic Real Pro Ultra Massage Chair - EP-MA70</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Model number - whole product</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>SERP (panasonic.com, techcrunch)</t>
+        </is>
+      </c>
     </row>
     <row r="472">
-      <c r="A472" s="3" t="inlineStr">
+      <c r="A472" s="2" t="inlineStr">
         <is>
           <t>/products/panasonic-model-nncd87ks</t>
         </is>
       </c>
-      <c r="B472" s="3" t="inlineStr">
+      <c r="B472" s="2" t="inlineStr">
         <is>
           <t>Panasonic</t>
         </is>
       </c>
-      <c r="C472" s="3" t="inlineStr"/>
-      <c r="D472" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E472" s="3" t="inlineStr"/>
-      <c r="F472" s="3" t="inlineStr"/>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>Panasonic 1.2 Cu. Ft. 4-in-1 Combination Microwave Oven with Air Fryer Stainless Steel - NN-CD87KS</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance; REVIEW: 34L ≈ 1.2 cu. ft.</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>SERP (panasonic.com, rtings)</t>
+        </is>
+      </c>
     </row>
     <row r="473">
-      <c r="A473" s="3" t="inlineStr">
+      <c r="A473" t="inlineStr">
         <is>
           <t>/products/panasonic-model-nnsc73ls</t>
         </is>
       </c>
-      <c r="B473" s="3" t="inlineStr">
+      <c r="B473" t="inlineStr">
         <is>
           <t>Panasonic</t>
         </is>
       </c>
-      <c r="C473" s="3" t="inlineStr"/>
-      <c r="D473" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E473" s="3" t="inlineStr"/>
-      <c r="F473" s="3" t="inlineStr"/>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Panasonic 1.6 Cu. Ft. 1200W Countertop Inverter Microwave Oven Stainless Steel - NN-SC73LS</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>SERP (panasonic help, homedepot, consumerreports)</t>
+        </is>
+      </c>
     </row>
     <row r="474">
-      <c r="A474" s="3" t="inlineStr">
+      <c r="A474" s="2" t="inlineStr">
         <is>
           <t>/products/philips-healthy-cook-300005954981</t>
         </is>
       </c>
-      <c r="B474" s="3" t="inlineStr">
+      <c r="B474" s="2" t="inlineStr">
         <is>
           <t>Philips</t>
         </is>
       </c>
-      <c r="C474" s="3" t="inlineStr"/>
-      <c r="D474" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E474" s="3" t="inlineStr"/>
-      <c r="F474" s="3" t="inlineStr"/>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>Philips Kitchen Appliance Part - 300005954981</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW: no listing found</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
     </row>
     <row r="475">
-      <c r="A475" s="3" t="inlineStr">
+      <c r="A475" s="2" t="inlineStr">
         <is>
           <t>/products/philips-healthy-cook-hr2204-70</t>
         </is>
       </c>
-      <c r="B475" s="3" t="inlineStr">
+      <c r="B475" s="2" t="inlineStr">
         <is>
           <t>Philips</t>
         </is>
       </c>
-      <c r="C475" s="3" t="inlineStr"/>
-      <c r="D475" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E475" s="3" t="inlineStr"/>
-      <c r="F475" s="3" t="inlineStr"/>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>Philips Viva Collection Soup Maker - HR2204/70</t>
+        </is>
+      </c>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW: URL says "healthy cook"; product is a soup maker</t>
+        </is>
+      </c>
+      <c r="F475" s="2" t="inlineStr">
+        <is>
+          <t>SERP (philips, shopsavvy)</t>
+        </is>
+      </c>
     </row>
     <row r="476">
-      <c r="A476" s="3" t="inlineStr">
+      <c r="A476" t="inlineStr">
         <is>
           <t>/products/philips-norelco-482232110344-personal-care-power-cord</t>
         </is>
       </c>
-      <c r="B476" s="3" t="inlineStr">
+      <c r="B476" t="inlineStr">
         <is>
           <t>Philips</t>
         </is>
       </c>
-      <c r="C476" s="3" t="inlineStr"/>
-      <c r="D476" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E476" s="3" t="inlineStr"/>
-      <c r="F476" s="3" t="inlineStr"/>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Philips Norelco Shaver Power Cord - 482232110344</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Listed as AC / black coil cord</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>partselect, ereplacementparts, encompass</t>
+        </is>
+      </c>
     </row>
     <row r="477">
-      <c r="A477" s="3" t="inlineStr">
+      <c r="A477" s="2" t="inlineStr">
         <is>
           <t>/products/pioneer-ade7039</t>
         </is>
       </c>
-      <c r="B477" s="3" t="inlineStr">
+      <c r="B477" s="2" t="inlineStr">
         <is>
           <t>Pioneer</t>
         </is>
       </c>
-      <c r="C477" s="3" t="inlineStr"/>
-      <c r="D477" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E477" s="3" t="inlineStr"/>
-      <c r="F477" s="3" t="inlineStr"/>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>Pioneer Audio Part - ADE7039</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW: no listing found; ADE7039 matches an Analog Devices chip, verify part number</t>
+        </is>
+      </c>
+      <c r="F477" s="2" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
     </row>
     <row r="478">
-      <c r="A478" s="3" t="inlineStr">
+      <c r="A478" t="inlineStr">
         <is>
           <t>/products/rheem-46-101905-01</t>
         </is>
       </c>
-      <c r="B478" s="3" t="inlineStr">
+      <c r="B478" t="inlineStr">
         <is>
           <t>Rheem</t>
         </is>
       </c>
-      <c r="C478" s="3" t="inlineStr"/>
-      <c r="D478" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E478" s="3" t="inlineStr"/>
-      <c r="F478" s="3" t="inlineStr"/>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Rheem Furnace / Air Handler Control Transformer 24V 40VA - 46-101905-01</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr"/>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>SERP (technicalhotandcoldparts, hvacprosales, partstown)</t>
+        </is>
+      </c>
     </row>
     <row r="479">
-      <c r="A479" s="3" t="inlineStr">
+      <c r="A479" t="inlineStr">
         <is>
           <t>/products/ryobi-elect-tools-039858011016</t>
         </is>
       </c>
-      <c r="B479" s="3" t="inlineStr">
+      <c r="B479" t="inlineStr">
         <is>
           <t>Ryobi</t>
         </is>
       </c>
-      <c r="C479" s="3" t="inlineStr"/>
-      <c r="D479" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E479" s="3" t="inlineStr"/>
-      <c r="F479" s="3" t="inlineStr"/>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Ryobi 18V Hybrid Air Cannon Fan Motor Assembly - 039858011016</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Fits P3340; NLA at some sellers</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>partselect, ereplacementparts</t>
+        </is>
+      </c>
     </row>
     <row r="480">
-      <c r="A480" s="3" t="inlineStr">
+      <c r="A480" t="inlineStr">
         <is>
           <t>/products/samsung-bn59-01456a</t>
         </is>
       </c>
-      <c r="B480" s="3" t="inlineStr">
+      <c r="B480" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C480" s="3" t="inlineStr"/>
-      <c r="D480" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E480" s="3" t="inlineStr"/>
-      <c r="F480" s="3" t="inlineStr"/>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Samsung TV SolarCell Smart Remote Control - BN59-01456A</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>2024 Eco Smart Control (The Frame LS03D)</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>shopjimmy, encompass, partselect, appliancepartspros</t>
+        </is>
+      </c>
     </row>
     <row r="481">
-      <c r="A481" s="3" t="inlineStr">
+      <c r="A481" s="2" t="inlineStr">
         <is>
           <t>/products/samsung-dve45b6300v-a3</t>
         </is>
       </c>
-      <c r="B481" s="3" t="inlineStr">
+      <c r="B481" s="2" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C481" s="3" t="inlineStr"/>
-      <c r="D481" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E481" s="3" t="inlineStr"/>
-      <c r="F481" s="3" t="inlineStr"/>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>Samsung 7.5 Cu. Ft. Smart Electric Dryer with Steam Sanitize+ Brushed Black - DVE45B6300V/A3</t>
+        </is>
+      </c>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance; REVIEW: V = Brushed Black inferred from Samsung suffix convention</t>
+        </is>
+      </c>
+      <c r="F481" s="2" t="inlineStr">
+        <is>
+          <t>SERP (samsung.com sibling variants, ajmadison)</t>
+        </is>
+      </c>
     </row>
     <row r="482">
-      <c r="A482" s="3" t="inlineStr">
+      <c r="A482" t="inlineStr">
         <is>
           <t>/products/samsung-model-un50nu6900fxza</t>
         </is>
       </c>
-      <c r="B482" s="3" t="inlineStr">
+      <c r="B482" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C482" s="3" t="inlineStr"/>
-      <c r="D482" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E482" s="3" t="inlineStr"/>
-      <c r="F482" s="3" t="inlineStr"/>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Samsung 50" NU6900 4K UHD Smart LED TV - UN50NU6900FXZA</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Model number - whole product</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>SERP (ebay, greentoe, woot)</t>
+        </is>
+      </c>
     </row>
     <row r="483">
-      <c r="A483" s="3" t="inlineStr">
+      <c r="A483" t="inlineStr">
         <is>
           <t>/products/samsung-ra-f36db433-aa</t>
         </is>
       </c>
-      <c r="B483" s="3" t="inlineStr">
+      <c r="B483" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C483" s="3" t="inlineStr"/>
-      <c r="D483" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E483" s="3" t="inlineStr"/>
-      <c r="F483" s="3" t="inlineStr"/>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Samsung Bespoke 4-Door French Door Refrigerator Bottom Panel Charcoal Glass - RA-F36DB433/AA</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr"/>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>SERP (walmart, plessers, canadianappliance)</t>
+        </is>
+      </c>
     </row>
     <row r="484">
-      <c r="A484" s="3" t="inlineStr">
+      <c r="A484" t="inlineStr">
         <is>
           <t>/products/samsung-rf90f23aeceaa</t>
         </is>
       </c>
-      <c r="B484" s="3" t="inlineStr">
+      <c r="B484" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C484" s="3" t="inlineStr"/>
-      <c r="D484" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E484" s="3" t="inlineStr"/>
-      <c r="F484" s="3" t="inlineStr"/>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Samsung Bespoke 23 Cu. Ft. Counter Depth 4-Door French Door Refrigerator with Family Hub+ - RF90F23AECEAA</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>SERP (ajmadison, energystar, townappliance)</t>
+        </is>
+      </c>
     </row>
     <row r="485">
-      <c r="A485" s="3" t="inlineStr">
+      <c r="A485" t="inlineStr">
         <is>
           <t>/products/samsung-wd53dba900hba1</t>
         </is>
       </c>
-      <c r="B485" s="3" t="inlineStr">
+      <c r="B485" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C485" s="3" t="inlineStr"/>
-      <c r="D485" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E485" s="3" t="inlineStr"/>
-      <c r="F485" s="3" t="inlineStr"/>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Samsung Bespoke AI 5.3 Cu. Ft. Ventless Heat Pump Washer Dryer Combo - WD53DBA900HBA1</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>shopjimmy, SERP (ajmadison, townappliance)</t>
+        </is>
+      </c>
     </row>
     <row r="486">
-      <c r="A486" s="3" t="inlineStr">
+      <c r="A486" t="inlineStr">
         <is>
           <t>/products/sharp-fpnlcb420mrk0</t>
         </is>
       </c>
-      <c r="B486" s="3" t="inlineStr">
+      <c r="B486" t="inlineStr">
         <is>
           <t>Sharp</t>
         </is>
       </c>
-      <c r="C486" s="3" t="inlineStr"/>
-      <c r="D486" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E486" s="3" t="inlineStr"/>
-      <c r="F486" s="3" t="inlineStr"/>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Sharp Microwave Control Panel Sub-Assembly - FPNLCB420MRK0</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr"/>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>ifixit, encompass, searspartsdirect, appliancefactoryparts, repairclinic</t>
+        </is>
+      </c>
     </row>
     <row r="487">
-      <c r="A487" s="3" t="inlineStr">
+      <c r="A487" t="inlineStr">
         <is>
           <t>/products/sharp-qaccda092wjpz</t>
         </is>
       </c>
-      <c r="B487" s="3" t="inlineStr">
+      <c r="B487" t="inlineStr">
         <is>
           <t>Sharp</t>
         </is>
       </c>
-      <c r="C487" s="3" t="inlineStr"/>
-      <c r="D487" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E487" s="3" t="inlineStr"/>
-      <c r="F487" s="3" t="inlineStr"/>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Sharp LCD TV AC Power Cord - QACCDA092WJPZ</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr"/>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>encompass, shopjimmy</t>
+        </is>
+      </c>
     </row>
     <row r="488">
-      <c r="A488" s="3" t="inlineStr">
+      <c r="A488" s="2" t="inlineStr">
         <is>
           <t>/products/snapper-1687787yp</t>
         </is>
       </c>
-      <c r="B488" s="3" t="inlineStr">
+      <c r="B488" s="2" t="inlineStr">
         <is>
           <t>Snapper</t>
         </is>
       </c>
-      <c r="C488" s="3" t="inlineStr"/>
-      <c r="D488" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E488" s="3" t="inlineStr"/>
-      <c r="F488" s="3" t="inlineStr"/>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>Snapper Lawn Tractor Part - 1687787YP</t>
+        </is>
+      </c>
+      <c r="D488" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW: part name not shown in results</t>
+        </is>
+      </c>
+      <c r="F488" s="2" t="inlineStr">
+        <is>
+          <t>ereplacementparts (SPX2246 parts list)</t>
+        </is>
+      </c>
     </row>
     <row r="489">
-      <c r="A489" s="3" t="inlineStr">
+      <c r="A489" t="inlineStr">
         <is>
           <t>/products/speed-queen-310p4</t>
         </is>
       </c>
-      <c r="B489" s="3" t="inlineStr">
+      <c r="B489" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="C489" s="3" t="inlineStr"/>
-      <c r="D489" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E489" s="3" t="inlineStr"/>
-      <c r="F489" s="3" t="inlineStr"/>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Speed Queen Washer Dryer Ratchet Extension Tool - 310P4</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr"/>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>reliableparts, partsdr, searspartsdirect, hnkparts, appliancepartspros, partadvantage, applianceparts4all</t>
+        </is>
+      </c>
     </row>
     <row r="490">
-      <c r="A490" s="3" t="inlineStr">
+      <c r="A490" t="inlineStr">
         <is>
           <t>/products/tcl-08-l12clj1-pw200aa</t>
         </is>
       </c>
-      <c r="B490" s="3" t="inlineStr">
+      <c r="B490" t="inlineStr">
         <is>
           <t>Tcl</t>
         </is>
       </c>
-      <c r="C490" s="3" t="inlineStr"/>
-      <c r="D490" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E490" s="3" t="inlineStr"/>
-      <c r="F490" s="3" t="inlineStr"/>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>TCL 43" LED TV Power Supply Board - 08-L12CLJ1-PW200AA</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Board 40-L12CH4-PWD1CG, fits 43S434</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>SERP (tvpartstoday, ebay)</t>
+        </is>
+      </c>
     </row>
     <row r="491">
-      <c r="A491" s="3" t="inlineStr">
+      <c r="A491" s="2" t="inlineStr">
         <is>
           <t>/products/tempur-pedic-hsc-tp-rf-taes</t>
         </is>
       </c>
-      <c r="B491" s="3" t="inlineStr">
+      <c r="B491" s="2" t="inlineStr">
         <is>
           <t>Tempur</t>
         </is>
       </c>
-      <c r="C491" s="3" t="inlineStr"/>
-      <c r="D491" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E491" s="3" t="inlineStr"/>
-      <c r="F491" s="3" t="inlineStr"/>
+      <c r="C491" s="2" t="inlineStr">
+        <is>
+          <t>Tempur-Pedic Ergo Premier Adjustable Bed Remote Control - HSC-TP-RF-TAES</t>
+        </is>
+      </c>
+      <c r="D491" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW: single source</t>
+        </is>
+      </c>
+      <c r="F491" s="2" t="inlineStr">
+        <is>
+          <t>SERP (ebay)</t>
+        </is>
+      </c>
     </row>
     <row r="492">
-      <c r="A492" s="3" t="inlineStr">
+      <c r="A492" t="inlineStr">
         <is>
           <t>/products/whirlpool-4344759</t>
         </is>
       </c>
-      <c r="B492" s="3" t="inlineStr">
+      <c r="B492" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C492" s="3" t="inlineStr"/>
-      <c r="D492" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E492" s="3" t="inlineStr"/>
-      <c r="F492" s="3" t="inlineStr"/>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Whirlpool KitchenAid Compact Refrigerator Door Gasket - 4344759</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Discontinued at most sellers</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>encompass, partsdr, reliableparts, partselect, repairclinic</t>
+        </is>
+      </c>
     </row>
     <row r="493">
-      <c r="A493" s="3" t="inlineStr">
+      <c r="A493" t="inlineStr">
         <is>
           <t>/products/whirlpool-4392067</t>
         </is>
       </c>
-      <c r="B493" s="3" t="inlineStr">
+      <c r="B493" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C493" s="3" t="inlineStr"/>
-      <c r="D493" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E493" s="3" t="inlineStr"/>
-      <c r="F493" s="3" t="inlineStr"/>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Whirlpool Dryer Maintenance Repair Kit - 4392067</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr"/>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>appliancepartspros, partsdr, repairclinic, applianceparts4all, encompass, hnkparts</t>
+        </is>
+      </c>
     </row>
     <row r="494">
-      <c r="A494" s="3" t="inlineStr">
+      <c r="A494" t="inlineStr">
         <is>
           <t>/products/whirlpool-67001895</t>
         </is>
       </c>
-      <c r="B494" s="3" t="inlineStr">
+      <c r="B494" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C494" s="3" t="inlineStr"/>
-      <c r="D494" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E494" s="3" t="inlineStr"/>
-      <c r="F494" s="3" t="inlineStr"/>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Whirlpool Refrigerator Evaporator Assembly - 67001895</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr"/>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>encompass, partsdr, appliancepartspros</t>
+        </is>
+      </c>
     </row>
     <row r="495">
-      <c r="A495" s="3" t="inlineStr">
+      <c r="A495" s="2" t="inlineStr">
         <is>
           <t>/products/whirlpool-model-3xes0fhqkb01</t>
         </is>
       </c>
-      <c r="B495" s="3" t="inlineStr">
+      <c r="B495" s="2" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C495" s="3" t="inlineStr"/>
-      <c r="D495" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E495" s="3" t="inlineStr"/>
-      <c r="F495" s="3" t="inlineStr"/>
+      <c r="C495" s="2" t="inlineStr">
+        <is>
+          <t>Whirlpool Refrigerator - 3XES0FHQKB01</t>
+        </is>
+      </c>
+      <c r="D495" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance; REVIEW: no spec page found</t>
+        </is>
+      </c>
+      <c r="F495" s="2" t="inlineStr">
+        <is>
+          <t>appliancefactoryparts (model parts page)</t>
+        </is>
+      </c>
     </row>
     <row r="496">
-      <c r="A496" s="3" t="inlineStr">
+      <c r="A496" t="inlineStr">
         <is>
           <t>/products/whirlpool-model-wrqa59cnkz</t>
         </is>
       </c>
-      <c r="B496" s="3" t="inlineStr">
+      <c r="B496" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C496" s="3" t="inlineStr"/>
-      <c r="D496" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E496" s="3" t="inlineStr"/>
-      <c r="F496" s="3" t="inlineStr"/>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Whirlpool 36" 19.4 Cu. Ft. Counter Depth 4-Door French Door Refrigerator Fingerprint Resistant Stainless - WRQA59CNKZ</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Model number - whole appliance</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>SERP (thebrick, reviewed, rtings, bestbuy.ca)</t>
+        </is>
+      </c>
     </row>
     <row r="497">
-      <c r="A497" s="3" t="inlineStr">
+      <c r="A497" s="2" t="inlineStr">
         <is>
           <t>/products/whirlpool-w10540089</t>
         </is>
       </c>
-      <c r="B497" s="3" t="inlineStr">
+      <c r="B497" s="2" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C497" s="3" t="inlineStr"/>
-      <c r="D497" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E497" s="3" t="inlineStr"/>
-      <c r="F497" s="3" t="inlineStr"/>
+      <c r="C497" s="2" t="inlineStr">
+        <is>
+          <t>Whirlpool Appliance Part - W10540089</t>
+        </is>
+      </c>
+      <c r="D497" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="E497" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW: no listing found on competitors or SERP</t>
+        </is>
+      </c>
+      <c r="F497" s="2" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
     </row>
     <row r="498">
-      <c r="A498" s="3" t="inlineStr">
+      <c r="A498" t="inlineStr">
         <is>
           <t>/products/whirlpool-w10727603</t>
         </is>
       </c>
-      <c r="B498" s="3" t="inlineStr">
+      <c r="B498" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C498" s="3" t="inlineStr"/>
-      <c r="D498" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E498" s="3" t="inlineStr"/>
-      <c r="F498" s="3" t="inlineStr"/>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Whirlpool KitchenAid Microwave Door Assembly - W10727603</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr"/>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>reliableparts, encompass, partselect, repairclinic</t>
+        </is>
+      </c>
     </row>
     <row r="499">
-      <c r="A499" s="3" t="inlineStr">
+      <c r="A499" t="inlineStr">
         <is>
           <t>/products/whirlpool-w10803367</t>
         </is>
       </c>
-      <c r="B499" s="3" t="inlineStr">
+      <c r="B499" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C499" s="3" t="inlineStr"/>
-      <c r="D499" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E499" s="3" t="inlineStr"/>
-      <c r="F499" s="3" t="inlineStr"/>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Whirlpool KitchenAid Dishwasher Touchpad Control Panel Black - W10803367</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr"/>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>applianceparts4all, appliancepartspros, encompass, searspartsdirect, reliableparts, partsdr, repairclinic</t>
+        </is>
+      </c>
     </row>
     <row r="500">
-      <c r="A500" s="3" t="inlineStr">
+      <c r="A500" t="inlineStr">
         <is>
           <t>/products/whirlpool-w11206737</t>
         </is>
       </c>
-      <c r="B500" s="3" t="inlineStr">
+      <c r="B500" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C500" s="3" t="inlineStr"/>
-      <c r="D500" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E500" s="3" t="inlineStr"/>
-      <c r="F500" s="3" t="inlineStr"/>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Whirlpool Range Hood Rotary Light / Fan Switch - W11206737</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr"/>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>applianceparts4all, reliableparts, partsdr, appliancepartspros, repairclinic, encompass</t>
+        </is>
+      </c>
     </row>
     <row r="501">
-      <c r="A501" s="3" t="inlineStr">
+      <c r="A501" t="inlineStr">
         <is>
           <t>/products/whirlpool-w11346622</t>
         </is>
       </c>
-      <c r="B501" s="3" t="inlineStr">
+      <c r="B501" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="C501" s="3" t="inlineStr"/>
-      <c r="D501" s="3" t="inlineStr">
-        <is>
-          <t>Not processed yet</t>
-        </is>
-      </c>
-      <c r="E501" s="3" t="inlineStr"/>
-      <c r="F501" s="3" t="inlineStr"/>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Whirlpool Refrigerator Water Reservoir Tank Assembly - W11346622</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr"/>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>hnkparts, appliancepartspros, reliableparts, applianceparts4all, partsdr, encompass</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F501"/>
